--- a/run/nhanes_pullrequest_IndVsArea_07.30.2026.xlsx
+++ b/run/nhanes_pullrequest_IndVsArea_07.30.2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jg1671/Documents/GitHub/nhanes_area_ses/run/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0F679C-7E67-9244-A2C4-9C1987F3623C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC6DD6C-88E1-B243-8078-C2C267C7FE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="69980" yWindow="600" windowWidth="35620" windowHeight="19760" xr2:uid="{BFFDAA01-B797-C24A-A87F-A362CCE94DEB}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16240" xr2:uid="{BFFDAA01-B797-C24A-A87F-A362CCE94DEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable_List" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3993" uniqueCount="1015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4176" uniqueCount="1106">
   <si>
     <t>RECODE</t>
   </si>
@@ -2416,9 +2416,6 @@
     <t>q_told_bronch</t>
   </si>
   <si>
-    <t>q_told_diabetes</t>
-  </si>
-  <si>
     <t>q_told_prediabetes</t>
   </si>
   <si>
@@ -2524,9 +2521,6 @@
     <t>q_med_diab</t>
   </si>
   <si>
-    <t>q_age_diab</t>
-  </si>
-  <si>
     <t>fg</t>
   </si>
   <si>
@@ -3083,6 +3077,285 @@
   </si>
   <si>
     <t>q_told_overwt_lt20</t>
+  </si>
+  <si>
+    <t>hb</t>
+  </si>
+  <si>
+    <t>Ever told  you had congestive heart failure?</t>
+  </si>
+  <si>
+    <t>q_told_chf</t>
+  </si>
+  <si>
+    <t>SPXBFEV1</t>
+  </si>
+  <si>
+    <t>Bronchodilator 2nd Test Spirometry, Forced Expiratory Volume in the first 1.0 second, in mL.</t>
+  </si>
+  <si>
+    <t>SPXBFVC</t>
+  </si>
+  <si>
+    <t>Bronchodilator 2nd Test Spirometry, Forced Vital Capacity, in mL.</t>
+  </si>
+  <si>
+    <t>SPXNFEV1</t>
+  </si>
+  <si>
+    <t>SPXNQFVC</t>
+  </si>
+  <si>
+    <t>Baseline 1st Test Spirometry, Forced Vital Capacity Quality Attribute.</t>
+  </si>
+  <si>
+    <t>fev1_post</t>
+  </si>
+  <si>
+    <t>fvc_post</t>
+  </si>
+  <si>
+    <t>fev1_pre</t>
+  </si>
+  <si>
+    <t>fvc_pre</t>
+  </si>
+  <si>
+    <t>overall Taste &amp; Smell Exam Status</t>
+  </si>
+  <si>
+    <t>q_told_anybronch</t>
+  </si>
+  <si>
+    <t>Albumin (mg/dL)</t>
+  </si>
+  <si>
+    <t>alb</t>
+  </si>
+  <si>
+    <t>LUXCAPM</t>
+  </si>
+  <si>
+    <t>Median controlled attenuated parameter (CAP) This indicator is presented as a whole number XXX, and the units for this measure are decibels per meter (dB/m).</t>
+  </si>
+  <si>
+    <t>LUXSMED</t>
+  </si>
+  <si>
+    <t>Median liver stiffness (E) This indicator is presented with one digit to the right of the decimal ratio (e.g. XX.X), and the units for this measure are kilopascals (kPa).</t>
+  </si>
+  <si>
+    <t>liver_stiff</t>
+  </si>
+  <si>
+    <t>LUXSIQRM</t>
+  </si>
+  <si>
+    <t>Ratio of the stiffness IQRe / median E stiffness value. This indicator is presented as a percent with one digit to the right of the decimal, (e.g. XX.X %).</t>
+  </si>
+  <si>
+    <t>liver_cap</t>
+  </si>
+  <si>
+    <t>liver_iqr</t>
+  </si>
+  <si>
+    <t>SPXNFVC</t>
+  </si>
+  <si>
+    <t>Baseline 1st Test Spirometry, Forced Vital Capacity, in mL</t>
+  </si>
+  <si>
+    <t>fvc_preq</t>
+  </si>
+  <si>
+    <t>MCQ160O</t>
+  </si>
+  <si>
+    <t>MCQ160P</t>
+  </si>
+  <si>
+    <t>q_told_stroke</t>
+  </si>
+  <si>
+    <t>MCQ160E</t>
+  </si>
+  <si>
+    <t>MCQ160e</t>
+  </si>
+  <si>
+    <t>Has a doctor or other health professional ever told {you/SP} that {you/s/he} . . .had a stroke?</t>
+  </si>
+  <si>
+    <t>q_told_diab_age</t>
+  </si>
+  <si>
+    <t>q_told_diab_age1</t>
+  </si>
+  <si>
+    <t>q_told_diab_age2</t>
+  </si>
+  <si>
+    <t>q_told_diab</t>
+  </si>
+  <si>
+    <t>Have you/Has SP ever been told by a doctor or health professional that {you have/{he/she/SP} has} diabetes or sugar diabetes?</t>
+  </si>
+  <si>
+    <t>DPQ010</t>
+  </si>
+  <si>
+    <t>Over the last 2 weeks, how often have you been bothered by the following problems: little interest or pleasure in doing things? Would you say…</t>
+  </si>
+  <si>
+    <t>Over the last 2 weeks, how often have you been bothered by the following problems:] feeling down, depressed, or hopeless?</t>
+  </si>
+  <si>
+    <t>DPQ020</t>
+  </si>
+  <si>
+    <t>DPQ030</t>
+  </si>
+  <si>
+    <t>[Over the last 2 weeks, how often have you been bothered by the following problems:] trouble falling or staying asleep, or sleeping too much?</t>
+  </si>
+  <si>
+    <t>DPQ040</t>
+  </si>
+  <si>
+    <t>[Over the last 2 weeks, how often have you been bothered by the following problems:] feeling tired or having little energy?</t>
+  </si>
+  <si>
+    <t>[Over the last 2 weeks, how often have you been bothered by the following problems:] poor appetite or overeating?</t>
+  </si>
+  <si>
+    <t>DPQ050</t>
+  </si>
+  <si>
+    <t>[Over the last 2 weeks, how often have you been bothered by the following problems:] feeling bad about yourself - or that you are a failure or have let yourself or your family down?</t>
+  </si>
+  <si>
+    <t>DPQ060</t>
+  </si>
+  <si>
+    <t>[Over the last 2 weeks, how often have you been bothered by the following problems:] trouble concentrating on things, such as reading the newspaper or watching TV?</t>
+  </si>
+  <si>
+    <t>DPQ070</t>
+  </si>
+  <si>
+    <t>[Over the last 2 weeks, how often have you been bothered by the following problems:] moving or speaking so slowly that other people could have noticed? Or the opposite - being so fidgety or restless that you have been moving around a lot more than usual?</t>
+  </si>
+  <si>
+    <t>DPQ080</t>
+  </si>
+  <si>
+    <t>Over the last 2 weeks, how often have you been bothered by the following problems: Thoughts that you would be better off dead or of hurting yourself in some way?</t>
+  </si>
+  <si>
+    <t>DPQ090</t>
+  </si>
+  <si>
+    <t>BOX 2. CHECK ITEM DPQ095: IF RESPONSE TO ANY OF QUESTIONS DPQ010 - DPQ090 = 1, 2, OR 3, GO TO DPQ100. OTHERWISE, GO TO NEXT SECTION</t>
+  </si>
+  <si>
+    <t>DPQ095</t>
+  </si>
+  <si>
+    <t>How difficult have these problems made it for you to do your work, take care of things at home, or get along with people?</t>
+  </si>
+  <si>
+    <t>DPQ100</t>
+  </si>
+  <si>
+    <t>q_phq_interest</t>
+  </si>
+  <si>
+    <t>q_phq_sleep</t>
+  </si>
+  <si>
+    <t>q_phq_energy</t>
+  </si>
+  <si>
+    <t>q_phq_appetite</t>
+  </si>
+  <si>
+    <t>q_phq_feelbad</t>
+  </si>
+  <si>
+    <t>q_phq_conc</t>
+  </si>
+  <si>
+    <t>q_phq_slow</t>
+  </si>
+  <si>
+    <t>q_phq_hurtself</t>
+  </si>
+  <si>
+    <t>q_phq_check</t>
+  </si>
+  <si>
+    <t>q_phq_work</t>
+  </si>
+  <si>
+    <t>q_phq_hope</t>
+  </si>
+  <si>
+    <t>RIDSTATR</t>
+  </si>
+  <si>
+    <t>Interview and Examination Status of the Sample Person</t>
+  </si>
+  <si>
+    <t>BPXOSY1</t>
+  </si>
+  <si>
+    <t>BPXOSY2</t>
+  </si>
+  <si>
+    <t>BPXOSY3</t>
+  </si>
+  <si>
+    <t>BPXODI1</t>
+  </si>
+  <si>
+    <t>BPXODI2</t>
+  </si>
+  <si>
+    <t>BPXODI3</t>
+  </si>
+  <si>
+    <t>Systolic - 1st oscillometric reading</t>
+  </si>
+  <si>
+    <t>Systolic - 2nd oscillometric reading</t>
+  </si>
+  <si>
+    <t>Systolic - 3rd oscillometric reading</t>
+  </si>
+  <si>
+    <t>Diastolic - 1st oscillometric reading</t>
+  </si>
+  <si>
+    <t>Diastolic - 2nd oscillometric reading</t>
+  </si>
+  <si>
+    <t>Diastolic - 3rd oscillometric reading</t>
+  </si>
+  <si>
+    <t>MCQ180f</t>
+  </si>
+  <si>
+    <t>How old {were you/was SP} when {you were/s/he was} first told {you/s/he} . . .had a stroke?</t>
+  </si>
+  <si>
+    <t>MCQ180F</t>
+  </si>
+  <si>
+    <t>q_told_stroke_age</t>
+  </si>
+  <si>
+    <t>LBXTLG</t>
   </si>
 </sst>
 </file>
@@ -3609,7 +3882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3D6F9ED-9DEC-0147-B030-50BD2869D005}">
-  <dimension ref="A1:G255"/>
+  <dimension ref="A1:G291"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="19.5" style="5" customWidth="1"/>
@@ -3715,18 +3988,16 @@
       <c r="A6" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="28" t="s">
-        <v>122</v>
+      <c r="B6" s="18" t="s">
+        <v>1087</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>120</v>
+        <v>1088</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>119</v>
-      </c>
+        <v>704</v>
+      </c>
+      <c r="E6" s="18"/>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
     </row>
@@ -3735,77 +4006,73 @@
         <v>121</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>193</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="F7" s="20"/>
+        <v>119</v>
+      </c>
+      <c r="F7" s="16"/>
       <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="18" t="s">
-        <v>212</v>
+        <v>121</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>211</v>
+        <v>129</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F8" s="20"/>
       <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="18" t="s">
-        <v>121</v>
+        <v>212</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>123</v>
+        <v>210</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>739</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="18" t="s">
         <v>121</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>193</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F10" s="20" t="s">
         <v>6</v>
@@ -3819,22 +4086,22 @@
         <v>121</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>177</v>
+        <v>127</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>193</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>283</v>
+        <v>136</v>
       </c>
       <c r="F11" s="20" t="s">
         <v>6</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3842,27 +4109,33 @@
         <v>121</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
+      <c r="E12" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>742</v>
+      </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="18" t="s">
         <v>121</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D13" s="18" t="s">
         <v>193</v>
@@ -3876,17 +4149,15 @@
         <v>121</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>190</v>
-      </c>
+      <c r="E14" s="28"/>
       <c r="F14" s="20"/>
       <c r="G14" s="20"/>
     </row>
@@ -3895,16 +4166,16 @@
         <v>121</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>193</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="F15" s="20"/>
       <c r="G15" s="20"/>
@@ -3914,16 +4185,16 @@
         <v>121</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>193</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F16" s="20"/>
       <c r="G16" s="20"/>
@@ -3933,16 +4204,16 @@
         <v>121</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D17" s="18" t="s">
         <v>193</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F17" s="20"/>
       <c r="G17" s="20"/>
@@ -3952,7 +4223,7 @@
         <v>121</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>187</v>
@@ -3961,7 +4232,7 @@
         <v>193</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
@@ -3971,10 +4242,10 @@
         <v>121</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D19" s="18" t="s">
         <v>193</v>
@@ -3990,16 +4261,16 @@
         <v>121</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="D20" s="18" t="s">
         <v>193</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F20" s="20"/>
       <c r="G20" s="20"/>
@@ -4009,7 +4280,7 @@
         <v>121</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>222</v>
@@ -4028,34 +4299,36 @@
         <v>121</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>654</v>
+        <v>219</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>655</v>
+        <v>222</v>
       </c>
       <c r="D22" s="18" t="s">
         <v>193</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>656</v>
+        <v>285</v>
       </c>
       <c r="F22" s="20"/>
       <c r="G22" s="20"/>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="18" t="s">
-        <v>224</v>
+        <v>121</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>227</v>
+        <v>654</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>228</v>
+        <v>655</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="E23" s="18"/>
+        <v>193</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>656</v>
+      </c>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
     </row>
@@ -4064,17 +4337,15 @@
         <v>224</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D24" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="E24" s="18" t="s">
-        <v>829</v>
-      </c>
+      <c r="E24" s="18"/>
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
     </row>
@@ -4083,18 +4354,18 @@
         <v>224</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="D25" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>830</v>
-      </c>
-      <c r="F25" s="16"/>
+        <v>827</v>
+      </c>
+      <c r="F25" s="20"/>
       <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7">
@@ -4102,16 +4373,16 @@
         <v>224</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D26" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="F26" s="16"/>
       <c r="G26" s="20"/>
@@ -4121,16 +4392,16 @@
         <v>224</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>831</v>
+        <v>1013</v>
       </c>
       <c r="F27" s="16"/>
       <c r="G27" s="20"/>
@@ -4140,16 +4411,16 @@
         <v>224</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D28" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="F28" s="16"/>
       <c r="G28" s="20"/>
@@ -4159,16 +4430,16 @@
         <v>224</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="D29" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="F29" s="16"/>
       <c r="G29" s="20"/>
@@ -4178,16 +4449,16 @@
         <v>224</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>239</v>
+        <v>281</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="D30" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="F30" s="16"/>
       <c r="G30" s="20"/>
@@ -4197,16 +4468,16 @@
         <v>224</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D31" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="F31" s="16"/>
       <c r="G31" s="20"/>
@@ -4216,16 +4487,16 @@
         <v>224</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D32" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="F32" s="16"/>
       <c r="G32" s="20"/>
@@ -4235,16 +4506,16 @@
         <v>224</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D33" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="F33" s="16"/>
       <c r="G33" s="20"/>
@@ -4254,16 +4525,16 @@
         <v>224</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D34" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="F34" s="16"/>
       <c r="G34" s="20"/>
@@ -4273,16 +4544,16 @@
         <v>224</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D35" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="F35" s="16"/>
       <c r="G35" s="20"/>
@@ -4292,54 +4563,54 @@
         <v>224</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>710</v>
+        <v>249</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>711</v>
+        <v>250</v>
       </c>
       <c r="D36" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
+      <c r="G36" s="20"/>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="18" t="s">
         <v>224</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D37" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="F37" s="16"/>
-      <c r="G37" s="20"/>
+      <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="18" t="s">
         <v>224</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>279</v>
+        <v>707</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>268</v>
+        <v>708</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="F38" s="16"/>
       <c r="G38" s="20"/>
@@ -4349,16 +4620,16 @@
         <v>224</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D39" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="F39" s="16"/>
       <c r="G39" s="20"/>
@@ -4368,16 +4639,16 @@
         <v>224</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D40" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="F40" s="16"/>
       <c r="G40" s="20"/>
@@ -4387,16 +4658,16 @@
         <v>224</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="D41" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="F41" s="16"/>
       <c r="G41" s="20"/>
@@ -4406,16 +4677,16 @@
         <v>224</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>398</v>
+        <v>287</v>
       </c>
       <c r="D42" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="F42" s="16"/>
       <c r="G42" s="20"/>
@@ -4424,17 +4695,17 @@
       <c r="A43" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="B43" s="18" t="s">
-        <v>291</v>
+      <c r="B43" s="28" t="s">
+        <v>290</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>276</v>
+        <v>398</v>
       </c>
       <c r="D43" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="F43" s="16"/>
       <c r="G43" s="20"/>
@@ -4444,7 +4715,7 @@
         <v>224</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>276</v>
@@ -4453,7 +4724,7 @@
         <v>229</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="F44" s="16"/>
       <c r="G44" s="20"/>
@@ -4463,18 +4734,18 @@
         <v>224</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>349</v>
+        <v>292</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>468</v>
+        <v>276</v>
       </c>
       <c r="D45" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>848</v>
-      </c>
-      <c r="F45" s="20"/>
+        <v>845</v>
+      </c>
+      <c r="F45" s="16"/>
       <c r="G45" s="20"/>
     </row>
     <row r="46" spans="1:7">
@@ -4482,16 +4753,16 @@
         <v>224</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>779</v>
+        <v>349</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>778</v>
+        <v>468</v>
       </c>
       <c r="D46" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="F46" s="20"/>
       <c r="G46" s="20"/>
@@ -4501,16 +4772,16 @@
         <v>224</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>399</v>
+        <v>1029</v>
       </c>
       <c r="D47" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>860</v>
+        <v>1030</v>
       </c>
       <c r="F47" s="20"/>
       <c r="G47" s="20"/>
@@ -4520,16 +4791,16 @@
         <v>224</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>295</v>
+        <v>779</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>400</v>
+        <v>778</v>
       </c>
       <c r="D48" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="F48" s="20"/>
       <c r="G48" s="20"/>
@@ -4539,16 +4810,16 @@
         <v>224</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D49" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="F49" s="20"/>
       <c r="G49" s="20"/>
@@ -4558,16 +4829,16 @@
         <v>224</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D50" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="F50" s="20"/>
       <c r="G50" s="20"/>
@@ -4577,16 +4848,16 @@
         <v>224</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D51" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F51" s="20"/>
       <c r="G51" s="20"/>
@@ -4596,16 +4867,16 @@
         <v>224</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D52" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="F52" s="20"/>
       <c r="G52" s="20"/>
@@ -4615,16 +4886,16 @@
         <v>224</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>784</v>
+        <v>298</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>785</v>
+        <v>402</v>
       </c>
       <c r="D53" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="F53" s="20"/>
       <c r="G53" s="20"/>
@@ -4634,16 +4905,16 @@
         <v>224</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>406</v>
+        <v>299</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D54" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="F54" s="20"/>
       <c r="G54" s="20"/>
@@ -4653,16 +4924,16 @@
         <v>224</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D55" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="F55" s="20"/>
       <c r="G55" s="20"/>
@@ -4672,16 +4943,16 @@
         <v>224</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D56" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="F56" s="20"/>
       <c r="G56" s="20"/>
@@ -4691,16 +4962,16 @@
         <v>224</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>405</v>
+        <v>786</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>409</v>
+        <v>787</v>
       </c>
       <c r="D57" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="F57" s="20"/>
       <c r="G57" s="20"/>
@@ -4710,16 +4981,16 @@
         <v>224</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D58" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="F58" s="20"/>
       <c r="G58" s="20"/>
@@ -4729,16 +5000,16 @@
         <v>224</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>306</v>
+        <v>405</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>713</v>
+        <v>409</v>
       </c>
       <c r="D59" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="F59" s="20"/>
       <c r="G59" s="20"/>
@@ -4748,89 +5019,93 @@
         <v>224</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>716</v>
+        <v>404</v>
       </c>
       <c r="D60" s="18" t="s">
         <v>229</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="F60" s="20"/>
       <c r="G60" s="20"/>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="18" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>546</v>
+        <v>306</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>544</v>
+        <v>713</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>793</v>
-      </c>
-      <c r="F61" s="16"/>
-      <c r="G61" s="16"/>
+        <v>853</v>
+      </c>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="18" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>548</v>
+        <v>304</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>547</v>
+        <v>716</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>792</v>
-      </c>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16"/>
+        <v>854</v>
+      </c>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="18" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>549</v>
+        <v>1105</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>551</v>
+        <v>713</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="E63" s="18"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16"/>
+        <v>229</v>
+      </c>
+      <c r="E63" s="18" t="s">
+        <v>854</v>
+      </c>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>551</v>
+        <v>1053</v>
       </c>
       <c r="D64" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="E64" s="18"/>
+      <c r="E64" s="18" t="s">
+        <v>1052</v>
+      </c>
       <c r="F64" s="16"/>
       <c r="G64" s="16"/>
     </row>
@@ -4839,15 +5114,17 @@
         <v>212</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>796</v>
+        <v>549</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>798</v>
+        <v>551</v>
       </c>
       <c r="D65" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="E65" s="18"/>
+      <c r="E65" s="18" t="s">
+        <v>1050</v>
+      </c>
       <c r="F65" s="16"/>
       <c r="G65" s="16"/>
     </row>
@@ -4856,15 +5133,17 @@
         <v>212</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>797</v>
+        <v>550</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>798</v>
+        <v>551</v>
       </c>
       <c r="D66" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="E66" s="18"/>
+      <c r="E66" s="18" t="s">
+        <v>1051</v>
+      </c>
       <c r="F66" s="16"/>
       <c r="G66" s="16"/>
     </row>
@@ -4873,16 +5152,16 @@
         <v>212</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D67" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>828</v>
+        <v>1050</v>
       </c>
       <c r="F67" s="16"/>
       <c r="G67" s="16"/>
@@ -4892,16 +5171,16 @@
         <v>212</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>603</v>
+        <v>796</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>607</v>
+        <v>797</v>
       </c>
       <c r="D68" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>864</v>
+        <v>1051</v>
       </c>
       <c r="F68" s="16"/>
       <c r="G68" s="16"/>
@@ -4911,16 +5190,16 @@
         <v>212</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>604</v>
+        <v>793</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>606</v>
+        <v>794</v>
       </c>
       <c r="D69" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>827</v>
+        <v>1049</v>
       </c>
       <c r="F69" s="16"/>
       <c r="G69" s="16"/>
@@ -4930,16 +5209,16 @@
         <v>212</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>826</v>
+        <v>607</v>
       </c>
       <c r="D70" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>827</v>
+        <v>862</v>
       </c>
       <c r="F70" s="16"/>
       <c r="G70" s="16"/>
@@ -4949,16 +5228,16 @@
         <v>212</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>553</v>
+        <v>604</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>552</v>
+        <v>606</v>
       </c>
       <c r="D71" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>799</v>
+        <v>826</v>
       </c>
       <c r="F71" s="16"/>
       <c r="G71" s="16"/>
@@ -4968,16 +5247,16 @@
         <v>212</v>
       </c>
       <c r="B72" s="18" t="s">
-        <v>555</v>
+        <v>605</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>554</v>
+        <v>825</v>
       </c>
       <c r="D72" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>865</v>
+        <v>826</v>
       </c>
       <c r="F72" s="16"/>
       <c r="G72" s="16"/>
@@ -4987,16 +5266,16 @@
         <v>212</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>801</v>
+        <v>544</v>
       </c>
       <c r="D73" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="F73" s="16"/>
       <c r="G73" s="16"/>
@@ -5006,16 +5285,16 @@
         <v>212</v>
       </c>
       <c r="B74" s="18" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>800</v>
+        <v>552</v>
       </c>
       <c r="D74" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="F74" s="16"/>
       <c r="G74" s="16"/>
@@ -5025,16 +5304,16 @@
         <v>212</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>800</v>
+        <v>554</v>
       </c>
       <c r="D75" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>804</v>
+        <v>863</v>
       </c>
       <c r="F75" s="16"/>
       <c r="G75" s="16"/>
@@ -5044,7 +5323,7 @@
         <v>212</v>
       </c>
       <c r="B76" s="18" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C76" s="18" t="s">
         <v>800</v>
@@ -5053,7 +5332,7 @@
         <v>223</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F76" s="16"/>
       <c r="G76" s="16"/>
@@ -5063,16 +5342,16 @@
         <v>212</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D77" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="F77" s="16"/>
       <c r="G77" s="16"/>
@@ -5082,16 +5361,16 @@
         <v>212</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D78" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="F78" s="16"/>
       <c r="G78" s="16"/>
@@ -5101,16 +5380,16 @@
         <v>212</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D79" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="F79" s="16"/>
       <c r="G79" s="16"/>
@@ -5120,16 +5399,16 @@
         <v>212</v>
       </c>
       <c r="B80" s="18" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D80" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="F80" s="16"/>
       <c r="G80" s="16"/>
@@ -5139,16 +5418,16 @@
         <v>212</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D81" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="F81" s="16"/>
       <c r="G81" s="16"/>
@@ -5158,16 +5437,16 @@
         <v>212</v>
       </c>
       <c r="B82" s="18" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D82" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="F82" s="16"/>
       <c r="G82" s="16"/>
@@ -5177,16 +5456,16 @@
         <v>212</v>
       </c>
       <c r="B83" s="18" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D83" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="F83" s="16"/>
       <c r="G83" s="16"/>
@@ -5196,16 +5475,16 @@
         <v>212</v>
       </c>
       <c r="B84" s="18" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D84" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E84" s="18" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="F84" s="16"/>
       <c r="G84" s="16"/>
@@ -5215,16 +5494,16 @@
         <v>212</v>
       </c>
       <c r="B85" s="18" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D85" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E85" s="18" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="F85" s="16"/>
       <c r="G85" s="16"/>
@@ -5234,16 +5513,16 @@
         <v>212</v>
       </c>
       <c r="B86" s="18" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D86" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E86" s="18" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="F86" s="16"/>
       <c r="G86" s="16"/>
@@ -5253,16 +5532,16 @@
         <v>212</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D87" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E87" s="18" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="F87" s="16"/>
       <c r="G87" s="16"/>
@@ -5272,16 +5551,16 @@
         <v>212</v>
       </c>
       <c r="B88" s="18" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D88" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="F88" s="16"/>
       <c r="G88" s="16"/>
@@ -5291,16 +5570,16 @@
         <v>212</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D89" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E89" s="18" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="F89" s="16"/>
       <c r="G89" s="16"/>
@@ -5310,16 +5589,16 @@
         <v>212</v>
       </c>
       <c r="B90" s="18" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C90" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D90" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E90" s="18" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="F90" s="16"/>
       <c r="G90" s="16"/>
@@ -5329,16 +5608,16 @@
         <v>212</v>
       </c>
       <c r="B91" s="18" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C91" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D91" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E91" s="18" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="F91" s="16"/>
       <c r="G91" s="16"/>
@@ -5348,16 +5627,16 @@
         <v>212</v>
       </c>
       <c r="B92" s="18" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C92" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D92" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E92" s="18" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="F92" s="16"/>
       <c r="G92" s="16"/>
@@ -5367,16 +5646,16 @@
         <v>212</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C93" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D93" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E93" s="18" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="F93" s="16"/>
       <c r="G93" s="16"/>
@@ -5386,16 +5665,16 @@
         <v>212</v>
       </c>
       <c r="B94" s="18" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C94" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D94" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E94" s="18" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="F94" s="16"/>
       <c r="G94" s="16"/>
@@ -5405,16 +5684,16 @@
         <v>212</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C95" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D95" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E95" s="18" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="F95" s="16"/>
       <c r="G95" s="16"/>
@@ -5424,16 +5703,16 @@
         <v>212</v>
       </c>
       <c r="B96" s="18" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C96" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D96" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E96" s="18" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="F96" s="16"/>
       <c r="G96" s="16"/>
@@ -5443,16 +5722,16 @@
         <v>212</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C97" s="18" t="s">
-        <v>602</v>
+        <v>799</v>
       </c>
       <c r="D97" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E97" s="18" t="s">
-        <v>863</v>
+        <v>822</v>
       </c>
       <c r="F97" s="16"/>
       <c r="G97" s="16"/>
@@ -5462,16 +5741,16 @@
         <v>212</v>
       </c>
       <c r="B98" s="18" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C98" s="18" t="s">
-        <v>866</v>
+        <v>799</v>
       </c>
       <c r="D98" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E98" s="18" t="s">
-        <v>901</v>
+        <v>823</v>
       </c>
       <c r="F98" s="16"/>
       <c r="G98" s="16"/>
@@ -5481,16 +5760,16 @@
         <v>212</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>541</v>
+        <v>580</v>
       </c>
       <c r="C99" s="18" t="s">
-        <v>765</v>
+        <v>799</v>
       </c>
       <c r="D99" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E99" s="18" t="s">
-        <v>1014</v>
+        <v>824</v>
       </c>
       <c r="F99" s="16"/>
       <c r="G99" s="16"/>
@@ -5500,16 +5779,16 @@
         <v>212</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>543</v>
+        <v>582</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>758</v>
+        <v>864</v>
       </c>
       <c r="D100" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E100" s="18" t="s">
-        <v>1013</v>
+        <v>899</v>
       </c>
       <c r="F100" s="16"/>
       <c r="G100" s="16"/>
@@ -5519,16 +5798,16 @@
         <v>212</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>583</v>
+        <v>615</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>760</v>
+        <v>894</v>
       </c>
       <c r="D101" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E101" s="18" t="s">
-        <v>788</v>
+        <v>895</v>
       </c>
       <c r="F101" s="16"/>
       <c r="G101" s="16"/>
@@ -5538,16 +5817,16 @@
         <v>212</v>
       </c>
       <c r="B102" s="18" t="s">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="C102" s="18" t="s">
-        <v>760</v>
+        <v>600</v>
       </c>
       <c r="D102" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E102" s="18" t="s">
-        <v>788</v>
+        <v>860</v>
       </c>
       <c r="F102" s="16"/>
       <c r="G102" s="16"/>
@@ -5557,16 +5836,16 @@
         <v>212</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>867</v>
+        <v>541</v>
       </c>
       <c r="C103" s="18" t="s">
-        <v>869</v>
+        <v>765</v>
       </c>
       <c r="D103" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E103" s="18" t="s">
-        <v>870</v>
+        <v>1012</v>
       </c>
       <c r="F103" s="16"/>
       <c r="G103" s="16"/>
@@ -5576,16 +5855,16 @@
         <v>212</v>
       </c>
       <c r="B104" s="18" t="s">
-        <v>868</v>
+        <v>581</v>
       </c>
       <c r="C104" s="18" t="s">
-        <v>869</v>
+        <v>602</v>
       </c>
       <c r="D104" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E104" s="18" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="F104" s="16"/>
       <c r="G104" s="16"/>
@@ -5595,16 +5874,16 @@
         <v>212</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>871</v>
+        <v>599</v>
       </c>
       <c r="C105" s="18" t="s">
-        <v>873</v>
+        <v>598</v>
       </c>
       <c r="D105" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E105" s="18" t="s">
-        <v>874</v>
+        <v>859</v>
       </c>
       <c r="F105" s="16"/>
       <c r="G105" s="16"/>
@@ -5614,16 +5893,16 @@
         <v>212</v>
       </c>
       <c r="B106" s="18" t="s">
-        <v>872</v>
+        <v>633</v>
       </c>
       <c r="C106" s="18" t="s">
-        <v>873</v>
+        <v>1014</v>
       </c>
       <c r="D106" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E106" s="18" t="s">
-        <v>874</v>
+        <v>1015</v>
       </c>
       <c r="F106" s="16"/>
       <c r="G106" s="16"/>
@@ -5633,16 +5912,16 @@
         <v>212</v>
       </c>
       <c r="B107" s="18" t="s">
-        <v>589</v>
+        <v>635</v>
       </c>
       <c r="C107" s="18" t="s">
-        <v>761</v>
+        <v>1014</v>
       </c>
       <c r="D107" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E107" s="18" t="s">
-        <v>789</v>
+        <v>1015</v>
       </c>
       <c r="F107" s="16"/>
       <c r="G107" s="16"/>
@@ -5652,16 +5931,16 @@
         <v>212</v>
       </c>
       <c r="B108" s="18" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="C108" s="18" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D108" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E108" s="18" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="F108" s="16"/>
       <c r="G108" s="16"/>
@@ -5671,16 +5950,16 @@
         <v>212</v>
       </c>
       <c r="B109" s="18" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="C109" s="18" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="D109" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E109" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="F109" s="16"/>
       <c r="G109" s="16"/>
@@ -5690,16 +5969,16 @@
         <v>212</v>
       </c>
       <c r="B110" s="18" t="s">
-        <v>594</v>
+        <v>865</v>
       </c>
       <c r="C110" s="18" t="s">
-        <v>763</v>
+        <v>867</v>
       </c>
       <c r="D110" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E110" s="18" t="s">
-        <v>790</v>
+        <v>868</v>
       </c>
       <c r="F110" s="16"/>
       <c r="G110" s="16"/>
@@ -5709,16 +5988,16 @@
         <v>212</v>
       </c>
       <c r="B111" s="18" t="s">
-        <v>597</v>
+        <v>866</v>
       </c>
       <c r="C111" s="18" t="s">
-        <v>764</v>
+        <v>867</v>
       </c>
       <c r="D111" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E111" s="18" t="s">
-        <v>791</v>
+        <v>868</v>
       </c>
       <c r="F111" s="16"/>
       <c r="G111" s="16"/>
@@ -5728,16 +6007,16 @@
         <v>212</v>
       </c>
       <c r="B112" s="18" t="s">
-        <v>596</v>
+        <v>1046</v>
       </c>
       <c r="C112" s="18" t="s">
-        <v>764</v>
+        <v>871</v>
       </c>
       <c r="D112" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E112" s="18" t="s">
-        <v>791</v>
+        <v>872</v>
       </c>
       <c r="F112" s="16"/>
       <c r="G112" s="16"/>
@@ -5747,16 +6026,16 @@
         <v>212</v>
       </c>
       <c r="B113" s="18" t="s">
-        <v>599</v>
+        <v>1047</v>
       </c>
       <c r="C113" s="18" t="s">
-        <v>598</v>
+        <v>871</v>
       </c>
       <c r="D113" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E113" s="18" t="s">
-        <v>861</v>
+        <v>872</v>
       </c>
       <c r="F113" s="16"/>
       <c r="G113" s="16"/>
@@ -5766,16 +6045,16 @@
         <v>212</v>
       </c>
       <c r="B114" s="18" t="s">
-        <v>601</v>
+        <v>869</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>600</v>
+        <v>1048</v>
       </c>
       <c r="D114" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E114" s="18" t="s">
-        <v>862</v>
+        <v>1045</v>
       </c>
       <c r="F114" s="16"/>
       <c r="G114" s="16"/>
@@ -5785,16 +6064,16 @@
         <v>212</v>
       </c>
       <c r="B115" s="18" t="s">
-        <v>584</v>
+        <v>870</v>
       </c>
       <c r="C115" s="18" t="s">
-        <v>875</v>
+        <v>1048</v>
       </c>
       <c r="D115" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E115" s="18" t="s">
-        <v>877</v>
+        <v>1045</v>
       </c>
       <c r="F115" s="16"/>
       <c r="G115" s="16"/>
@@ -5804,16 +6083,16 @@
         <v>212</v>
       </c>
       <c r="B116" s="18" t="s">
-        <v>876</v>
+        <v>594</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>875</v>
+        <v>763</v>
       </c>
       <c r="D116" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E116" s="18" t="s">
-        <v>877</v>
+        <v>790</v>
       </c>
       <c r="F116" s="16"/>
       <c r="G116" s="16"/>
@@ -5823,16 +6102,16 @@
         <v>212</v>
       </c>
       <c r="B117" s="18" t="s">
-        <v>652</v>
+        <v>593</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>653</v>
+        <v>763</v>
       </c>
       <c r="D117" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E117" s="18" t="s">
-        <v>878</v>
+        <v>790</v>
       </c>
       <c r="F117" s="16"/>
       <c r="G117" s="16"/>
@@ -5842,16 +6121,16 @@
         <v>212</v>
       </c>
       <c r="B118" s="18" t="s">
-        <v>609</v>
+        <v>543</v>
       </c>
       <c r="C118" s="18" t="s">
-        <v>880</v>
+        <v>758</v>
       </c>
       <c r="D118" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E118" s="18" t="s">
-        <v>889</v>
+        <v>1011</v>
       </c>
       <c r="F118" s="16"/>
       <c r="G118" s="16"/>
@@ -5861,16 +6140,16 @@
         <v>212</v>
       </c>
       <c r="B119" s="18" t="s">
-        <v>611</v>
+        <v>597</v>
       </c>
       <c r="C119" s="18" t="s">
-        <v>879</v>
+        <v>764</v>
       </c>
       <c r="D119" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E119" s="18" t="s">
-        <v>890</v>
+        <v>791</v>
       </c>
       <c r="F119" s="16"/>
       <c r="G119" s="16"/>
@@ -5880,16 +6159,16 @@
         <v>212</v>
       </c>
       <c r="B120" s="18" t="s">
-        <v>881</v>
+        <v>596</v>
       </c>
       <c r="C120" s="18" t="s">
-        <v>882</v>
+        <v>764</v>
       </c>
       <c r="D120" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E120" s="18" t="s">
-        <v>891</v>
+        <v>791</v>
       </c>
       <c r="F120" s="16"/>
       <c r="G120" s="16"/>
@@ -5899,16 +6178,16 @@
         <v>212</v>
       </c>
       <c r="B121" s="18" t="s">
-        <v>883</v>
+        <v>1043</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>884</v>
+        <v>762</v>
       </c>
       <c r="D121" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E121" s="18" t="s">
-        <v>892</v>
+        <v>789</v>
       </c>
       <c r="F121" s="16"/>
       <c r="G121" s="16"/>
@@ -5918,16 +6197,16 @@
         <v>212</v>
       </c>
       <c r="B122" s="18" t="s">
-        <v>885</v>
+        <v>590</v>
       </c>
       <c r="C122" s="18" t="s">
-        <v>886</v>
+        <v>762</v>
       </c>
       <c r="D122" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E122" s="18" t="s">
-        <v>893</v>
+        <v>789</v>
       </c>
       <c r="F122" s="16"/>
       <c r="G122" s="16"/>
@@ -5937,16 +6216,16 @@
         <v>212</v>
       </c>
       <c r="B123" s="18" t="s">
-        <v>613</v>
+        <v>1044</v>
       </c>
       <c r="C123" s="18" t="s">
-        <v>887</v>
+        <v>761</v>
       </c>
       <c r="D123" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E123" s="18" t="s">
-        <v>894</v>
+        <v>1028</v>
       </c>
       <c r="F123" s="16"/>
       <c r="G123" s="16"/>
@@ -5956,16 +6235,16 @@
         <v>212</v>
       </c>
       <c r="B124" s="18" t="s">
-        <v>614</v>
+        <v>589</v>
       </c>
       <c r="C124" s="18" t="s">
-        <v>888</v>
+        <v>761</v>
       </c>
       <c r="D124" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E124" s="18" t="s">
-        <v>895</v>
+        <v>1028</v>
       </c>
       <c r="F124" s="16"/>
       <c r="G124" s="16"/>
@@ -5975,16 +6254,16 @@
         <v>212</v>
       </c>
       <c r="B125" s="18" t="s">
-        <v>615</v>
+        <v>1103</v>
       </c>
       <c r="C125" s="18" t="s">
-        <v>896</v>
+        <v>1102</v>
       </c>
       <c r="D125" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E125" s="18" t="s">
-        <v>897</v>
+        <v>1104</v>
       </c>
       <c r="F125" s="16"/>
       <c r="G125" s="16"/>
@@ -5994,16 +6273,16 @@
         <v>212</v>
       </c>
       <c r="B126" s="18" t="s">
-        <v>618</v>
+        <v>1101</v>
       </c>
       <c r="C126" s="18" t="s">
-        <v>617</v>
+        <v>1102</v>
       </c>
       <c r="D126" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E126" s="18" t="s">
-        <v>900</v>
+        <v>1104</v>
       </c>
       <c r="F126" s="16"/>
       <c r="G126" s="16"/>
@@ -6013,16 +6292,16 @@
         <v>212</v>
       </c>
       <c r="B127" s="18" t="s">
-        <v>686</v>
+        <v>584</v>
       </c>
       <c r="C127" s="18" t="s">
-        <v>687</v>
+        <v>873</v>
       </c>
       <c r="D127" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E127" s="18" t="s">
-        <v>899</v>
+        <v>875</v>
       </c>
       <c r="F127" s="16"/>
       <c r="G127" s="16"/>
@@ -6032,16 +6311,16 @@
         <v>212</v>
       </c>
       <c r="B128" s="18" t="s">
-        <v>619</v>
+        <v>874</v>
       </c>
       <c r="C128" s="18" t="s">
-        <v>898</v>
+        <v>873</v>
       </c>
       <c r="D128" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E128" s="18" t="s">
-        <v>902</v>
+        <v>875</v>
       </c>
       <c r="F128" s="16"/>
       <c r="G128" s="16"/>
@@ -6051,16 +6330,16 @@
         <v>212</v>
       </c>
       <c r="B129" s="18" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C129" s="18" t="s">
-        <v>751</v>
+        <v>653</v>
       </c>
       <c r="D129" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E129" s="18" t="s">
-        <v>767</v>
+        <v>876</v>
       </c>
       <c r="F129" s="16"/>
       <c r="G129" s="16"/>
@@ -6070,16 +6349,16 @@
         <v>212</v>
       </c>
       <c r="B130" s="18" t="s">
-        <v>659</v>
+        <v>609</v>
       </c>
       <c r="C130" s="18" t="s">
-        <v>752</v>
+        <v>878</v>
       </c>
       <c r="D130" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E130" s="18" t="s">
-        <v>768</v>
+        <v>887</v>
       </c>
       <c r="F130" s="16"/>
       <c r="G130" s="16"/>
@@ -6089,16 +6368,16 @@
         <v>212</v>
       </c>
       <c r="B131" s="18" t="s">
-        <v>661</v>
+        <v>611</v>
       </c>
       <c r="C131" s="18" t="s">
-        <v>750</v>
+        <v>877</v>
       </c>
       <c r="D131" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E131" s="18" t="s">
-        <v>769</v>
+        <v>888</v>
       </c>
       <c r="F131" s="16"/>
       <c r="G131" s="16"/>
@@ -6108,16 +6387,16 @@
         <v>212</v>
       </c>
       <c r="B132" s="18" t="s">
-        <v>688</v>
+        <v>879</v>
       </c>
       <c r="C132" s="18" t="s">
-        <v>689</v>
+        <v>880</v>
       </c>
       <c r="D132" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E132" s="18" t="s">
-        <v>909</v>
+        <v>889</v>
       </c>
       <c r="F132" s="16"/>
       <c r="G132" s="16"/>
@@ -6127,16 +6406,16 @@
         <v>212</v>
       </c>
       <c r="B133" s="18" t="s">
-        <v>690</v>
+        <v>881</v>
       </c>
       <c r="C133" s="18" t="s">
-        <v>908</v>
+        <v>882</v>
       </c>
       <c r="D133" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E133" s="18" t="s">
-        <v>910</v>
+        <v>890</v>
       </c>
       <c r="F133" s="16"/>
       <c r="G133" s="16"/>
@@ -6146,16 +6425,16 @@
         <v>212</v>
       </c>
       <c r="B134" s="18" t="s">
-        <v>692</v>
+        <v>883</v>
       </c>
       <c r="C134" s="18" t="s">
-        <v>693</v>
+        <v>884</v>
       </c>
       <c r="D134" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E134" s="18" t="s">
-        <v>911</v>
+        <v>891</v>
       </c>
       <c r="F134" s="16"/>
       <c r="G134" s="16"/>
@@ -6165,16 +6444,16 @@
         <v>212</v>
       </c>
       <c r="B135" s="18" t="s">
-        <v>694</v>
+        <v>613</v>
       </c>
       <c r="C135" s="18" t="s">
-        <v>737</v>
+        <v>885</v>
       </c>
       <c r="D135" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E135" s="18" t="s">
-        <v>903</v>
+        <v>892</v>
       </c>
       <c r="F135" s="16"/>
       <c r="G135" s="16"/>
@@ -6184,16 +6463,16 @@
         <v>212</v>
       </c>
       <c r="B136" s="18" t="s">
-        <v>696</v>
+        <v>614</v>
       </c>
       <c r="C136" s="18" t="s">
-        <v>738</v>
+        <v>886</v>
       </c>
       <c r="D136" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E136" s="18" t="s">
-        <v>912</v>
+        <v>893</v>
       </c>
       <c r="F136" s="16"/>
       <c r="G136" s="16"/>
@@ -6203,16 +6482,16 @@
         <v>212</v>
       </c>
       <c r="B137" s="18" t="s">
-        <v>698</v>
+        <v>618</v>
       </c>
       <c r="C137" s="18" t="s">
-        <v>699</v>
+        <v>617</v>
       </c>
       <c r="D137" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E137" s="18" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="F137" s="16"/>
       <c r="G137" s="16"/>
@@ -6222,16 +6501,16 @@
         <v>212</v>
       </c>
       <c r="B138" s="18" t="s">
-        <v>702</v>
+        <v>686</v>
       </c>
       <c r="C138" s="18" t="s">
-        <v>906</v>
+        <v>687</v>
       </c>
       <c r="D138" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E138" s="18" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
       <c r="F138" s="16"/>
       <c r="G138" s="16"/>
@@ -6241,16 +6520,16 @@
         <v>212</v>
       </c>
       <c r="B139" s="18" t="s">
-        <v>905</v>
+        <v>619</v>
       </c>
       <c r="C139" s="18" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
       <c r="D139" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E139" s="18" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="F139" s="16"/>
       <c r="G139" s="16"/>
@@ -6260,16 +6539,16 @@
         <v>212</v>
       </c>
       <c r="B140" s="18" t="s">
-        <v>914</v>
+        <v>1054</v>
       </c>
       <c r="C140" s="18" t="s">
-        <v>915</v>
+        <v>1055</v>
       </c>
       <c r="D140" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E140" s="18" t="s">
-        <v>917</v>
+        <v>1076</v>
       </c>
       <c r="F140" s="16"/>
       <c r="G140" s="16"/>
@@ -6279,16 +6558,16 @@
         <v>212</v>
       </c>
       <c r="B141" s="18" t="s">
-        <v>916</v>
+        <v>1057</v>
       </c>
       <c r="C141" s="18" t="s">
-        <v>915</v>
+        <v>1056</v>
       </c>
       <c r="D141" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E141" s="18" t="s">
-        <v>917</v>
+        <v>1086</v>
       </c>
       <c r="F141" s="16"/>
       <c r="G141" s="16"/>
@@ -6298,16 +6577,16 @@
         <v>212</v>
       </c>
       <c r="B142" s="18" t="s">
-        <v>700</v>
+        <v>1058</v>
       </c>
       <c r="C142" s="18" t="s">
-        <v>904</v>
+        <v>1059</v>
       </c>
       <c r="D142" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E142" s="18" t="s">
-        <v>922</v>
+        <v>1077</v>
       </c>
       <c r="F142" s="16"/>
       <c r="G142" s="16"/>
@@ -6317,16 +6596,16 @@
         <v>212</v>
       </c>
       <c r="B143" s="18" t="s">
-        <v>918</v>
+        <v>1060</v>
       </c>
       <c r="C143" s="18" t="s">
-        <v>919</v>
+        <v>1061</v>
       </c>
       <c r="D143" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E143" s="18" t="s">
-        <v>922</v>
+        <v>1078</v>
       </c>
       <c r="F143" s="16"/>
       <c r="G143" s="16"/>
@@ -6336,33 +6615,35 @@
         <v>212</v>
       </c>
       <c r="B144" s="18" t="s">
-        <v>920</v>
+        <v>1063</v>
       </c>
       <c r="C144" s="18" t="s">
-        <v>921</v>
+        <v>1062</v>
       </c>
       <c r="D144" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E144" s="18" t="s">
-        <v>922</v>
-      </c>
+        <v>1079</v>
+      </c>
+      <c r="F144" s="16"/>
+      <c r="G144" s="16"/>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B145" s="18" t="s">
-        <v>723</v>
+        <v>1065</v>
       </c>
       <c r="C145" s="18" t="s">
-        <v>729</v>
+        <v>1064</v>
       </c>
       <c r="D145" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E145" s="18" t="s">
-        <v>747</v>
+        <v>1080</v>
       </c>
       <c r="F145" s="16"/>
       <c r="G145" s="16"/>
@@ -6372,16 +6653,16 @@
         <v>212</v>
       </c>
       <c r="B146" s="18" t="s">
-        <v>724</v>
+        <v>1067</v>
       </c>
       <c r="C146" s="18" t="s">
-        <v>730</v>
+        <v>1066</v>
       </c>
       <c r="D146" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E146" s="18" t="s">
-        <v>748</v>
+        <v>1081</v>
       </c>
       <c r="F146" s="16"/>
       <c r="G146" s="16"/>
@@ -6391,16 +6672,16 @@
         <v>212</v>
       </c>
       <c r="B147" s="18" t="s">
-        <v>725</v>
+        <v>1069</v>
       </c>
       <c r="C147" s="18" t="s">
-        <v>731</v>
+        <v>1068</v>
       </c>
       <c r="D147" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E147" s="18" t="s">
-        <v>749</v>
+        <v>1082</v>
       </c>
       <c r="F147" s="16"/>
       <c r="G147" s="16"/>
@@ -6410,62 +6691,54 @@
         <v>212</v>
       </c>
       <c r="B148" s="18" t="s">
-        <v>735</v>
+        <v>1071</v>
       </c>
       <c r="C148" s="18" t="s">
-        <v>736</v>
+        <v>1070</v>
       </c>
       <c r="D148" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E148" s="18" t="s">
-        <v>927</v>
-      </c>
-      <c r="F148" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G148" s="16" t="s">
-        <v>743</v>
-      </c>
+        <v>1083</v>
+      </c>
+      <c r="F148" s="16"/>
+      <c r="G148" s="16"/>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B149" s="18" t="s">
-        <v>746</v>
+        <v>1073</v>
       </c>
       <c r="C149" s="18" t="s">
-        <v>736</v>
+        <v>1072</v>
       </c>
       <c r="D149" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E149" s="18" t="s">
-        <v>927</v>
-      </c>
-      <c r="F149" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G149" s="16" t="s">
-        <v>743</v>
-      </c>
+        <v>1084</v>
+      </c>
+      <c r="F149" s="16"/>
+      <c r="G149" s="16"/>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B150" s="18" t="s">
-        <v>923</v>
+        <v>1075</v>
       </c>
       <c r="C150" s="18" t="s">
-        <v>924</v>
+        <v>1074</v>
       </c>
       <c r="D150" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E150" s="18" t="s">
-        <v>928</v>
+        <v>1085</v>
       </c>
       <c r="F150" s="16"/>
       <c r="G150" s="16"/>
@@ -6475,16 +6748,16 @@
         <v>212</v>
       </c>
       <c r="B151" s="18" t="s">
-        <v>925</v>
+        <v>659</v>
       </c>
       <c r="C151" s="18" t="s">
-        <v>924</v>
+        <v>752</v>
       </c>
       <c r="D151" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E151" s="18" t="s">
-        <v>928</v>
+        <v>768</v>
       </c>
       <c r="F151" s="16"/>
       <c r="G151" s="16"/>
@@ -6494,16 +6767,16 @@
         <v>212</v>
       </c>
       <c r="B152" s="18" t="s">
-        <v>926</v>
+        <v>661</v>
       </c>
       <c r="C152" s="18" t="s">
-        <v>924</v>
+        <v>750</v>
       </c>
       <c r="D152" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E152" s="18" t="s">
-        <v>928</v>
+        <v>769</v>
       </c>
       <c r="F152" s="16"/>
       <c r="G152" s="16"/>
@@ -6513,16 +6786,16 @@
         <v>212</v>
       </c>
       <c r="B153" s="18" t="s">
-        <v>930</v>
+        <v>658</v>
       </c>
       <c r="C153" s="18" t="s">
-        <v>929</v>
+        <v>751</v>
       </c>
       <c r="D153" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E153" s="18" t="s">
-        <v>931</v>
+        <v>767</v>
       </c>
       <c r="F153" s="16"/>
       <c r="G153" s="16"/>
@@ -6532,16 +6805,16 @@
         <v>212</v>
       </c>
       <c r="B154" s="18" t="s">
-        <v>933</v>
+        <v>688</v>
       </c>
       <c r="C154" s="18" t="s">
-        <v>932</v>
+        <v>689</v>
       </c>
       <c r="D154" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E154" s="18" t="s">
-        <v>936</v>
+        <v>907</v>
       </c>
       <c r="F154" s="16"/>
       <c r="G154" s="16"/>
@@ -6551,16 +6824,16 @@
         <v>212</v>
       </c>
       <c r="B155" s="18" t="s">
-        <v>935</v>
+        <v>690</v>
       </c>
       <c r="C155" s="18" t="s">
-        <v>934</v>
+        <v>906</v>
       </c>
       <c r="D155" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E155" s="18" t="s">
-        <v>939</v>
+        <v>908</v>
       </c>
       <c r="F155" s="16"/>
       <c r="G155" s="16"/>
@@ -6570,16 +6843,16 @@
         <v>212</v>
       </c>
       <c r="B156" s="18" t="s">
-        <v>938</v>
+        <v>692</v>
       </c>
       <c r="C156" s="18" t="s">
-        <v>937</v>
+        <v>693</v>
       </c>
       <c r="D156" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E156" s="18" t="s">
-        <v>940</v>
+        <v>909</v>
       </c>
       <c r="F156" s="16"/>
       <c r="G156" s="16"/>
@@ -6589,16 +6862,16 @@
         <v>212</v>
       </c>
       <c r="B157" s="18" t="s">
-        <v>941</v>
+        <v>694</v>
       </c>
       <c r="C157" s="18" t="s">
-        <v>943</v>
+        <v>737</v>
       </c>
       <c r="D157" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E157" s="18" t="s">
-        <v>940</v>
+        <v>901</v>
       </c>
       <c r="F157" s="16"/>
       <c r="G157" s="16"/>
@@ -6608,16 +6881,16 @@
         <v>212</v>
       </c>
       <c r="B158" s="18" t="s">
-        <v>942</v>
+        <v>696</v>
       </c>
       <c r="C158" s="18" t="s">
-        <v>944</v>
+        <v>738</v>
       </c>
       <c r="D158" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E158" s="18" t="s">
-        <v>940</v>
+        <v>910</v>
       </c>
       <c r="F158" s="16"/>
       <c r="G158" s="16"/>
@@ -6627,16 +6900,16 @@
         <v>212</v>
       </c>
       <c r="B159" s="18" t="s">
-        <v>945</v>
+        <v>698</v>
       </c>
       <c r="C159" s="18" t="s">
-        <v>946</v>
+        <v>699</v>
       </c>
       <c r="D159" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E159" s="18" t="s">
-        <v>947</v>
+        <v>911</v>
       </c>
       <c r="F159" s="16"/>
       <c r="G159" s="16"/>
@@ -6646,16 +6919,16 @@
         <v>212</v>
       </c>
       <c r="B160" s="18" t="s">
-        <v>948</v>
+        <v>700</v>
       </c>
       <c r="C160" s="18" t="s">
-        <v>950</v>
+        <v>902</v>
       </c>
       <c r="D160" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E160" s="18" t="s">
-        <v>951</v>
+        <v>920</v>
       </c>
       <c r="F160" s="16"/>
       <c r="G160" s="16"/>
@@ -6665,16 +6938,16 @@
         <v>212</v>
       </c>
       <c r="B161" s="18" t="s">
-        <v>949</v>
+        <v>916</v>
       </c>
       <c r="C161" s="18" t="s">
-        <v>950</v>
+        <v>917</v>
       </c>
       <c r="D161" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E161" s="18" t="s">
-        <v>951</v>
+        <v>920</v>
       </c>
       <c r="F161" s="16"/>
       <c r="G161" s="16"/>
@@ -6684,35 +6957,33 @@
         <v>212</v>
       </c>
       <c r="B162" s="18" t="s">
-        <v>953</v>
+        <v>918</v>
       </c>
       <c r="C162" s="18" t="s">
-        <v>952</v>
+        <v>919</v>
       </c>
       <c r="D162" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E162" s="18" t="s">
-        <v>955</v>
-      </c>
-      <c r="F162" s="16"/>
-      <c r="G162" s="16"/>
+        <v>920</v>
+      </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B163" s="18" t="s">
-        <v>954</v>
+        <v>702</v>
       </c>
       <c r="C163" s="18" t="s">
-        <v>952</v>
+        <v>904</v>
       </c>
       <c r="D163" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E163" s="18" t="s">
-        <v>955</v>
+        <v>905</v>
       </c>
       <c r="F163" s="16"/>
       <c r="G163" s="16"/>
@@ -6722,16 +6993,16 @@
         <v>212</v>
       </c>
       <c r="B164" s="18" t="s">
-        <v>956</v>
+        <v>903</v>
       </c>
       <c r="C164" s="18" t="s">
-        <v>957</v>
+        <v>904</v>
       </c>
       <c r="D164" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E164" s="18" t="s">
-        <v>970</v>
+        <v>905</v>
       </c>
       <c r="F164" s="16"/>
       <c r="G164" s="16"/>
@@ -6741,16 +7012,16 @@
         <v>212</v>
       </c>
       <c r="B165" s="18" t="s">
-        <v>958</v>
+        <v>912</v>
       </c>
       <c r="C165" s="18" t="s">
-        <v>961</v>
+        <v>913</v>
       </c>
       <c r="D165" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E165" s="18" t="s">
-        <v>971</v>
+        <v>915</v>
       </c>
       <c r="F165" s="16"/>
       <c r="G165" s="16"/>
@@ -6760,16 +7031,16 @@
         <v>212</v>
       </c>
       <c r="B166" s="18" t="s">
-        <v>959</v>
+        <v>914</v>
       </c>
       <c r="C166" s="18" t="s">
-        <v>962</v>
+        <v>913</v>
       </c>
       <c r="D166" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E166" s="18" t="s">
-        <v>972</v>
+        <v>915</v>
       </c>
       <c r="F166" s="16"/>
       <c r="G166" s="16"/>
@@ -6779,16 +7050,16 @@
         <v>212</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>960</v>
+        <v>723</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>963</v>
+        <v>729</v>
       </c>
       <c r="D167" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E167" s="18" t="s">
-        <v>973</v>
+        <v>747</v>
       </c>
       <c r="F167" s="16"/>
       <c r="G167" s="16"/>
@@ -6798,16 +7069,16 @@
         <v>212</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>965</v>
+        <v>724</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>964</v>
+        <v>730</v>
       </c>
       <c r="D168" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E168" s="18" t="s">
-        <v>998</v>
+        <v>748</v>
       </c>
       <c r="F168" s="16"/>
       <c r="G168" s="16"/>
@@ -6817,16 +7088,16 @@
         <v>212</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>967</v>
+        <v>725</v>
       </c>
       <c r="C169" s="18" t="s">
-        <v>966</v>
+        <v>731</v>
       </c>
       <c r="D169" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E169" s="18" t="s">
-        <v>974</v>
+        <v>749</v>
       </c>
       <c r="F169" s="16"/>
       <c r="G169" s="16"/>
@@ -6836,54 +7107,62 @@
         <v>212</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>968</v>
+        <v>735</v>
       </c>
       <c r="C170" s="18" t="s">
-        <v>969</v>
+        <v>736</v>
       </c>
       <c r="D170" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E170" s="18" t="s">
-        <v>975</v>
-      </c>
-      <c r="F170" s="16"/>
-      <c r="G170" s="16"/>
+        <v>925</v>
+      </c>
+      <c r="F170" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G170" s="16" t="s">
+        <v>743</v>
+      </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>976</v>
+        <v>746</v>
       </c>
       <c r="C171" s="18" t="s">
-        <v>977</v>
+        <v>736</v>
       </c>
       <c r="D171" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E171" s="18" t="s">
-        <v>999</v>
-      </c>
-      <c r="F171" s="16"/>
-      <c r="G171" s="16"/>
+        <v>925</v>
+      </c>
+      <c r="F171" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G171" s="16" t="s">
+        <v>743</v>
+      </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B172" s="18" t="s">
-        <v>979</v>
+        <v>921</v>
       </c>
       <c r="C172" s="18" t="s">
-        <v>978</v>
+        <v>922</v>
       </c>
       <c r="D172" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E172" s="18" t="s">
-        <v>980</v>
+        <v>926</v>
       </c>
       <c r="F172" s="16"/>
       <c r="G172" s="16"/>
@@ -6893,16 +7172,16 @@
         <v>212</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>981</v>
+        <v>923</v>
       </c>
       <c r="C173" s="18" t="s">
-        <v>982</v>
+        <v>922</v>
       </c>
       <c r="D173" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E173" s="18" t="s">
-        <v>983</v>
+        <v>926</v>
       </c>
       <c r="F173" s="16"/>
       <c r="G173" s="16"/>
@@ -6912,16 +7191,16 @@
         <v>212</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>987</v>
+        <v>924</v>
       </c>
       <c r="C174" s="18" t="s">
-        <v>988</v>
+        <v>922</v>
       </c>
       <c r="D174" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E174" s="18" t="s">
-        <v>1000</v>
+        <v>926</v>
       </c>
       <c r="F174" s="16"/>
       <c r="G174" s="16"/>
@@ -6931,16 +7210,16 @@
         <v>212</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>989</v>
+        <v>928</v>
       </c>
       <c r="C175" s="18" t="s">
-        <v>990</v>
+        <v>927</v>
       </c>
       <c r="D175" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E175" s="18" t="s">
-        <v>991</v>
+        <v>929</v>
       </c>
       <c r="F175" s="16"/>
       <c r="G175" s="16"/>
@@ -6950,16 +7229,16 @@
         <v>212</v>
       </c>
       <c r="B176" s="18" t="s">
-        <v>984</v>
+        <v>931</v>
       </c>
       <c r="C176" s="18" t="s">
-        <v>992</v>
+        <v>930</v>
       </c>
       <c r="D176" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E176" s="18" t="s">
-        <v>1010</v>
+        <v>934</v>
       </c>
       <c r="F176" s="16"/>
       <c r="G176" s="16"/>
@@ -6969,16 +7248,16 @@
         <v>212</v>
       </c>
       <c r="B177" s="18" t="s">
-        <v>993</v>
+        <v>933</v>
       </c>
       <c r="C177" s="18" t="s">
-        <v>994</v>
+        <v>932</v>
       </c>
       <c r="D177" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E177" s="18" t="s">
-        <v>1001</v>
+        <v>937</v>
       </c>
       <c r="F177" s="16"/>
       <c r="G177" s="16"/>
@@ -6988,16 +7267,16 @@
         <v>212</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>995</v>
+        <v>936</v>
       </c>
       <c r="C178" s="18" t="s">
-        <v>996</v>
+        <v>935</v>
       </c>
       <c r="D178" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E178" s="18" t="s">
-        <v>997</v>
+        <v>938</v>
       </c>
       <c r="F178" s="16"/>
       <c r="G178" s="16"/>
@@ -7007,16 +7286,16 @@
         <v>212</v>
       </c>
       <c r="B179" s="18" t="s">
-        <v>985</v>
+        <v>939</v>
       </c>
       <c r="C179" s="18" t="s">
-        <v>1002</v>
+        <v>941</v>
       </c>
       <c r="D179" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E179" s="18" t="s">
-        <v>1011</v>
+        <v>938</v>
       </c>
       <c r="F179" s="16"/>
       <c r="G179" s="16"/>
@@ -7026,16 +7305,16 @@
         <v>212</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>1005</v>
+        <v>940</v>
       </c>
       <c r="C180" s="18" t="s">
-        <v>1003</v>
+        <v>942</v>
       </c>
       <c r="D180" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E180" s="18" t="s">
-        <v>1004</v>
+        <v>938</v>
       </c>
       <c r="F180" s="16"/>
       <c r="G180" s="16"/>
@@ -7045,16 +7324,16 @@
         <v>212</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>1006</v>
+        <v>943</v>
       </c>
       <c r="C181" s="18" t="s">
-        <v>1007</v>
+        <v>944</v>
       </c>
       <c r="D181" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E181" s="18" t="s">
-        <v>1008</v>
+        <v>945</v>
       </c>
       <c r="F181" s="16"/>
       <c r="G181" s="16"/>
@@ -7064,1500 +7343,2184 @@
         <v>212</v>
       </c>
       <c r="B182" s="18" t="s">
-        <v>986</v>
+        <v>946</v>
       </c>
       <c r="C182" s="18" t="s">
-        <v>1009</v>
+        <v>948</v>
       </c>
       <c r="D182" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E182" s="18" t="s">
-        <v>1012</v>
+        <v>949</v>
       </c>
       <c r="F182" s="16"/>
       <c r="G182" s="16"/>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B183" s="18" t="s">
-        <v>636</v>
+        <v>947</v>
       </c>
       <c r="C183" s="18" t="s">
-        <v>662</v>
+        <v>948</v>
       </c>
       <c r="D183" s="18" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E183" s="18" t="s">
-        <v>674</v>
+        <v>949</v>
       </c>
       <c r="F183" s="16"/>
       <c r="G183" s="16"/>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B184" s="18" t="s">
-        <v>637</v>
+        <v>951</v>
       </c>
       <c r="C184" s="18" t="s">
-        <v>663</v>
+        <v>950</v>
       </c>
       <c r="D184" s="18" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E184" s="18" t="s">
-        <v>675</v>
+        <v>953</v>
       </c>
       <c r="F184" s="16"/>
       <c r="G184" s="16"/>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>638</v>
+        <v>952</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>676</v>
+        <v>950</v>
       </c>
       <c r="D185" s="18" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E185" s="18" t="s">
-        <v>677</v>
+        <v>953</v>
       </c>
       <c r="F185" s="16"/>
       <c r="G185" s="16"/>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B186" s="18" t="s">
-        <v>649</v>
+        <v>954</v>
       </c>
       <c r="C186" s="18" t="s">
-        <v>648</v>
+        <v>955</v>
       </c>
       <c r="D186" s="18" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E186" s="18" t="s">
-        <v>678</v>
+        <v>968</v>
       </c>
       <c r="F186" s="16"/>
       <c r="G186" s="16"/>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B187" s="18" t="s">
-        <v>650</v>
-      </c>
-      <c r="C187" s="19" t="s">
-        <v>651</v>
+        <v>956</v>
+      </c>
+      <c r="C187" s="18" t="s">
+        <v>959</v>
       </c>
       <c r="D187" s="18" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E187" s="18" t="s">
-        <v>679</v>
+        <v>969</v>
       </c>
       <c r="F187" s="16"/>
       <c r="G187" s="16"/>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>639</v>
+        <v>957</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>664</v>
+        <v>960</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E188" s="18" t="s">
-        <v>717</v>
+        <v>970</v>
       </c>
       <c r="F188" s="16"/>
       <c r="G188" s="16"/>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>640</v>
+        <v>958</v>
       </c>
       <c r="C189" s="18" t="s">
-        <v>665</v>
+        <v>961</v>
       </c>
       <c r="D189" s="18" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E189" s="18" t="s">
-        <v>718</v>
+        <v>971</v>
       </c>
       <c r="F189" s="16"/>
       <c r="G189" s="16"/>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B190" s="18" t="s">
-        <v>641</v>
+        <v>963</v>
       </c>
       <c r="C190" s="18" t="s">
-        <v>666</v>
+        <v>962</v>
       </c>
       <c r="D190" s="18" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E190" s="18" t="s">
-        <v>719</v>
+        <v>996</v>
       </c>
       <c r="F190" s="16"/>
       <c r="G190" s="16"/>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>642</v>
+        <v>965</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>667</v>
+        <v>964</v>
       </c>
       <c r="D191" s="18" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E191" s="18" t="s">
-        <v>673</v>
+        <v>972</v>
       </c>
       <c r="F191" s="16"/>
       <c r="G191" s="16"/>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B192" s="18" t="s">
-        <v>643</v>
+        <v>966</v>
       </c>
       <c r="C192" s="18" t="s">
-        <v>668</v>
+        <v>967</v>
       </c>
       <c r="D192" s="18" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E192" s="18" t="s">
-        <v>720</v>
+        <v>973</v>
       </c>
       <c r="F192" s="16"/>
       <c r="G192" s="16"/>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B193" s="18" t="s">
-        <v>644</v>
+        <v>974</v>
       </c>
       <c r="C193" s="18" t="s">
-        <v>669</v>
+        <v>975</v>
       </c>
       <c r="D193" s="18" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E193" s="18" t="s">
-        <v>721</v>
+        <v>997</v>
       </c>
       <c r="F193" s="16"/>
       <c r="G193" s="16"/>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B194" s="18" t="s">
-        <v>645</v>
+        <v>977</v>
       </c>
       <c r="C194" s="18" t="s">
-        <v>670</v>
+        <v>976</v>
       </c>
       <c r="D194" s="18" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E194" s="18" t="s">
-        <v>722</v>
+        <v>978</v>
       </c>
       <c r="F194" s="16"/>
       <c r="G194" s="16"/>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B195" s="18" t="s">
-        <v>646</v>
+        <v>979</v>
       </c>
       <c r="C195" s="18" t="s">
-        <v>671</v>
+        <v>980</v>
       </c>
       <c r="D195" s="18" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E195" s="18" t="s">
-        <v>672</v>
+        <v>981</v>
       </c>
       <c r="F195" s="16"/>
       <c r="G195" s="16"/>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="18" t="s">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="B196" s="18" t="s">
-        <v>5</v>
+        <v>985</v>
       </c>
       <c r="C196" s="18" t="s">
-        <v>4</v>
+        <v>986</v>
       </c>
       <c r="D196" s="18" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="E196" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F196" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G196" s="16" t="s">
-        <v>7</v>
-      </c>
+        <v>998</v>
+      </c>
+      <c r="F196" s="16"/>
+      <c r="G196" s="16"/>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="18" t="s">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="B197" s="18" t="s">
-        <v>9</v>
+        <v>987</v>
       </c>
       <c r="C197" s="18" t="s">
-        <v>8</v>
+        <v>988</v>
       </c>
       <c r="D197" s="18" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="E197" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="F197" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G197" s="16" t="s">
-        <v>10</v>
-      </c>
+        <v>989</v>
+      </c>
+      <c r="F197" s="16"/>
+      <c r="G197" s="16"/>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="18" t="s">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="B198" s="18" t="s">
-        <v>12</v>
+        <v>982</v>
       </c>
       <c r="C198" s="18" t="s">
-        <v>11</v>
+        <v>990</v>
       </c>
       <c r="D198" s="18" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="E198" s="18" t="s">
-        <v>167</v>
+        <v>1008</v>
       </c>
       <c r="F198" s="16"/>
       <c r="G198" s="16"/>
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="18" t="s">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="B199" s="18" t="s">
-        <v>14</v>
+        <v>991</v>
       </c>
       <c r="C199" s="18" t="s">
-        <v>13</v>
+        <v>992</v>
       </c>
       <c r="D199" s="18" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="E199" s="18" t="s">
-        <v>166</v>
+        <v>999</v>
       </c>
       <c r="F199" s="16"/>
       <c r="G199" s="16"/>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="18" t="s">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="B200" s="18" t="s">
-        <v>16</v>
+        <v>993</v>
       </c>
       <c r="C200" s="18" t="s">
-        <v>15</v>
+        <v>994</v>
       </c>
       <c r="D200" s="18" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="E200" s="18" t="s">
-        <v>168</v>
+        <v>995</v>
       </c>
       <c r="F200" s="16"/>
       <c r="G200" s="16"/>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="18" t="s">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="B201" s="18" t="s">
-        <v>19</v>
+        <v>983</v>
       </c>
       <c r="C201" s="18" t="s">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="D201" s="18" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="E201" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="F201" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G201" s="16" t="s">
-        <v>134</v>
-      </c>
+        <v>1009</v>
+      </c>
+      <c r="F201" s="16"/>
+      <c r="G201" s="16"/>
     </row>
     <row r="202" spans="1:7">
       <c r="A202" s="18" t="s">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="B202" s="18" t="s">
-        <v>133</v>
+        <v>1003</v>
       </c>
       <c r="C202" s="18" t="s">
-        <v>20</v>
+        <v>1001</v>
       </c>
       <c r="D202" s="18" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="E202" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="F202" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G202" s="16" t="s">
-        <v>21</v>
-      </c>
+        <v>1002</v>
+      </c>
+      <c r="F202" s="16"/>
+      <c r="G202" s="16"/>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" s="18" t="s">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="B203" s="18" t="s">
-        <v>132</v>
+        <v>1004</v>
       </c>
       <c r="C203" s="18" t="s">
-        <v>17</v>
+        <v>1005</v>
       </c>
       <c r="D203" s="18" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="E203" s="18" t="s">
-        <v>140</v>
+        <v>1006</v>
       </c>
       <c r="F203" s="16"/>
       <c r="G203" s="16"/>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" s="18" t="s">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="B204" s="18" t="s">
-        <v>23</v>
+        <v>984</v>
       </c>
       <c r="C204" s="18" t="s">
-        <v>24</v>
+        <v>1007</v>
       </c>
       <c r="D204" s="18" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="E204" s="18" t="s">
-        <v>139</v>
+        <v>1010</v>
       </c>
       <c r="F204" s="16"/>
       <c r="G204" s="16"/>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B205" s="18" t="s">
-        <v>141</v>
+        <v>636</v>
       </c>
       <c r="C205" s="18" t="s">
-        <v>22</v>
+        <v>662</v>
       </c>
       <c r="D205" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E205" s="18" t="s">
-        <v>142</v>
+        <v>674</v>
       </c>
       <c r="F205" s="16"/>
       <c r="G205" s="16"/>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B206" s="18" t="s">
-        <v>25</v>
+        <v>637</v>
       </c>
       <c r="C206" s="18" t="s">
-        <v>26</v>
+        <v>663</v>
       </c>
       <c r="D206" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E206" s="18" t="s">
-        <v>143</v>
+        <v>675</v>
       </c>
       <c r="F206" s="16"/>
       <c r="G206" s="16"/>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B207" s="18" t="s">
-        <v>27</v>
+        <v>638</v>
       </c>
       <c r="C207" s="18" t="s">
-        <v>28</v>
+        <v>676</v>
       </c>
       <c r="D207" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E207" s="18" t="s">
-        <v>149</v>
+        <v>677</v>
       </c>
       <c r="F207" s="16"/>
       <c r="G207" s="16"/>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B208" s="18" t="s">
-        <v>29</v>
+        <v>649</v>
       </c>
       <c r="C208" s="18" t="s">
-        <v>30</v>
+        <v>648</v>
       </c>
       <c r="D208" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E208" s="18" t="s">
-        <v>148</v>
+        <v>678</v>
       </c>
       <c r="F208" s="16"/>
       <c r="G208" s="16"/>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B209" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C209" s="18" t="s">
-        <v>32</v>
+        <v>650</v>
+      </c>
+      <c r="C209" s="19" t="s">
+        <v>651</v>
       </c>
       <c r="D209" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E209" s="18" t="s">
-        <v>147</v>
+        <v>679</v>
       </c>
       <c r="F209" s="16"/>
       <c r="G209" s="16"/>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B210" s="18" t="s">
-        <v>33</v>
+        <v>639</v>
       </c>
       <c r="C210" s="18" t="s">
-        <v>34</v>
+        <v>664</v>
       </c>
       <c r="D210" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E210" s="18" t="s">
-        <v>146</v>
+        <v>717</v>
       </c>
       <c r="F210" s="16"/>
       <c r="G210" s="16"/>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B211" s="18" t="s">
-        <v>35</v>
+        <v>640</v>
       </c>
       <c r="C211" s="18" t="s">
-        <v>36</v>
+        <v>665</v>
       </c>
       <c r="D211" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E211" s="18" t="s">
-        <v>145</v>
+        <v>718</v>
       </c>
       <c r="F211" s="16"/>
       <c r="G211" s="16"/>
     </row>
     <row r="212" spans="1:7">
       <c r="A212" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B212" s="18" t="s">
-        <v>37</v>
+        <v>641</v>
       </c>
       <c r="C212" s="18" t="s">
-        <v>38</v>
+        <v>666</v>
       </c>
       <c r="D212" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E212" s="18" t="s">
-        <v>144</v>
+        <v>719</v>
       </c>
       <c r="F212" s="16"/>
       <c r="G212" s="16"/>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B213" s="18" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="C213" s="18" t="s">
-        <v>150</v>
+        <v>667</v>
       </c>
       <c r="D213" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E213" s="18" t="s">
-        <v>151</v>
+        <v>673</v>
       </c>
       <c r="F213" s="16"/>
       <c r="G213" s="16"/>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="B214" s="28" t="s">
-        <v>40</v>
+        <v>282</v>
+      </c>
+      <c r="B214" s="18" t="s">
+        <v>643</v>
       </c>
       <c r="C214" s="18" t="s">
-        <v>4</v>
+        <v>668</v>
       </c>
       <c r="D214" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E214" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="F214" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G214" s="16" t="s">
-        <v>7</v>
-      </c>
+        <v>720</v>
+      </c>
+      <c r="F214" s="16"/>
+      <c r="G214" s="16"/>
     </row>
     <row r="215" spans="1:7">
       <c r="A215" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B215" s="18" t="s">
-        <v>9</v>
+        <v>644</v>
       </c>
       <c r="C215" s="18" t="s">
-        <v>8</v>
+        <v>669</v>
       </c>
       <c r="D215" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E215" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="F215" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G215" s="16" t="s">
-        <v>10</v>
-      </c>
+        <v>721</v>
+      </c>
+      <c r="F215" s="16"/>
+      <c r="G215" s="16"/>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B216" s="18" t="s">
-        <v>41</v>
+        <v>645</v>
       </c>
       <c r="C216" s="18" t="s">
-        <v>11</v>
+        <v>670</v>
       </c>
       <c r="D216" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E216" s="18" t="s">
-        <v>171</v>
+        <v>722</v>
       </c>
       <c r="F216" s="16"/>
       <c r="G216" s="16"/>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B217" s="18" t="s">
-        <v>42</v>
+        <v>646</v>
       </c>
       <c r="C217" s="18" t="s">
-        <v>13</v>
+        <v>671</v>
       </c>
       <c r="D217" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E217" s="18" t="s">
-        <v>172</v>
+        <v>672</v>
       </c>
       <c r="F217" s="16"/>
       <c r="G217" s="16"/>
     </row>
     <row r="218" spans="1:7">
       <c r="A218" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B218" s="18" t="s">
-        <v>43</v>
+        <v>1089</v>
       </c>
       <c r="C218" s="18" t="s">
-        <v>15</v>
+        <v>1095</v>
       </c>
       <c r="D218" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E218" s="18" t="s">
-        <v>173</v>
+        <v>717</v>
       </c>
       <c r="F218" s="16"/>
       <c r="G218" s="16"/>
     </row>
     <row r="219" spans="1:7">
       <c r="A219" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B219" s="18" t="s">
-        <v>44</v>
+        <v>1090</v>
       </c>
       <c r="C219" s="18" t="s">
-        <v>17</v>
+        <v>1096</v>
       </c>
       <c r="D219" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E219" s="18" t="s">
-        <v>152</v>
+        <v>718</v>
       </c>
       <c r="F219" s="16"/>
       <c r="G219" s="16"/>
     </row>
     <row r="220" spans="1:7">
       <c r="A220" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B220" s="18" t="s">
-        <v>45</v>
+        <v>1091</v>
       </c>
       <c r="C220" s="18" t="s">
-        <v>18</v>
+        <v>1097</v>
       </c>
       <c r="D220" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E220" s="18" t="s">
-        <v>153</v>
+        <v>719</v>
       </c>
       <c r="F220" s="16"/>
       <c r="G220" s="16"/>
     </row>
     <row r="221" spans="1:7">
       <c r="A221" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B221" s="18" t="s">
-        <v>46</v>
+        <v>1092</v>
       </c>
       <c r="C221" s="18" t="s">
-        <v>22</v>
+        <v>1098</v>
       </c>
       <c r="D221" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E221" s="18" t="s">
-        <v>154</v>
+        <v>720</v>
       </c>
       <c r="F221" s="16"/>
       <c r="G221" s="16"/>
     </row>
     <row r="222" spans="1:7">
       <c r="A222" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B222" s="18" t="s">
-        <v>47</v>
+        <v>1093</v>
       </c>
       <c r="C222" s="18" t="s">
-        <v>24</v>
+        <v>1099</v>
       </c>
       <c r="D222" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E222" s="18" t="s">
-        <v>155</v>
+        <v>721</v>
       </c>
       <c r="F222" s="16"/>
       <c r="G222" s="16"/>
     </row>
     <row r="223" spans="1:7">
       <c r="A223" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B223" s="18" t="s">
-        <v>48</v>
+        <v>1094</v>
       </c>
       <c r="C223" s="18" t="s">
-        <v>26</v>
+        <v>1100</v>
       </c>
       <c r="D223" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E223" s="18" t="s">
-        <v>156</v>
+        <v>722</v>
       </c>
       <c r="F223" s="16"/>
       <c r="G223" s="16"/>
     </row>
     <row r="224" spans="1:7">
       <c r="A224" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B224" s="18" t="s">
-        <v>49</v>
+        <v>1016</v>
       </c>
       <c r="C224" s="18" t="s">
-        <v>28</v>
+        <v>1017</v>
       </c>
       <c r="D224" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E224" s="18" t="s">
-        <v>157</v>
+        <v>1023</v>
       </c>
       <c r="F224" s="16"/>
       <c r="G224" s="16"/>
     </row>
     <row r="225" spans="1:7">
       <c r="A225" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B225" s="18" t="s">
-        <v>50</v>
+        <v>1018</v>
       </c>
       <c r="C225" s="18" t="s">
-        <v>30</v>
+        <v>1019</v>
       </c>
       <c r="D225" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E225" s="18" t="s">
-        <v>158</v>
+        <v>1024</v>
       </c>
       <c r="F225" s="16"/>
       <c r="G225" s="16"/>
     </row>
     <row r="226" spans="1:7">
       <c r="A226" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B226" s="18" t="s">
-        <v>51</v>
+        <v>1020</v>
       </c>
       <c r="C226" s="18" t="s">
-        <v>32</v>
+        <v>1027</v>
       </c>
       <c r="D226" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E226" s="18" t="s">
-        <v>159</v>
+        <v>1025</v>
       </c>
       <c r="F226" s="16"/>
       <c r="G226" s="16"/>
     </row>
     <row r="227" spans="1:7">
       <c r="A227" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B227" s="18" t="s">
-        <v>52</v>
+        <v>1040</v>
       </c>
       <c r="C227" s="18" t="s">
-        <v>34</v>
+        <v>1041</v>
       </c>
       <c r="D227" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E227" s="18" t="s">
-        <v>160</v>
+        <v>1026</v>
       </c>
       <c r="F227" s="16"/>
       <c r="G227" s="16"/>
     </row>
     <row r="228" spans="1:7">
       <c r="A228" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B228" s="18" t="s">
-        <v>53</v>
+        <v>1021</v>
       </c>
       <c r="C228" s="18" t="s">
-        <v>36</v>
+        <v>1022</v>
       </c>
       <c r="D228" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E228" s="18" t="s">
-        <v>161</v>
+        <v>1042</v>
       </c>
       <c r="F228" s="16"/>
       <c r="G228" s="16"/>
     </row>
     <row r="229" spans="1:7">
       <c r="A229" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B229" s="18" t="s">
-        <v>54</v>
+        <v>1031</v>
       </c>
       <c r="C229" s="18" t="s">
-        <v>38</v>
+        <v>1032</v>
       </c>
       <c r="D229" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E229" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="F229" s="16"/>
-      <c r="G229" s="16"/>
+        <v>1038</v>
+      </c>
+      <c r="F229" s="20"/>
+      <c r="G229" s="20"/>
     </row>
     <row r="230" spans="1:7">
       <c r="A230" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B230" s="18" t="s">
-        <v>55</v>
+        <v>1033</v>
       </c>
       <c r="C230" s="18" t="s">
-        <v>150</v>
+        <v>1034</v>
       </c>
       <c r="D230" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E230" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="F230" s="16"/>
-      <c r="G230" s="16"/>
+        <v>1035</v>
+      </c>
+      <c r="F230" s="20"/>
+      <c r="G230" s="20"/>
     </row>
     <row r="231" spans="1:7">
       <c r="A231" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B231" s="18" t="s">
-        <v>57</v>
+        <v>1036</v>
       </c>
       <c r="C231" s="18" t="s">
-        <v>56</v>
+        <v>1037</v>
       </c>
       <c r="D231" s="18" t="s">
         <v>200</v>
       </c>
       <c r="E231" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="F231" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G231" s="16" t="s">
-        <v>58</v>
-      </c>
+        <v>1039</v>
+      </c>
+      <c r="F231" s="20"/>
+      <c r="G231" s="20"/>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B232" s="18" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="C232" s="18" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="D232" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E232" s="18" t="s">
-        <v>622</v>
-      </c>
-      <c r="F232" s="16"/>
-      <c r="G232" s="16"/>
+        <v>164</v>
+      </c>
+      <c r="F232" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G232" s="16" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="233" spans="1:7">
       <c r="A233" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B233" s="18" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="C233" s="18" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D233" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E233" s="18" t="s">
-        <v>623</v>
+        <v>165</v>
       </c>
       <c r="F233" s="16" t="s">
         <v>6</v>
       </c>
       <c r="G233" s="16" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
     </row>
     <row r="234" spans="1:7">
       <c r="A234" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B234" s="18" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="C234" s="18" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="D234" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E234" s="18" t="s">
-        <v>627</v>
+        <v>167</v>
       </c>
       <c r="F234" s="16"/>
       <c r="G234" s="16"/>
     </row>
     <row r="235" spans="1:7">
       <c r="A235" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B235" s="18" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="C235" s="18" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D235" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E235" s="18" t="s">
-        <v>626</v>
-      </c>
-      <c r="F235" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G235" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="F235" s="16"/>
+      <c r="G235" s="16"/>
     </row>
     <row r="236" spans="1:7">
       <c r="A236" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B236" s="18" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="C236" s="18" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="D236" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E236" s="18" t="s">
-        <v>624</v>
+        <v>168</v>
       </c>
       <c r="F236" s="16"/>
       <c r="G236" s="16"/>
     </row>
     <row r="237" spans="1:7">
       <c r="A237" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B237" s="18" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="C237" s="18" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D237" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E237" s="18" t="s">
-        <v>625</v>
+        <v>137</v>
       </c>
       <c r="F237" s="16" t="s">
         <v>6</v>
       </c>
       <c r="G237" s="16" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
     </row>
     <row r="238" spans="1:7">
       <c r="A238" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B238" s="18" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="C238" s="18" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D238" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E238" s="18" t="s">
-        <v>629</v>
-      </c>
-      <c r="F238" s="16"/>
-      <c r="G238" s="16"/>
+        <v>138</v>
+      </c>
+      <c r="F238" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G238" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="239" spans="1:7">
       <c r="A239" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B239" s="18" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="C239" s="18" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="D239" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E239" s="18" t="s">
-        <v>630</v>
-      </c>
-      <c r="F239" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G239" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="F239" s="16"/>
+      <c r="G239" s="16"/>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B240" s="18" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="C240" s="18" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="D240" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E240" s="18" t="s">
-        <v>628</v>
+        <v>139</v>
       </c>
       <c r="F240" s="16"/>
       <c r="G240" s="16"/>
     </row>
     <row r="241" spans="1:7">
       <c r="A241" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B241" s="18" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="C241" s="18" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="D241" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E241" s="18" t="s">
-        <v>631</v>
-      </c>
-      <c r="F241" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G241" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="F241" s="16"/>
+      <c r="G241" s="16"/>
     </row>
     <row r="242" spans="1:7">
       <c r="A242" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B242" s="18" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="C242" s="18" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="D242" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E242" s="18" t="s">
-        <v>684</v>
-      </c>
-      <c r="F242" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G242" s="16" t="s">
-        <v>82</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="F242" s="16"/>
+      <c r="G242" s="16"/>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B243" s="18" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="C243" s="18" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="D243" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E243" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="F243" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G243" s="16" t="s">
-        <v>85</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="F243" s="16"/>
+      <c r="G243" s="16"/>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B244" s="18" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="C244" s="18" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="D244" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E244" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="F244" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G244" s="16" t="s">
-        <v>88</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="F244" s="16"/>
+      <c r="G244" s="16"/>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B245" s="18" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="C245" s="18" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="D245" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E245" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="F245" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G245" s="16" t="s">
-        <v>91</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="F245" s="16"/>
+      <c r="G245" s="16"/>
     </row>
     <row r="246" spans="1:7">
       <c r="A246" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="D246" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E246" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="F246" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G246" s="16" t="s">
-        <v>94</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="F246" s="16"/>
+      <c r="G246" s="16"/>
     </row>
     <row r="247" spans="1:7">
       <c r="A247" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="C247" s="18" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="D247" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E247" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="F247" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G247" s="16" t="s">
-        <v>97</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="F247" s="16"/>
+      <c r="G247" s="16"/>
     </row>
     <row r="248" spans="1:7">
       <c r="A248" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B248" s="18" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="C248" s="18" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="D248" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E248" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="F248" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G248" s="16" t="s">
-        <v>100</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="F248" s="16"/>
+      <c r="G248" s="16"/>
     </row>
     <row r="249" spans="1:7">
       <c r="A249" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>101</v>
+        <v>150</v>
       </c>
       <c r="D249" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E249" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="F249" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G249" s="16" t="s">
-        <v>103</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="F249" s="16"/>
+      <c r="G249" s="16"/>
     </row>
     <row r="250" spans="1:7">
       <c r="A250" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="B250" s="18" t="s">
-        <v>105</v>
+        <v>118</v>
+      </c>
+      <c r="B250" s="28" t="s">
+        <v>40</v>
       </c>
       <c r="C250" s="18" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="D250" s="18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E250" s="18" t="s">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="F250" s="16" t="s">
         <v>6</v>
       </c>
       <c r="G250" s="16" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
     </row>
     <row r="251" spans="1:7">
       <c r="A251" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="C251" s="18" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="D251" s="18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E251" s="18" t="s">
-        <v>632</v>
-      </c>
-      <c r="F251" s="16"/>
-      <c r="G251" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="F251" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G251" s="16" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="252" spans="1:7">
       <c r="A252" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="D252" s="18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E252" s="18" t="s">
-        <v>680</v>
-      </c>
-      <c r="F252" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G252" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="F252" s="16"/>
+      <c r="G252" s="16"/>
     </row>
     <row r="253" spans="1:7">
       <c r="A253" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="C253" s="18" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D253" s="18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E253" s="18" t="s">
-        <v>682</v>
+        <v>172</v>
       </c>
       <c r="F253" s="16"/>
       <c r="G253" s="16"/>
     </row>
     <row r="254" spans="1:7">
       <c r="A254" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E254" s="18" t="s">
-        <v>681</v>
-      </c>
-      <c r="F254" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G254" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="F254" s="16"/>
+      <c r="G254" s="16"/>
     </row>
     <row r="255" spans="1:7">
       <c r="A255" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B255" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C255" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D255" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E255" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="F255" s="16"/>
+      <c r="G255" s="16"/>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B256" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C256" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D256" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E256" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="F256" s="16"/>
+      <c r="G256" s="16"/>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B257" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C257" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D257" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E257" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="F257" s="16"/>
+      <c r="G257" s="16"/>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B258" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C258" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D258" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E258" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F258" s="16"/>
+      <c r="G258" s="16"/>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B259" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C259" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D259" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E259" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="F259" s="16"/>
+      <c r="G259" s="16"/>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B260" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C260" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D260" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E260" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F260" s="16"/>
+      <c r="G260" s="16"/>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B261" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C261" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D261" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E261" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="F261" s="16"/>
+      <c r="G261" s="16"/>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B262" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C262" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D262" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E262" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F262" s="16"/>
+      <c r="G262" s="16"/>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B263" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C263" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D263" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E263" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F263" s="16"/>
+      <c r="G263" s="16"/>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B264" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C264" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D264" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E264" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="F264" s="16"/>
+      <c r="G264" s="16"/>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B265" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C265" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D265" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E265" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="F265" s="16"/>
+      <c r="G265" s="16"/>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B266" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C266" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="D266" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E266" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="F266" s="16"/>
+      <c r="G266" s="16"/>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" s="18" t="s">
         <v>282</v>
       </c>
-      <c r="B255" s="18" t="s">
+      <c r="B267" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C267" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D267" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E267" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="F267" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G267" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B268" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C268" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D268" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E268" s="18" t="s">
+        <v>622</v>
+      </c>
+      <c r="F268" s="16"/>
+      <c r="G268" s="16"/>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B269" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C269" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D269" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E269" s="18" t="s">
+        <v>623</v>
+      </c>
+      <c r="F269" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G269" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B270" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C270" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D270" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E270" s="18" t="s">
+        <v>627</v>
+      </c>
+      <c r="F270" s="16"/>
+      <c r="G270" s="16"/>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B271" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C271" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D271" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E271" s="18" t="s">
+        <v>626</v>
+      </c>
+      <c r="F271" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G271" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B272" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C272" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D272" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E272" s="18" t="s">
+        <v>624</v>
+      </c>
+      <c r="F272" s="16"/>
+      <c r="G272" s="16"/>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B273" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C273" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D273" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E273" s="18" t="s">
+        <v>625</v>
+      </c>
+      <c r="F273" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G273" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B274" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C274" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D274" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E274" s="18" t="s">
+        <v>629</v>
+      </c>
+      <c r="F274" s="16"/>
+      <c r="G274" s="16"/>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B275" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C275" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D275" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E275" s="18" t="s">
+        <v>630</v>
+      </c>
+      <c r="F275" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G275" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B276" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C276" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D276" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E276" s="18" t="s">
+        <v>628</v>
+      </c>
+      <c r="F276" s="16"/>
+      <c r="G276" s="16"/>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B277" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C277" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D277" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E277" s="18" t="s">
+        <v>631</v>
+      </c>
+      <c r="F277" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G277" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B278" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C278" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D278" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E278" s="18" t="s">
+        <v>684</v>
+      </c>
+      <c r="F278" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G278" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B279" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C279" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D279" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E279" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="F279" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G279" s="16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B280" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C280" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D280" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E280" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="F280" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G280" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B281" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C281" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D281" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E281" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="F281" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G281" s="16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B282" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C282" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D282" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E282" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="F282" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G282" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B283" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C283" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D283" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E283" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="F283" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G283" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B284" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C284" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D284" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E284" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="F284" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G284" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B285" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C285" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D285" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E285" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="F285" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G285" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B286" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C286" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D286" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E286" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="F286" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G286" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B287" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C287" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D287" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E287" s="18" t="s">
+        <v>632</v>
+      </c>
+      <c r="F287" s="16"/>
+      <c r="G287" s="16"/>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B288" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C288" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D288" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E288" s="18" t="s">
+        <v>680</v>
+      </c>
+      <c r="F288" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G288" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B289" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C289" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D289" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E289" s="18" t="s">
+        <v>682</v>
+      </c>
+      <c r="F289" s="16"/>
+      <c r="G289" s="16"/>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B290" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C290" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D290" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E290" s="18" t="s">
+        <v>681</v>
+      </c>
+      <c r="F290" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G290" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B291" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="C255" s="18" t="s">
+      <c r="C291" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D255" s="18" t="s">
+      <c r="D291" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="E255" s="18" t="s">
+      <c r="E291" s="18" t="s">
         <v>683</v>
       </c>
-      <c r="F255" s="16" t="s">
+      <c r="F291" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G255" s="16" t="s">
+      <c r="G291" s="16" t="s">
         <v>117</v>
       </c>
     </row>

--- a/run/nhanes_pullrequest_IndVsArea_07.30.2026.xlsx
+++ b/run/nhanes_pullrequest_IndVsArea_07.30.2026.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jg1671/Documents/GitHub/nhanes_area_ses/run/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC6DD6C-88E1-B243-8078-C2C267C7FE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA9C5BD-9A37-FA41-9D67-B699D16BD182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16240" xr2:uid="{BFFDAA01-B797-C24A-A87F-A362CCE94DEB}"/>
+    <workbookView xWindow="36900" yWindow="2060" windowWidth="36800" windowHeight="21340" xr2:uid="{BFFDAA01-B797-C24A-A87F-A362CCE94DEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable_List" sheetId="6" r:id="rId1"/>
-    <sheet name="Variable_List_2" sheetId="4" r:id="rId2"/>
-    <sheet name="Variable_List_1" sheetId="5" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId2"/>
+    <sheet name="Variable_List_2" sheetId="4" r:id="rId3"/>
+    <sheet name="Variable_List_1" sheetId="5" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$H$1:$H$153</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,8 +41,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4176" uniqueCount="1106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4399" uniqueCount="1145">
   <si>
     <t>RECODE</t>
   </si>
@@ -3356,13 +3382,130 @@
   </si>
   <si>
     <t>LBXTLG</t>
+  </si>
+  <si>
+    <t>WTINT2YR</t>
+  </si>
+  <si>
+    <t>WTMEC2YR</t>
+  </si>
+  <si>
+    <t>WTSCI2YR</t>
+  </si>
+  <si>
+    <t>WTDR2D</t>
+  </si>
+  <si>
+    <t>RXDRSC1</t>
+  </si>
+  <si>
+    <t>RXDRSC3</t>
+  </si>
+  <si>
+    <t>RXDRSC2</t>
+  </si>
+  <si>
+    <t>ICD-10-CM code 3.</t>
+  </si>
+  <si>
+    <t>ICD-10-CM code 2.</t>
+  </si>
+  <si>
+    <t>ICD-10-CM code 1.</t>
+  </si>
+  <si>
+    <t>q_icd2</t>
+  </si>
+  <si>
+    <t>q_icd1</t>
+  </si>
+  <si>
+    <t>q_icd3</t>
+  </si>
+  <si>
+    <t>PAD200</t>
+  </si>
+  <si>
+    <t>PAD320</t>
+  </si>
+  <si>
+    <t>The next questions are about physical activities including exercise, sports, and physically active hobbies that {you/SP} may have done in {your/his/her} leisure time or at school over the past 30 days. First I will ask you about vigorous activities that cause heavy sweating or large increases in breathing or heart rate. Then I will ask you about moderate activities that cause only light sweating or a slight to moderate increase in breathing or heart rate. Over the past 30 days, did {you/SP} do any vigorous activities for at least 10 minutes that caused heavy sweating, or large increases in breathing or heart rate? Some examples are running, lap swimming, aerobics classes or fast bicycling</t>
+  </si>
+  <si>
+    <t>[Over the past 30 days], did {you/SP} do moderate activities for at least 10 minutes that cause only light sweating or a slight to moderate increase in breathing or heart rate? Some examples are brisk walking, bicycling for pleasure, golf, and dancing .</t>
+  </si>
+  <si>
+    <t>q_mvpa_anympa</t>
+  </si>
+  <si>
+    <t>q_mvpa_anyvpa</t>
+  </si>
+  <si>
+    <t>ALQ101</t>
+  </si>
+  <si>
+    <t>ALQ100</t>
+  </si>
+  <si>
+    <t>The next questions are about drinking alcoholic beverages. Included are liquor (such as whiskey or gin), beer, wine, wine coolers, and any other type of alcoholic beverage. In any one year, {have you/has SP} had at least 12 drinks of any type of alcoholic beverage? By a drink, I mean a 12 oz. beer, a 4 oz. glass of wine, or an ounce of liquor.</t>
+  </si>
+  <si>
+    <t>ALQ110</t>
+  </si>
+  <si>
+    <t>q_alc_any_yr</t>
+  </si>
+  <si>
+    <t>q_alc_any_life</t>
+  </si>
+  <si>
+    <t>In {your/SP's} entire life, {have you/has he/has she} had at least 12 drinks of any type of alcoholic beverage?</t>
+  </si>
+  <si>
+    <t>ALQ111</t>
+  </si>
+  <si>
+    <t>The next questions are about drinking alcoholic beverages. Included are liquor (such as whiskey or gin), beer, wine, wine coolers, and any other type of alcoholic beverage.\r In {your/SP's} entire life, {have you/has he/has she} had at least 1 drink of any kind of alcohol, not counting small tastes or sips? By a drink, I mean a 12 oz. beer, a 5 oz. glass of wine, or one and a half ounces of liquor.</t>
+  </si>
+  <si>
+    <t>ALQ121</t>
+  </si>
+  <si>
+    <t>During the past 12 months, about how often did {you/SP} drink any type of alcoholic beverage?\r PROBE: How many days per week, per month, or per year did {you/SP} drink?</t>
+  </si>
+  <si>
+    <t>ALD100</t>
+  </si>
+  <si>
+    <t>special</t>
+  </si>
+  <si>
+    <t>q_anxietty</t>
+  </si>
+  <si>
+    <t>q_genhealth</t>
+  </si>
+  <si>
+    <t>q_hc_</t>
+  </si>
+  <si>
+    <t>q_hh_</t>
+  </si>
+  <si>
+    <t>HUQ080</t>
+  </si>
+  <si>
+    <t>How many different times did {you/SP} stay in any hospital overnight or longer {during the past 12 months}?</t>
+  </si>
+  <si>
+    <t>HUD070</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3436,6 +3579,31 @@
       <sz val="12"/>
       <name val="Aptos Display"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3514,7 +3682,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -3548,6 +3716,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3882,12 +4054,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3D6F9ED-9DEC-0147-B030-50BD2869D005}">
-  <dimension ref="A1:G291"/>
+  <dimension ref="A1:G304"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="19.5" style="5" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="126.6640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="120.5" style="5" customWidth="1"/>
     <col min="4" max="4" width="25.83203125" style="5" customWidth="1"/>
     <col min="5" max="5" width="33.6640625" style="5" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
@@ -3961,7 +4133,7 @@
         <v>182</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>193</v>
+        <v>704</v>
       </c>
       <c r="E4" s="18"/>
       <c r="F4" s="16"/>
@@ -3978,7 +4150,7 @@
         <v>647</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>193</v>
+        <v>704</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="16"/>
@@ -3994,8 +4166,8 @@
       <c r="C6" s="18" t="s">
         <v>1088</v>
       </c>
-      <c r="D6" s="18" t="s">
-        <v>704</v>
+      <c r="D6" t="s">
+        <v>1106</v>
       </c>
       <c r="E6" s="18"/>
       <c r="F6" s="16"/>
@@ -4011,8 +4183,8 @@
       <c r="C7" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D7" s="18" t="s">
-        <v>193</v>
+      <c r="D7" t="s">
+        <v>1106</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>119</v>
@@ -4030,8 +4202,8 @@
       <c r="C8" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="18" t="s">
-        <v>193</v>
+      <c r="D8" t="s">
+        <v>1106</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>213</v>
@@ -4049,8 +4221,8 @@
       <c r="C9" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="D9" s="18" t="s">
-        <v>223</v>
+      <c r="D9" t="s">
+        <v>1106</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>215</v>
@@ -4068,8 +4240,8 @@
       <c r="C10" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>193</v>
+      <c r="D10" t="s">
+        <v>1106</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>135</v>
@@ -4091,8 +4263,8 @@
       <c r="C11" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>193</v>
+      <c r="D11" t="s">
+        <v>1106</v>
       </c>
       <c r="E11" s="18" t="s">
         <v>136</v>
@@ -4114,8 +4286,8 @@
       <c r="C12" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="D12" s="18" t="s">
-        <v>193</v>
+      <c r="D12" t="s">
+        <v>1106</v>
       </c>
       <c r="E12" s="18" t="s">
         <v>283</v>
@@ -4137,8 +4309,8 @@
       <c r="C13" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>193</v>
+      <c r="D13" t="s">
+        <v>1106</v>
       </c>
       <c r="E13" s="28"/>
       <c r="F13" s="20"/>
@@ -4154,8 +4326,8 @@
       <c r="C14" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="D14" s="18" t="s">
-        <v>193</v>
+      <c r="D14" t="s">
+        <v>1106</v>
       </c>
       <c r="E14" s="28"/>
       <c r="F14" s="20"/>
@@ -4171,8 +4343,8 @@
       <c r="C15" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="D15" s="18" t="s">
-        <v>193</v>
+      <c r="D15" t="s">
+        <v>1106</v>
       </c>
       <c r="E15" s="18" t="s">
         <v>190</v>
@@ -4190,8 +4362,8 @@
       <c r="C16" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="D16" s="18" t="s">
-        <v>193</v>
+      <c r="D16" t="s">
+        <v>1106</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>220</v>
@@ -4209,8 +4381,8 @@
       <c r="C17" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="D17" s="18" t="s">
-        <v>193</v>
+      <c r="D17" t="s">
+        <v>1106</v>
       </c>
       <c r="E17" s="18" t="s">
         <v>221</v>
@@ -4228,8 +4400,8 @@
       <c r="C18" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="D18" s="18" t="s">
-        <v>193</v>
+      <c r="D18" t="s">
+        <v>1106</v>
       </c>
       <c r="E18" s="18" t="s">
         <v>220</v>
@@ -4247,8 +4419,8 @@
       <c r="C19" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="D19" s="18" t="s">
-        <v>193</v>
+      <c r="D19" t="s">
+        <v>1106</v>
       </c>
       <c r="E19" s="18" t="s">
         <v>284</v>
@@ -4266,8 +4438,8 @@
       <c r="C20" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="D20" s="18" t="s">
-        <v>193</v>
+      <c r="D20" t="s">
+        <v>1106</v>
       </c>
       <c r="E20" s="18" t="s">
         <v>284</v>
@@ -4285,8 +4457,8 @@
       <c r="C21" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="D21" s="18" t="s">
-        <v>193</v>
+      <c r="D21" t="s">
+        <v>1106</v>
       </c>
       <c r="E21" s="18" t="s">
         <v>285</v>
@@ -4304,8 +4476,8 @@
       <c r="C22" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="D22" s="18" t="s">
-        <v>193</v>
+      <c r="D22" t="s">
+        <v>1106</v>
       </c>
       <c r="E22" s="18" t="s">
         <v>285</v>
@@ -4323,8 +4495,8 @@
       <c r="C23" s="18" t="s">
         <v>655</v>
       </c>
-      <c r="D23" s="18" t="s">
-        <v>193</v>
+      <c r="D23" t="s">
+        <v>1106</v>
       </c>
       <c r="E23" s="18" t="s">
         <v>656</v>
@@ -4343,7 +4515,7 @@
         <v>228</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>229</v>
+        <v>704</v>
       </c>
       <c r="E24" s="18"/>
       <c r="F24" s="20"/>
@@ -4359,8 +4531,8 @@
       <c r="C25" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="D25" s="18" t="s">
-        <v>229</v>
+      <c r="D25" s="28" t="s">
+        <v>227</v>
       </c>
       <c r="E25" s="18" t="s">
         <v>827</v>
@@ -4378,8 +4550,8 @@
       <c r="C26" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="D26" s="18" t="s">
-        <v>229</v>
+      <c r="D26" t="s">
+        <v>1107</v>
       </c>
       <c r="E26" s="18" t="s">
         <v>828</v>
@@ -4397,8 +4569,8 @@
       <c r="C27" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="D27" s="18" t="s">
-        <v>229</v>
+      <c r="D27" t="s">
+        <v>1107</v>
       </c>
       <c r="E27" s="18" t="s">
         <v>1013</v>
@@ -4416,8 +4588,8 @@
       <c r="C28" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="D28" s="18" t="s">
-        <v>229</v>
+      <c r="D28" t="s">
+        <v>1107</v>
       </c>
       <c r="E28" s="18" t="s">
         <v>829</v>
@@ -4435,8 +4607,8 @@
       <c r="C29" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="D29" s="18" t="s">
-        <v>229</v>
+      <c r="D29" t="s">
+        <v>1107</v>
       </c>
       <c r="E29" s="18" t="s">
         <v>830</v>
@@ -4454,8 +4626,8 @@
       <c r="C30" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="D30" s="18" t="s">
-        <v>229</v>
+      <c r="D30" t="s">
+        <v>1107</v>
       </c>
       <c r="E30" s="18" t="s">
         <v>831</v>
@@ -4473,8 +4645,8 @@
       <c r="C31" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="D31" s="18" t="s">
-        <v>229</v>
+      <c r="D31" t="s">
+        <v>1107</v>
       </c>
       <c r="E31" s="18" t="s">
         <v>832</v>
@@ -4492,8 +4664,8 @@
       <c r="C32" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="D32" s="18" t="s">
-        <v>229</v>
+      <c r="D32" t="s">
+        <v>1107</v>
       </c>
       <c r="E32" s="18" t="s">
         <v>833</v>
@@ -4511,8 +4683,8 @@
       <c r="C33" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="D33" s="18" t="s">
-        <v>229</v>
+      <c r="D33" t="s">
+        <v>1107</v>
       </c>
       <c r="E33" s="18" t="s">
         <v>834</v>
@@ -4530,8 +4702,8 @@
       <c r="C34" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="D34" s="18" t="s">
-        <v>229</v>
+      <c r="D34" t="s">
+        <v>1107</v>
       </c>
       <c r="E34" s="18" t="s">
         <v>835</v>
@@ -4549,8 +4721,8 @@
       <c r="C35" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="D35" s="18" t="s">
-        <v>229</v>
+      <c r="D35" t="s">
+        <v>1107</v>
       </c>
       <c r="E35" s="18" t="s">
         <v>836</v>
@@ -4568,8 +4740,8 @@
       <c r="C36" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="D36" s="18" t="s">
-        <v>229</v>
+      <c r="D36" t="s">
+        <v>1107</v>
       </c>
       <c r="E36" s="18" t="s">
         <v>837</v>
@@ -4587,8 +4759,8 @@
       <c r="C37" s="18" t="s">
         <v>711</v>
       </c>
-      <c r="D37" s="18" t="s">
-        <v>229</v>
+      <c r="D37" t="s">
+        <v>1107</v>
       </c>
       <c r="E37" s="18" t="s">
         <v>838</v>
@@ -4606,8 +4778,8 @@
       <c r="C38" s="18" t="s">
         <v>708</v>
       </c>
-      <c r="D38" s="18" t="s">
-        <v>229</v>
+      <c r="D38" s="28" t="s">
+        <v>227</v>
       </c>
       <c r="E38" s="18" t="s">
         <v>839</v>
@@ -4625,8 +4797,8 @@
       <c r="C39" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="D39" s="18" t="s">
-        <v>229</v>
+      <c r="D39" t="s">
+        <v>1107</v>
       </c>
       <c r="E39" s="18" t="s">
         <v>840</v>
@@ -4644,8 +4816,8 @@
       <c r="C40" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="D40" s="18" t="s">
-        <v>229</v>
+      <c r="D40" t="s">
+        <v>1107</v>
       </c>
       <c r="E40" s="18" t="s">
         <v>841</v>
@@ -4663,8 +4835,8 @@
       <c r="C41" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="D41" s="18" t="s">
-        <v>229</v>
+      <c r="D41" t="s">
+        <v>1107</v>
       </c>
       <c r="E41" s="18" t="s">
         <v>842</v>
@@ -4682,8 +4854,8 @@
       <c r="C42" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="D42" s="18" t="s">
-        <v>229</v>
+      <c r="D42" t="s">
+        <v>1107</v>
       </c>
       <c r="E42" s="18" t="s">
         <v>843</v>
@@ -4701,8 +4873,8 @@
       <c r="C43" s="18" t="s">
         <v>398</v>
       </c>
-      <c r="D43" s="18" t="s">
-        <v>229</v>
+      <c r="D43" t="s">
+        <v>1107</v>
       </c>
       <c r="E43" s="18" t="s">
         <v>844</v>
@@ -4720,8 +4892,8 @@
       <c r="C44" s="18" t="s">
         <v>276</v>
       </c>
-      <c r="D44" s="18" t="s">
-        <v>229</v>
+      <c r="D44" t="s">
+        <v>1107</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>845</v>
@@ -4739,8 +4911,8 @@
       <c r="C45" s="18" t="s">
         <v>276</v>
       </c>
-      <c r="D45" s="18" t="s">
-        <v>229</v>
+      <c r="D45" t="s">
+        <v>1107</v>
       </c>
       <c r="E45" s="18" t="s">
         <v>845</v>
@@ -4758,8 +4930,8 @@
       <c r="C46" s="18" t="s">
         <v>468</v>
       </c>
-      <c r="D46" s="18" t="s">
-        <v>229</v>
+      <c r="D46" t="s">
+        <v>1107</v>
       </c>
       <c r="E46" s="18" t="s">
         <v>846</v>
@@ -4777,8 +4949,8 @@
       <c r="C47" s="18" t="s">
         <v>1029</v>
       </c>
-      <c r="D47" s="18" t="s">
-        <v>229</v>
+      <c r="D47" t="s">
+        <v>1107</v>
       </c>
       <c r="E47" s="18" t="s">
         <v>1030</v>
@@ -4796,8 +4968,8 @@
       <c r="C48" s="18" t="s">
         <v>778</v>
       </c>
-      <c r="D48" s="18" t="s">
-        <v>229</v>
+      <c r="D48" t="s">
+        <v>1107</v>
       </c>
       <c r="E48" s="18" t="s">
         <v>847</v>
@@ -4815,8 +4987,8 @@
       <c r="C49" s="18" t="s">
         <v>399</v>
       </c>
-      <c r="D49" s="18" t="s">
-        <v>229</v>
+      <c r="D49" t="s">
+        <v>1107</v>
       </c>
       <c r="E49" s="18" t="s">
         <v>858</v>
@@ -4834,8 +5006,8 @@
       <c r="C50" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="D50" s="18" t="s">
-        <v>229</v>
+      <c r="D50" t="s">
+        <v>1107</v>
       </c>
       <c r="E50" s="18" t="s">
         <v>848</v>
@@ -4853,8 +5025,8 @@
       <c r="C51" s="18" t="s">
         <v>401</v>
       </c>
-      <c r="D51" s="18" t="s">
-        <v>229</v>
+      <c r="D51" t="s">
+        <v>1107</v>
       </c>
       <c r="E51" s="18" t="s">
         <v>849</v>
@@ -4872,8 +5044,8 @@
       <c r="C52" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="D52" s="18" t="s">
-        <v>229</v>
+      <c r="D52" t="s">
+        <v>1107</v>
       </c>
       <c r="E52" s="18" t="s">
         <v>850</v>
@@ -4891,8 +5063,8 @@
       <c r="C53" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="D53" s="18" t="s">
-        <v>229</v>
+      <c r="D53" t="s">
+        <v>1107</v>
       </c>
       <c r="E53" s="18" t="s">
         <v>850</v>
@@ -4910,8 +5082,8 @@
       <c r="C54" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="D54" s="18" t="s">
-        <v>229</v>
+      <c r="D54" t="s">
+        <v>1107</v>
       </c>
       <c r="E54" s="18" t="s">
         <v>855</v>
@@ -4929,8 +5101,8 @@
       <c r="C55" s="18" t="s">
         <v>785</v>
       </c>
-      <c r="D55" s="18" t="s">
-        <v>229</v>
+      <c r="D55" t="s">
+        <v>1107</v>
       </c>
       <c r="E55" s="18" t="s">
         <v>856</v>
@@ -4948,8 +5120,8 @@
       <c r="C56" s="18" t="s">
         <v>407</v>
       </c>
-      <c r="D56" s="18" t="s">
-        <v>229</v>
+      <c r="D56" t="s">
+        <v>1107</v>
       </c>
       <c r="E56" s="18" t="s">
         <v>851</v>
@@ -4967,8 +5139,8 @@
       <c r="C57" s="18" t="s">
         <v>787</v>
       </c>
-      <c r="D57" s="18" t="s">
-        <v>229</v>
+      <c r="D57" t="s">
+        <v>1107</v>
       </c>
       <c r="E57" s="18" t="s">
         <v>857</v>
@@ -4986,8 +5158,8 @@
       <c r="C58" s="18" t="s">
         <v>409</v>
       </c>
-      <c r="D58" s="18" t="s">
-        <v>229</v>
+      <c r="D58" t="s">
+        <v>1107</v>
       </c>
       <c r="E58" s="18" t="s">
         <v>851</v>
@@ -5005,8 +5177,8 @@
       <c r="C59" s="18" t="s">
         <v>409</v>
       </c>
-      <c r="D59" s="18" t="s">
-        <v>229</v>
+      <c r="D59" t="s">
+        <v>1107</v>
       </c>
       <c r="E59" s="18" t="s">
         <v>851</v>
@@ -5024,8 +5196,8 @@
       <c r="C60" s="18" t="s">
         <v>404</v>
       </c>
-      <c r="D60" s="18" t="s">
-        <v>229</v>
+      <c r="D60" t="s">
+        <v>227</v>
       </c>
       <c r="E60" s="18" t="s">
         <v>852</v>
@@ -5043,8 +5215,8 @@
       <c r="C61" s="18" t="s">
         <v>713</v>
       </c>
-      <c r="D61" s="18" t="s">
-        <v>229</v>
+      <c r="D61" t="s">
+        <v>1107</v>
       </c>
       <c r="E61" s="18" t="s">
         <v>853</v>
@@ -5062,8 +5234,8 @@
       <c r="C62" s="18" t="s">
         <v>716</v>
       </c>
-      <c r="D62" s="18" t="s">
-        <v>229</v>
+      <c r="D62" t="s">
+        <v>227</v>
       </c>
       <c r="E62" s="18" t="s">
         <v>854</v>
@@ -5081,8 +5253,8 @@
       <c r="C63" s="18" t="s">
         <v>713</v>
       </c>
-      <c r="D63" s="18" t="s">
-        <v>229</v>
+      <c r="D63" t="s">
+        <v>227</v>
       </c>
       <c r="E63" s="18" t="s">
         <v>854</v>
@@ -5100,8 +5272,8 @@
       <c r="C64" s="18" t="s">
         <v>1053</v>
       </c>
-      <c r="D64" s="18" t="s">
-        <v>223</v>
+      <c r="D64" t="s">
+        <v>1106</v>
       </c>
       <c r="E64" s="18" t="s">
         <v>1052</v>
@@ -5119,8 +5291,8 @@
       <c r="C65" s="18" t="s">
         <v>551</v>
       </c>
-      <c r="D65" s="18" t="s">
-        <v>223</v>
+      <c r="D65" t="s">
+        <v>1106</v>
       </c>
       <c r="E65" s="18" t="s">
         <v>1050</v>
@@ -5138,8 +5310,8 @@
       <c r="C66" s="18" t="s">
         <v>551</v>
       </c>
-      <c r="D66" s="18" t="s">
-        <v>223</v>
+      <c r="D66" t="s">
+        <v>1106</v>
       </c>
       <c r="E66" s="18" t="s">
         <v>1051</v>
@@ -5157,8 +5329,8 @@
       <c r="C67" s="18" t="s">
         <v>797</v>
       </c>
-      <c r="D67" s="18" t="s">
-        <v>223</v>
+      <c r="D67" t="s">
+        <v>1106</v>
       </c>
       <c r="E67" s="18" t="s">
         <v>1050</v>
@@ -5176,8 +5348,8 @@
       <c r="C68" s="18" t="s">
         <v>797</v>
       </c>
-      <c r="D68" s="18" t="s">
-        <v>223</v>
+      <c r="D68" t="s">
+        <v>1106</v>
       </c>
       <c r="E68" s="18" t="s">
         <v>1051</v>
@@ -5195,8 +5367,8 @@
       <c r="C69" s="18" t="s">
         <v>794</v>
       </c>
-      <c r="D69" s="18" t="s">
-        <v>223</v>
+      <c r="D69" t="s">
+        <v>1106</v>
       </c>
       <c r="E69" s="18" t="s">
         <v>1049</v>
@@ -5214,8 +5386,8 @@
       <c r="C70" s="18" t="s">
         <v>607</v>
       </c>
-      <c r="D70" s="18" t="s">
-        <v>223</v>
+      <c r="D70" t="s">
+        <v>1106</v>
       </c>
       <c r="E70" s="18" t="s">
         <v>862</v>
@@ -5233,8 +5405,8 @@
       <c r="C71" s="18" t="s">
         <v>606</v>
       </c>
-      <c r="D71" s="18" t="s">
-        <v>223</v>
+      <c r="D71" t="s">
+        <v>1106</v>
       </c>
       <c r="E71" s="18" t="s">
         <v>826</v>
@@ -5252,8 +5424,8 @@
       <c r="C72" s="18" t="s">
         <v>825</v>
       </c>
-      <c r="D72" s="18" t="s">
-        <v>223</v>
+      <c r="D72" t="s">
+        <v>1106</v>
       </c>
       <c r="E72" s="18" t="s">
         <v>826</v>
@@ -5271,8 +5443,8 @@
       <c r="C73" s="18" t="s">
         <v>544</v>
       </c>
-      <c r="D73" s="18" t="s">
-        <v>223</v>
+      <c r="D73" t="s">
+        <v>1106</v>
       </c>
       <c r="E73" s="18" t="s">
         <v>792</v>
@@ -5290,8 +5462,8 @@
       <c r="C74" s="18" t="s">
         <v>552</v>
       </c>
-      <c r="D74" s="18" t="s">
-        <v>223</v>
+      <c r="D74" t="s">
+        <v>1106</v>
       </c>
       <c r="E74" s="18" t="s">
         <v>798</v>
@@ -5309,8 +5481,8 @@
       <c r="C75" s="18" t="s">
         <v>554</v>
       </c>
-      <c r="D75" s="18" t="s">
-        <v>223</v>
+      <c r="D75" t="s">
+        <v>1106</v>
       </c>
       <c r="E75" s="18" t="s">
         <v>863</v>
@@ -5328,8 +5500,8 @@
       <c r="C76" s="18" t="s">
         <v>800</v>
       </c>
-      <c r="D76" s="18" t="s">
-        <v>223</v>
+      <c r="D76" t="s">
+        <v>1106</v>
       </c>
       <c r="E76" s="18" t="s">
         <v>801</v>
@@ -5347,8 +5519,8 @@
       <c r="C77" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D77" s="18" t="s">
-        <v>223</v>
+      <c r="D77" t="s">
+        <v>1106</v>
       </c>
       <c r="E77" s="18" t="s">
         <v>802</v>
@@ -5366,8 +5538,8 @@
       <c r="C78" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D78" s="18" t="s">
-        <v>223</v>
+      <c r="D78" t="s">
+        <v>1106</v>
       </c>
       <c r="E78" s="18" t="s">
         <v>803</v>
@@ -5385,8 +5557,8 @@
       <c r="C79" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D79" s="18" t="s">
-        <v>223</v>
+      <c r="D79" t="s">
+        <v>1106</v>
       </c>
       <c r="E79" s="18" t="s">
         <v>804</v>
@@ -5404,8 +5576,8 @@
       <c r="C80" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D80" s="18" t="s">
-        <v>223</v>
+      <c r="D80" t="s">
+        <v>1106</v>
       </c>
       <c r="E80" s="18" t="s">
         <v>805</v>
@@ -5423,8 +5595,8 @@
       <c r="C81" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D81" s="18" t="s">
-        <v>223</v>
+      <c r="D81" t="s">
+        <v>1106</v>
       </c>
       <c r="E81" s="18" t="s">
         <v>806</v>
@@ -5442,8 +5614,8 @@
       <c r="C82" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D82" s="18" t="s">
-        <v>223</v>
+      <c r="D82" t="s">
+        <v>1106</v>
       </c>
       <c r="E82" s="18" t="s">
         <v>807</v>
@@ -5461,8 +5633,8 @@
       <c r="C83" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D83" s="18" t="s">
-        <v>223</v>
+      <c r="D83" t="s">
+        <v>1106</v>
       </c>
       <c r="E83" s="18" t="s">
         <v>808</v>
@@ -5480,8 +5652,8 @@
       <c r="C84" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D84" s="18" t="s">
-        <v>223</v>
+      <c r="D84" t="s">
+        <v>1106</v>
       </c>
       <c r="E84" s="18" t="s">
         <v>809</v>
@@ -5499,8 +5671,8 @@
       <c r="C85" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D85" s="18" t="s">
-        <v>223</v>
+      <c r="D85" t="s">
+        <v>1106</v>
       </c>
       <c r="E85" s="18" t="s">
         <v>810</v>
@@ -5518,8 +5690,8 @@
       <c r="C86" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D86" s="18" t="s">
-        <v>223</v>
+      <c r="D86" t="s">
+        <v>1106</v>
       </c>
       <c r="E86" s="18" t="s">
         <v>811</v>
@@ -5537,8 +5709,8 @@
       <c r="C87" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D87" s="18" t="s">
-        <v>223</v>
+      <c r="D87" t="s">
+        <v>1106</v>
       </c>
       <c r="E87" s="18" t="s">
         <v>812</v>
@@ -5556,8 +5728,8 @@
       <c r="C88" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D88" s="18" t="s">
-        <v>223</v>
+      <c r="D88" t="s">
+        <v>1106</v>
       </c>
       <c r="E88" s="18" t="s">
         <v>813</v>
@@ -5575,8 +5747,8 @@
       <c r="C89" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D89" s="18" t="s">
-        <v>223</v>
+      <c r="D89" t="s">
+        <v>1106</v>
       </c>
       <c r="E89" s="18" t="s">
         <v>814</v>
@@ -5594,8 +5766,8 @@
       <c r="C90" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D90" s="18" t="s">
-        <v>223</v>
+      <c r="D90" t="s">
+        <v>1106</v>
       </c>
       <c r="E90" s="18" t="s">
         <v>815</v>
@@ -5613,8 +5785,8 @@
       <c r="C91" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D91" s="18" t="s">
-        <v>223</v>
+      <c r="D91" t="s">
+        <v>1106</v>
       </c>
       <c r="E91" s="18" t="s">
         <v>816</v>
@@ -5632,8 +5804,8 @@
       <c r="C92" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D92" s="18" t="s">
-        <v>223</v>
+      <c r="D92" t="s">
+        <v>1106</v>
       </c>
       <c r="E92" s="18" t="s">
         <v>817</v>
@@ -5651,8 +5823,8 @@
       <c r="C93" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D93" s="18" t="s">
-        <v>223</v>
+      <c r="D93" t="s">
+        <v>1106</v>
       </c>
       <c r="E93" s="18" t="s">
         <v>818</v>
@@ -5670,8 +5842,8 @@
       <c r="C94" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D94" s="18" t="s">
-        <v>223</v>
+      <c r="D94" t="s">
+        <v>1106</v>
       </c>
       <c r="E94" s="18" t="s">
         <v>819</v>
@@ -5689,8 +5861,8 @@
       <c r="C95" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D95" s="18" t="s">
-        <v>223</v>
+      <c r="D95" t="s">
+        <v>1106</v>
       </c>
       <c r="E95" s="18" t="s">
         <v>820</v>
@@ -5708,8 +5880,8 @@
       <c r="C96" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D96" s="18" t="s">
-        <v>223</v>
+      <c r="D96" t="s">
+        <v>1106</v>
       </c>
       <c r="E96" s="18" t="s">
         <v>821</v>
@@ -5727,8 +5899,8 @@
       <c r="C97" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D97" s="18" t="s">
-        <v>223</v>
+      <c r="D97" t="s">
+        <v>1106</v>
       </c>
       <c r="E97" s="18" t="s">
         <v>822</v>
@@ -5746,8 +5918,8 @@
       <c r="C98" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D98" s="18" t="s">
-        <v>223</v>
+      <c r="D98" t="s">
+        <v>1106</v>
       </c>
       <c r="E98" s="18" t="s">
         <v>823</v>
@@ -5765,8 +5937,8 @@
       <c r="C99" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="D99" s="18" t="s">
-        <v>223</v>
+      <c r="D99" t="s">
+        <v>1106</v>
       </c>
       <c r="E99" s="18" t="s">
         <v>824</v>
@@ -5784,8 +5956,8 @@
       <c r="C100" s="18" t="s">
         <v>864</v>
       </c>
-      <c r="D100" s="18" t="s">
-        <v>223</v>
+      <c r="D100" t="s">
+        <v>1106</v>
       </c>
       <c r="E100" s="18" t="s">
         <v>899</v>
@@ -5803,8 +5975,8 @@
       <c r="C101" s="18" t="s">
         <v>894</v>
       </c>
-      <c r="D101" s="18" t="s">
-        <v>223</v>
+      <c r="D101" t="s">
+        <v>1106</v>
       </c>
       <c r="E101" s="18" t="s">
         <v>895</v>
@@ -5822,8 +5994,8 @@
       <c r="C102" s="18" t="s">
         <v>600</v>
       </c>
-      <c r="D102" s="18" t="s">
-        <v>223</v>
+      <c r="D102" t="s">
+        <v>1106</v>
       </c>
       <c r="E102" s="18" t="s">
         <v>860</v>
@@ -5841,8 +6013,8 @@
       <c r="C103" s="18" t="s">
         <v>765</v>
       </c>
-      <c r="D103" s="18" t="s">
-        <v>223</v>
+      <c r="D103" t="s">
+        <v>1106</v>
       </c>
       <c r="E103" s="18" t="s">
         <v>1012</v>
@@ -5860,8 +6032,8 @@
       <c r="C104" s="18" t="s">
         <v>602</v>
       </c>
-      <c r="D104" s="18" t="s">
-        <v>223</v>
+      <c r="D104" t="s">
+        <v>1106</v>
       </c>
       <c r="E104" s="18" t="s">
         <v>861</v>
@@ -5879,8 +6051,8 @@
       <c r="C105" s="18" t="s">
         <v>598</v>
       </c>
-      <c r="D105" s="18" t="s">
-        <v>223</v>
+      <c r="D105" t="s">
+        <v>1106</v>
       </c>
       <c r="E105" s="18" t="s">
         <v>859</v>
@@ -5898,8 +6070,8 @@
       <c r="C106" s="18" t="s">
         <v>1014</v>
       </c>
-      <c r="D106" s="18" t="s">
-        <v>223</v>
+      <c r="D106" t="s">
+        <v>1106</v>
       </c>
       <c r="E106" s="18" t="s">
         <v>1015</v>
@@ -5917,8 +6089,8 @@
       <c r="C107" s="18" t="s">
         <v>1014</v>
       </c>
-      <c r="D107" s="18" t="s">
-        <v>223</v>
+      <c r="D107" t="s">
+        <v>1106</v>
       </c>
       <c r="E107" s="18" t="s">
         <v>1015</v>
@@ -5936,8 +6108,8 @@
       <c r="C108" s="18" t="s">
         <v>760</v>
       </c>
-      <c r="D108" s="18" t="s">
-        <v>223</v>
+      <c r="D108" t="s">
+        <v>1106</v>
       </c>
       <c r="E108" s="18" t="s">
         <v>788</v>
@@ -5955,8 +6127,8 @@
       <c r="C109" s="18" t="s">
         <v>760</v>
       </c>
-      <c r="D109" s="18" t="s">
-        <v>223</v>
+      <c r="D109" t="s">
+        <v>1106</v>
       </c>
       <c r="E109" s="18" t="s">
         <v>788</v>
@@ -5974,8 +6146,8 @@
       <c r="C110" s="18" t="s">
         <v>867</v>
       </c>
-      <c r="D110" s="18" t="s">
-        <v>223</v>
+      <c r="D110" t="s">
+        <v>1106</v>
       </c>
       <c r="E110" s="18" t="s">
         <v>868</v>
@@ -5993,8 +6165,8 @@
       <c r="C111" s="18" t="s">
         <v>867</v>
       </c>
-      <c r="D111" s="18" t="s">
-        <v>223</v>
+      <c r="D111" t="s">
+        <v>1106</v>
       </c>
       <c r="E111" s="18" t="s">
         <v>868</v>
@@ -6012,8 +6184,8 @@
       <c r="C112" s="18" t="s">
         <v>871</v>
       </c>
-      <c r="D112" s="18" t="s">
-        <v>223</v>
+      <c r="D112" t="s">
+        <v>1106</v>
       </c>
       <c r="E112" s="18" t="s">
         <v>872</v>
@@ -6031,8 +6203,8 @@
       <c r="C113" s="18" t="s">
         <v>871</v>
       </c>
-      <c r="D113" s="18" t="s">
-        <v>223</v>
+      <c r="D113" t="s">
+        <v>1106</v>
       </c>
       <c r="E113" s="18" t="s">
         <v>872</v>
@@ -6050,8 +6222,8 @@
       <c r="C114" s="18" t="s">
         <v>1048</v>
       </c>
-      <c r="D114" s="18" t="s">
-        <v>223</v>
+      <c r="D114" t="s">
+        <v>1106</v>
       </c>
       <c r="E114" s="18" t="s">
         <v>1045</v>
@@ -6069,8 +6241,8 @@
       <c r="C115" s="18" t="s">
         <v>1048</v>
       </c>
-      <c r="D115" s="18" t="s">
-        <v>223</v>
+      <c r="D115" t="s">
+        <v>1106</v>
       </c>
       <c r="E115" s="18" t="s">
         <v>1045</v>
@@ -6088,8 +6260,8 @@
       <c r="C116" s="18" t="s">
         <v>763</v>
       </c>
-      <c r="D116" s="18" t="s">
-        <v>223</v>
+      <c r="D116" t="s">
+        <v>1106</v>
       </c>
       <c r="E116" s="18" t="s">
         <v>790</v>
@@ -6107,8 +6279,8 @@
       <c r="C117" s="18" t="s">
         <v>763</v>
       </c>
-      <c r="D117" s="18" t="s">
-        <v>223</v>
+      <c r="D117" t="s">
+        <v>1106</v>
       </c>
       <c r="E117" s="18" t="s">
         <v>790</v>
@@ -6126,8 +6298,8 @@
       <c r="C118" s="18" t="s">
         <v>758</v>
       </c>
-      <c r="D118" s="18" t="s">
-        <v>223</v>
+      <c r="D118" t="s">
+        <v>1106</v>
       </c>
       <c r="E118" s="18" t="s">
         <v>1011</v>
@@ -6145,8 +6317,8 @@
       <c r="C119" s="18" t="s">
         <v>764</v>
       </c>
-      <c r="D119" s="18" t="s">
-        <v>223</v>
+      <c r="D119" t="s">
+        <v>1106</v>
       </c>
       <c r="E119" s="18" t="s">
         <v>791</v>
@@ -6164,8 +6336,8 @@
       <c r="C120" s="18" t="s">
         <v>764</v>
       </c>
-      <c r="D120" s="18" t="s">
-        <v>223</v>
+      <c r="D120" t="s">
+        <v>1106</v>
       </c>
       <c r="E120" s="18" t="s">
         <v>791</v>
@@ -6183,8 +6355,8 @@
       <c r="C121" s="18" t="s">
         <v>762</v>
       </c>
-      <c r="D121" s="18" t="s">
-        <v>223</v>
+      <c r="D121" t="s">
+        <v>1106</v>
       </c>
       <c r="E121" s="18" t="s">
         <v>789</v>
@@ -6202,8 +6374,8 @@
       <c r="C122" s="18" t="s">
         <v>762</v>
       </c>
-      <c r="D122" s="18" t="s">
-        <v>223</v>
+      <c r="D122" t="s">
+        <v>1106</v>
       </c>
       <c r="E122" s="18" t="s">
         <v>789</v>
@@ -6221,8 +6393,8 @@
       <c r="C123" s="18" t="s">
         <v>761</v>
       </c>
-      <c r="D123" s="18" t="s">
-        <v>223</v>
+      <c r="D123" t="s">
+        <v>1106</v>
       </c>
       <c r="E123" s="18" t="s">
         <v>1028</v>
@@ -6240,8 +6412,8 @@
       <c r="C124" s="18" t="s">
         <v>761</v>
       </c>
-      <c r="D124" s="18" t="s">
-        <v>223</v>
+      <c r="D124" t="s">
+        <v>1106</v>
       </c>
       <c r="E124" s="18" t="s">
         <v>1028</v>
@@ -6259,8 +6431,8 @@
       <c r="C125" s="18" t="s">
         <v>1102</v>
       </c>
-      <c r="D125" s="18" t="s">
-        <v>223</v>
+      <c r="D125" t="s">
+        <v>1106</v>
       </c>
       <c r="E125" s="18" t="s">
         <v>1104</v>
@@ -6278,8 +6450,8 @@
       <c r="C126" s="18" t="s">
         <v>1102</v>
       </c>
-      <c r="D126" s="18" t="s">
-        <v>223</v>
+      <c r="D126" t="s">
+        <v>1106</v>
       </c>
       <c r="E126" s="18" t="s">
         <v>1104</v>
@@ -6297,8 +6469,8 @@
       <c r="C127" s="18" t="s">
         <v>873</v>
       </c>
-      <c r="D127" s="18" t="s">
-        <v>223</v>
+      <c r="D127" t="s">
+        <v>1106</v>
       </c>
       <c r="E127" s="18" t="s">
         <v>875</v>
@@ -6316,8 +6488,8 @@
       <c r="C128" s="18" t="s">
         <v>873</v>
       </c>
-      <c r="D128" s="18" t="s">
-        <v>223</v>
+      <c r="D128" t="s">
+        <v>1106</v>
       </c>
       <c r="E128" s="18" t="s">
         <v>875</v>
@@ -6335,8 +6507,8 @@
       <c r="C129" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="D129" s="18" t="s">
-        <v>223</v>
+      <c r="D129" t="s">
+        <v>1106</v>
       </c>
       <c r="E129" s="18" t="s">
         <v>876</v>
@@ -6354,8 +6526,8 @@
       <c r="C130" s="18" t="s">
         <v>878</v>
       </c>
-      <c r="D130" s="18" t="s">
-        <v>223</v>
+      <c r="D130" t="s">
+        <v>1106</v>
       </c>
       <c r="E130" s="18" t="s">
         <v>887</v>
@@ -6373,8 +6545,8 @@
       <c r="C131" s="18" t="s">
         <v>877</v>
       </c>
-      <c r="D131" s="18" t="s">
-        <v>223</v>
+      <c r="D131" t="s">
+        <v>1106</v>
       </c>
       <c r="E131" s="18" t="s">
         <v>888</v>
@@ -6392,8 +6564,8 @@
       <c r="C132" s="18" t="s">
         <v>880</v>
       </c>
-      <c r="D132" s="18" t="s">
-        <v>223</v>
+      <c r="D132" t="s">
+        <v>1106</v>
       </c>
       <c r="E132" s="18" t="s">
         <v>889</v>
@@ -6411,8 +6583,8 @@
       <c r="C133" s="18" t="s">
         <v>882</v>
       </c>
-      <c r="D133" s="18" t="s">
-        <v>223</v>
+      <c r="D133" t="s">
+        <v>1106</v>
       </c>
       <c r="E133" s="18" t="s">
         <v>890</v>
@@ -6430,8 +6602,8 @@
       <c r="C134" s="18" t="s">
         <v>884</v>
       </c>
-      <c r="D134" s="18" t="s">
-        <v>223</v>
+      <c r="D134" t="s">
+        <v>1106</v>
       </c>
       <c r="E134" s="18" t="s">
         <v>891</v>
@@ -6449,8 +6621,8 @@
       <c r="C135" s="18" t="s">
         <v>885</v>
       </c>
-      <c r="D135" s="18" t="s">
-        <v>223</v>
+      <c r="D135" t="s">
+        <v>1106</v>
       </c>
       <c r="E135" s="18" t="s">
         <v>892</v>
@@ -6468,8 +6640,8 @@
       <c r="C136" s="18" t="s">
         <v>886</v>
       </c>
-      <c r="D136" s="18" t="s">
-        <v>223</v>
+      <c r="D136" t="s">
+        <v>1106</v>
       </c>
       <c r="E136" s="18" t="s">
         <v>893</v>
@@ -6487,8 +6659,8 @@
       <c r="C137" s="18" t="s">
         <v>617</v>
       </c>
-      <c r="D137" s="18" t="s">
-        <v>223</v>
+      <c r="D137" t="s">
+        <v>1108</v>
       </c>
       <c r="E137" s="18" t="s">
         <v>898</v>
@@ -6506,8 +6678,8 @@
       <c r="C138" s="18" t="s">
         <v>687</v>
       </c>
-      <c r="D138" s="18" t="s">
-        <v>223</v>
+      <c r="D138" t="s">
+        <v>1108</v>
       </c>
       <c r="E138" s="18" t="s">
         <v>897</v>
@@ -6525,8 +6697,8 @@
       <c r="C139" s="18" t="s">
         <v>896</v>
       </c>
-      <c r="D139" s="18" t="s">
-        <v>223</v>
+      <c r="D139" t="s">
+        <v>1108</v>
       </c>
       <c r="E139" s="18" t="s">
         <v>900</v>
@@ -6545,7 +6717,7 @@
         <v>1055</v>
       </c>
       <c r="D140" s="18" t="s">
-        <v>223</v>
+        <v>1107</v>
       </c>
       <c r="E140" s="18" t="s">
         <v>1076</v>
@@ -6564,7 +6736,7 @@
         <v>1056</v>
       </c>
       <c r="D141" s="18" t="s">
-        <v>223</v>
+        <v>1107</v>
       </c>
       <c r="E141" s="18" t="s">
         <v>1086</v>
@@ -6583,7 +6755,7 @@
         <v>1059</v>
       </c>
       <c r="D142" s="18" t="s">
-        <v>223</v>
+        <v>1107</v>
       </c>
       <c r="E142" s="18" t="s">
         <v>1077</v>
@@ -6602,7 +6774,7 @@
         <v>1061</v>
       </c>
       <c r="D143" s="18" t="s">
-        <v>223</v>
+        <v>1107</v>
       </c>
       <c r="E143" s="18" t="s">
         <v>1078</v>
@@ -6621,7 +6793,7 @@
         <v>1062</v>
       </c>
       <c r="D144" s="18" t="s">
-        <v>223</v>
+        <v>1107</v>
       </c>
       <c r="E144" s="18" t="s">
         <v>1079</v>
@@ -6640,7 +6812,7 @@
         <v>1064</v>
       </c>
       <c r="D145" s="18" t="s">
-        <v>223</v>
+        <v>1107</v>
       </c>
       <c r="E145" s="18" t="s">
         <v>1080</v>
@@ -6659,7 +6831,7 @@
         <v>1066</v>
       </c>
       <c r="D146" s="18" t="s">
-        <v>223</v>
+        <v>1107</v>
       </c>
       <c r="E146" s="18" t="s">
         <v>1081</v>
@@ -6678,7 +6850,7 @@
         <v>1068</v>
       </c>
       <c r="D147" s="18" t="s">
-        <v>223</v>
+        <v>1107</v>
       </c>
       <c r="E147" s="18" t="s">
         <v>1082</v>
@@ -6697,7 +6869,7 @@
         <v>1070</v>
       </c>
       <c r="D148" s="18" t="s">
-        <v>223</v>
+        <v>1107</v>
       </c>
       <c r="E148" s="18" t="s">
         <v>1083</v>
@@ -6716,7 +6888,7 @@
         <v>1072</v>
       </c>
       <c r="D149" s="18" t="s">
-        <v>223</v>
+        <v>1107</v>
       </c>
       <c r="E149" s="18" t="s">
         <v>1084</v>
@@ -6735,7 +6907,7 @@
         <v>1074</v>
       </c>
       <c r="D150" s="18" t="s">
-        <v>223</v>
+        <v>1107</v>
       </c>
       <c r="E150" s="18" t="s">
         <v>1085</v>
@@ -6753,8 +6925,8 @@
       <c r="C151" s="18" t="s">
         <v>752</v>
       </c>
-      <c r="D151" s="18" t="s">
-        <v>223</v>
+      <c r="D151" t="s">
+        <v>1106</v>
       </c>
       <c r="E151" s="18" t="s">
         <v>768</v>
@@ -6772,8 +6944,8 @@
       <c r="C152" s="18" t="s">
         <v>750</v>
       </c>
-      <c r="D152" s="18" t="s">
-        <v>223</v>
+      <c r="D152" t="s">
+        <v>1106</v>
       </c>
       <c r="E152" s="18" t="s">
         <v>769</v>
@@ -6791,8 +6963,8 @@
       <c r="C153" s="18" t="s">
         <v>751</v>
       </c>
-      <c r="D153" s="18" t="s">
-        <v>223</v>
+      <c r="D153" t="s">
+        <v>1106</v>
       </c>
       <c r="E153" s="18" t="s">
         <v>767</v>
@@ -6805,16 +6977,16 @@
         <v>212</v>
       </c>
       <c r="B154" s="18" t="s">
-        <v>688</v>
+        <v>1126</v>
       </c>
       <c r="C154" s="18" t="s">
-        <v>689</v>
-      </c>
-      <c r="D154" s="18" t="s">
-        <v>223</v>
+        <v>1127</v>
+      </c>
+      <c r="D154" t="s">
+        <v>1106</v>
       </c>
       <c r="E154" s="18" t="s">
-        <v>907</v>
+        <v>1129</v>
       </c>
       <c r="F154" s="16"/>
       <c r="G154" s="16"/>
@@ -6824,16 +6996,16 @@
         <v>212</v>
       </c>
       <c r="B155" s="18" t="s">
-        <v>690</v>
+        <v>1136</v>
       </c>
       <c r="C155" s="18" t="s">
-        <v>906</v>
-      </c>
-      <c r="D155" s="18" t="s">
-        <v>223</v>
+        <v>1127</v>
+      </c>
+      <c r="D155" t="s">
+        <v>1106</v>
       </c>
       <c r="E155" s="18" t="s">
-        <v>908</v>
+        <v>1129</v>
       </c>
       <c r="F155" s="16"/>
       <c r="G155" s="16"/>
@@ -6843,16 +7015,16 @@
         <v>212</v>
       </c>
       <c r="B156" s="18" t="s">
-        <v>692</v>
+        <v>1125</v>
       </c>
       <c r="C156" s="18" t="s">
-        <v>693</v>
-      </c>
-      <c r="D156" s="18" t="s">
-        <v>223</v>
+        <v>1127</v>
+      </c>
+      <c r="D156" t="s">
+        <v>1106</v>
       </c>
       <c r="E156" s="18" t="s">
-        <v>909</v>
+        <v>1129</v>
       </c>
       <c r="F156" s="16"/>
       <c r="G156" s="16"/>
@@ -6862,16 +7034,16 @@
         <v>212</v>
       </c>
       <c r="B157" s="18" t="s">
-        <v>694</v>
+        <v>1128</v>
       </c>
       <c r="C157" s="18" t="s">
-        <v>737</v>
-      </c>
-      <c r="D157" s="18" t="s">
-        <v>223</v>
+        <v>1131</v>
+      </c>
+      <c r="D157" t="s">
+        <v>1106</v>
       </c>
       <c r="E157" s="18" t="s">
-        <v>901</v>
+        <v>1130</v>
       </c>
       <c r="F157" s="16"/>
       <c r="G157" s="16"/>
@@ -6881,16 +7053,16 @@
         <v>212</v>
       </c>
       <c r="B158" s="18" t="s">
-        <v>696</v>
+        <v>1132</v>
       </c>
       <c r="C158" s="18" t="s">
-        <v>738</v>
-      </c>
-      <c r="D158" s="18" t="s">
-        <v>223</v>
+        <v>1133</v>
+      </c>
+      <c r="D158" t="s">
+        <v>1106</v>
       </c>
       <c r="E158" s="18" t="s">
-        <v>910</v>
+        <v>1130</v>
       </c>
       <c r="F158" s="16"/>
       <c r="G158" s="16"/>
@@ -6900,16 +7072,16 @@
         <v>212</v>
       </c>
       <c r="B159" s="18" t="s">
-        <v>698</v>
+        <v>1134</v>
       </c>
       <c r="C159" s="18" t="s">
-        <v>699</v>
-      </c>
-      <c r="D159" s="18" t="s">
-        <v>223</v>
+        <v>1135</v>
+      </c>
+      <c r="D159" t="s">
+        <v>1106</v>
       </c>
       <c r="E159" s="18" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="F159" s="16"/>
       <c r="G159" s="16"/>
@@ -6919,16 +7091,16 @@
         <v>212</v>
       </c>
       <c r="B160" s="18" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="C160" s="18" t="s">
-        <v>902</v>
-      </c>
-      <c r="D160" s="18" t="s">
-        <v>223</v>
+        <v>689</v>
+      </c>
+      <c r="D160" t="s">
+        <v>1106</v>
       </c>
       <c r="E160" s="18" t="s">
-        <v>920</v>
+        <v>907</v>
       </c>
       <c r="F160" s="16"/>
       <c r="G160" s="16"/>
@@ -6938,16 +7110,16 @@
         <v>212</v>
       </c>
       <c r="B161" s="18" t="s">
-        <v>916</v>
+        <v>690</v>
       </c>
       <c r="C161" s="18" t="s">
-        <v>917</v>
-      </c>
-      <c r="D161" s="18" t="s">
-        <v>223</v>
+        <v>906</v>
+      </c>
+      <c r="D161" t="s">
+        <v>1106</v>
       </c>
       <c r="E161" s="18" t="s">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="F161" s="16"/>
       <c r="G161" s="16"/>
@@ -6957,33 +7129,35 @@
         <v>212</v>
       </c>
       <c r="B162" s="18" t="s">
-        <v>918</v>
+        <v>692</v>
       </c>
       <c r="C162" s="18" t="s">
-        <v>919</v>
-      </c>
-      <c r="D162" s="18" t="s">
-        <v>223</v>
+        <v>693</v>
+      </c>
+      <c r="D162" t="s">
+        <v>1106</v>
       </c>
       <c r="E162" s="18" t="s">
-        <v>920</v>
-      </c>
+        <v>909</v>
+      </c>
+      <c r="F162" s="16"/>
+      <c r="G162" s="16"/>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B163" s="18" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="C163" s="18" t="s">
-        <v>904</v>
-      </c>
-      <c r="D163" s="18" t="s">
-        <v>223</v>
+        <v>737</v>
+      </c>
+      <c r="D163" t="s">
+        <v>1106</v>
       </c>
       <c r="E163" s="18" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="F163" s="16"/>
       <c r="G163" s="16"/>
@@ -6993,16 +7167,16 @@
         <v>212</v>
       </c>
       <c r="B164" s="18" t="s">
-        <v>903</v>
+        <v>696</v>
       </c>
       <c r="C164" s="18" t="s">
-        <v>904</v>
-      </c>
-      <c r="D164" s="18" t="s">
-        <v>223</v>
+        <v>738</v>
+      </c>
+      <c r="D164" t="s">
+        <v>1106</v>
       </c>
       <c r="E164" s="18" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="F164" s="16"/>
       <c r="G164" s="16"/>
@@ -7012,16 +7186,16 @@
         <v>212</v>
       </c>
       <c r="B165" s="18" t="s">
-        <v>912</v>
+        <v>698</v>
       </c>
       <c r="C165" s="18" t="s">
-        <v>913</v>
-      </c>
-      <c r="D165" s="18" t="s">
-        <v>223</v>
+        <v>699</v>
+      </c>
+      <c r="D165" t="s">
+        <v>1106</v>
       </c>
       <c r="E165" s="18" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="F165" s="16"/>
       <c r="G165" s="16"/>
@@ -7031,16 +7205,16 @@
         <v>212</v>
       </c>
       <c r="B166" s="18" t="s">
-        <v>914</v>
+        <v>700</v>
       </c>
       <c r="C166" s="18" t="s">
-        <v>913</v>
-      </c>
-      <c r="D166" s="18" t="s">
-        <v>223</v>
+        <v>902</v>
+      </c>
+      <c r="D166" t="s">
+        <v>1106</v>
       </c>
       <c r="E166" s="18" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="F166" s="16"/>
       <c r="G166" s="16"/>
@@ -7050,16 +7224,16 @@
         <v>212</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>723</v>
+        <v>916</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>729</v>
-      </c>
-      <c r="D167" s="18" t="s">
-        <v>223</v>
+        <v>917</v>
+      </c>
+      <c r="D167" t="s">
+        <v>1106</v>
       </c>
       <c r="E167" s="18" t="s">
-        <v>747</v>
+        <v>920</v>
       </c>
       <c r="F167" s="16"/>
       <c r="G167" s="16"/>
@@ -7069,35 +7243,33 @@
         <v>212</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>724</v>
+        <v>918</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>730</v>
-      </c>
-      <c r="D168" s="18" t="s">
-        <v>223</v>
+        <v>919</v>
+      </c>
+      <c r="D168" t="s">
+        <v>1106</v>
       </c>
       <c r="E168" s="18" t="s">
-        <v>748</v>
-      </c>
-      <c r="F168" s="16"/>
-      <c r="G168" s="16"/>
+        <v>920</v>
+      </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>725</v>
+        <v>702</v>
       </c>
       <c r="C169" s="18" t="s">
-        <v>731</v>
-      </c>
-      <c r="D169" s="18" t="s">
-        <v>223</v>
+        <v>904</v>
+      </c>
+      <c r="D169" t="s">
+        <v>1106</v>
       </c>
       <c r="E169" s="18" t="s">
-        <v>749</v>
+        <v>905</v>
       </c>
       <c r="F169" s="16"/>
       <c r="G169" s="16"/>
@@ -7107,62 +7279,54 @@
         <v>212</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>735</v>
+        <v>903</v>
       </c>
       <c r="C170" s="18" t="s">
-        <v>736</v>
-      </c>
-      <c r="D170" s="18" t="s">
-        <v>223</v>
+        <v>904</v>
+      </c>
+      <c r="D170" t="s">
+        <v>1106</v>
       </c>
       <c r="E170" s="18" t="s">
-        <v>925</v>
-      </c>
-      <c r="F170" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G170" s="16" t="s">
-        <v>743</v>
-      </c>
+        <v>905</v>
+      </c>
+      <c r="F170" s="16"/>
+      <c r="G170" s="16"/>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>746</v>
+        <v>912</v>
       </c>
       <c r="C171" s="18" t="s">
-        <v>736</v>
-      </c>
-      <c r="D171" s="18" t="s">
-        <v>223</v>
+        <v>913</v>
+      </c>
+      <c r="D171" t="s">
+        <v>1106</v>
       </c>
       <c r="E171" s="18" t="s">
-        <v>925</v>
-      </c>
-      <c r="F171" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G171" s="16" t="s">
-        <v>743</v>
-      </c>
+        <v>915</v>
+      </c>
+      <c r="F171" s="16"/>
+      <c r="G171" s="16"/>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B172" s="18" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="C172" s="18" t="s">
-        <v>922</v>
-      </c>
-      <c r="D172" s="18" t="s">
-        <v>223</v>
+        <v>913</v>
+      </c>
+      <c r="D172" t="s">
+        <v>1106</v>
       </c>
       <c r="E172" s="18" t="s">
-        <v>926</v>
+        <v>915</v>
       </c>
       <c r="F172" s="16"/>
       <c r="G172" s="16"/>
@@ -7172,16 +7336,16 @@
         <v>212</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>923</v>
+        <v>723</v>
       </c>
       <c r="C173" s="18" t="s">
-        <v>922</v>
-      </c>
-      <c r="D173" s="18" t="s">
-        <v>223</v>
+        <v>729</v>
+      </c>
+      <c r="D173" t="s">
+        <v>1106</v>
       </c>
       <c r="E173" s="18" t="s">
-        <v>926</v>
+        <v>747</v>
       </c>
       <c r="F173" s="16"/>
       <c r="G173" s="16"/>
@@ -7191,16 +7355,16 @@
         <v>212</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>924</v>
+        <v>724</v>
       </c>
       <c r="C174" s="18" t="s">
-        <v>922</v>
-      </c>
-      <c r="D174" s="18" t="s">
-        <v>223</v>
+        <v>730</v>
+      </c>
+      <c r="D174" t="s">
+        <v>1106</v>
       </c>
       <c r="E174" s="18" t="s">
-        <v>926</v>
+        <v>748</v>
       </c>
       <c r="F174" s="16"/>
       <c r="G174" s="16"/>
@@ -7210,16 +7374,16 @@
         <v>212</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>928</v>
+        <v>725</v>
       </c>
       <c r="C175" s="18" t="s">
-        <v>927</v>
-      </c>
-      <c r="D175" s="18" t="s">
-        <v>223</v>
+        <v>731</v>
+      </c>
+      <c r="D175" t="s">
+        <v>1106</v>
       </c>
       <c r="E175" s="18" t="s">
-        <v>929</v>
+        <v>749</v>
       </c>
       <c r="F175" s="16"/>
       <c r="G175" s="16"/>
@@ -7229,54 +7393,62 @@
         <v>212</v>
       </c>
       <c r="B176" s="18" t="s">
-        <v>931</v>
+        <v>735</v>
       </c>
       <c r="C176" s="18" t="s">
-        <v>930</v>
-      </c>
-      <c r="D176" s="18" t="s">
-        <v>223</v>
+        <v>736</v>
+      </c>
+      <c r="D176" t="s">
+        <v>1106</v>
       </c>
       <c r="E176" s="18" t="s">
-        <v>934</v>
-      </c>
-      <c r="F176" s="16"/>
-      <c r="G176" s="16"/>
+        <v>925</v>
+      </c>
+      <c r="F176" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G176" s="16" t="s">
+        <v>743</v>
+      </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B177" s="18" t="s">
-        <v>933</v>
+        <v>746</v>
       </c>
       <c r="C177" s="18" t="s">
-        <v>932</v>
-      </c>
-      <c r="D177" s="18" t="s">
-        <v>223</v>
+        <v>736</v>
+      </c>
+      <c r="D177" t="s">
+        <v>1106</v>
       </c>
       <c r="E177" s="18" t="s">
-        <v>937</v>
-      </c>
-      <c r="F177" s="16"/>
-      <c r="G177" s="16"/>
+        <v>925</v>
+      </c>
+      <c r="F177" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G177" s="16" t="s">
+        <v>743</v>
+      </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>936</v>
+        <v>921</v>
       </c>
       <c r="C178" s="18" t="s">
-        <v>935</v>
-      </c>
-      <c r="D178" s="18" t="s">
-        <v>223</v>
+        <v>922</v>
+      </c>
+      <c r="D178" t="s">
+        <v>1106</v>
       </c>
       <c r="E178" s="18" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
       <c r="F178" s="16"/>
       <c r="G178" s="16"/>
@@ -7286,16 +7458,16 @@
         <v>212</v>
       </c>
       <c r="B179" s="18" t="s">
-        <v>939</v>
+        <v>923</v>
       </c>
       <c r="C179" s="18" t="s">
-        <v>941</v>
-      </c>
-      <c r="D179" s="18" t="s">
-        <v>223</v>
+        <v>922</v>
+      </c>
+      <c r="D179" t="s">
+        <v>1106</v>
       </c>
       <c r="E179" s="18" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
       <c r="F179" s="16"/>
       <c r="G179" s="16"/>
@@ -7305,16 +7477,16 @@
         <v>212</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>940</v>
+        <v>924</v>
       </c>
       <c r="C180" s="18" t="s">
-        <v>942</v>
-      </c>
-      <c r="D180" s="18" t="s">
-        <v>223</v>
+        <v>922</v>
+      </c>
+      <c r="D180" t="s">
+        <v>1106</v>
       </c>
       <c r="E180" s="18" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
       <c r="F180" s="16"/>
       <c r="G180" s="16"/>
@@ -7324,16 +7496,16 @@
         <v>212</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>943</v>
+        <v>928</v>
       </c>
       <c r="C181" s="18" t="s">
-        <v>944</v>
-      </c>
-      <c r="D181" s="18" t="s">
-        <v>223</v>
+        <v>927</v>
+      </c>
+      <c r="D181" t="s">
+        <v>1106</v>
       </c>
       <c r="E181" s="18" t="s">
-        <v>945</v>
+        <v>929</v>
       </c>
       <c r="F181" s="16"/>
       <c r="G181" s="16"/>
@@ -7343,16 +7515,16 @@
         <v>212</v>
       </c>
       <c r="B182" s="18" t="s">
-        <v>946</v>
+        <v>931</v>
       </c>
       <c r="C182" s="18" t="s">
-        <v>948</v>
-      </c>
-      <c r="D182" s="18" t="s">
-        <v>223</v>
+        <v>930</v>
+      </c>
+      <c r="D182" t="s">
+        <v>1106</v>
       </c>
       <c r="E182" s="18" t="s">
-        <v>949</v>
+        <v>934</v>
       </c>
       <c r="F182" s="16"/>
       <c r="G182" s="16"/>
@@ -7362,16 +7534,16 @@
         <v>212</v>
       </c>
       <c r="B183" s="18" t="s">
-        <v>947</v>
+        <v>933</v>
       </c>
       <c r="C183" s="18" t="s">
-        <v>948</v>
-      </c>
-      <c r="D183" s="18" t="s">
-        <v>223</v>
+        <v>932</v>
+      </c>
+      <c r="D183" t="s">
+        <v>1106</v>
       </c>
       <c r="E183" s="18" t="s">
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="F183" s="16"/>
       <c r="G183" s="16"/>
@@ -7381,16 +7553,16 @@
         <v>212</v>
       </c>
       <c r="B184" s="18" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="C184" s="18" t="s">
-        <v>950</v>
-      </c>
-      <c r="D184" s="18" t="s">
-        <v>223</v>
+        <v>935</v>
+      </c>
+      <c r="D184" t="s">
+        <v>1106</v>
       </c>
       <c r="E184" s="18" t="s">
-        <v>953</v>
+        <v>938</v>
       </c>
       <c r="F184" s="16"/>
       <c r="G184" s="16"/>
@@ -7400,16 +7572,16 @@
         <v>212</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>952</v>
+        <v>939</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>950</v>
-      </c>
-      <c r="D185" s="18" t="s">
-        <v>223</v>
+        <v>941</v>
+      </c>
+      <c r="D185" t="s">
+        <v>1106</v>
       </c>
       <c r="E185" s="18" t="s">
-        <v>953</v>
+        <v>938</v>
       </c>
       <c r="F185" s="16"/>
       <c r="G185" s="16"/>
@@ -7419,16 +7591,16 @@
         <v>212</v>
       </c>
       <c r="B186" s="18" t="s">
-        <v>954</v>
+        <v>940</v>
       </c>
       <c r="C186" s="18" t="s">
-        <v>955</v>
-      </c>
-      <c r="D186" s="18" t="s">
-        <v>223</v>
+        <v>942</v>
+      </c>
+      <c r="D186" t="s">
+        <v>1106</v>
       </c>
       <c r="E186" s="18" t="s">
-        <v>968</v>
+        <v>938</v>
       </c>
       <c r="F186" s="16"/>
       <c r="G186" s="16"/>
@@ -7438,16 +7610,16 @@
         <v>212</v>
       </c>
       <c r="B187" s="18" t="s">
-        <v>956</v>
+        <v>1142</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>959</v>
+        <v>1143</v>
       </c>
       <c r="D187" s="18" t="s">
-        <v>223</v>
+        <v>1106</v>
       </c>
       <c r="E187" s="18" t="s">
-        <v>969</v>
+        <v>945</v>
       </c>
       <c r="F187" s="16"/>
       <c r="G187" s="16"/>
@@ -7457,16 +7629,16 @@
         <v>212</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>957</v>
+        <v>943</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>960</v>
-      </c>
-      <c r="D188" s="18" t="s">
-        <v>223</v>
+        <v>944</v>
+      </c>
+      <c r="D188" t="s">
+        <v>1106</v>
       </c>
       <c r="E188" s="18" t="s">
-        <v>970</v>
+        <v>945</v>
       </c>
       <c r="F188" s="16"/>
       <c r="G188" s="16"/>
@@ -7476,16 +7648,16 @@
         <v>212</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>958</v>
+        <v>1144</v>
       </c>
       <c r="C189" s="18" t="s">
-        <v>961</v>
-      </c>
-      <c r="D189" s="18" t="s">
-        <v>223</v>
+        <v>948</v>
+      </c>
+      <c r="D189" t="s">
+        <v>1106</v>
       </c>
       <c r="E189" s="18" t="s">
-        <v>971</v>
+        <v>949</v>
       </c>
       <c r="F189" s="16"/>
       <c r="G189" s="16"/>
@@ -7495,16 +7667,16 @@
         <v>212</v>
       </c>
       <c r="B190" s="18" t="s">
-        <v>963</v>
+        <v>946</v>
       </c>
       <c r="C190" s="18" t="s">
-        <v>962</v>
-      </c>
-      <c r="D190" s="18" t="s">
-        <v>223</v>
+        <v>948</v>
+      </c>
+      <c r="D190" t="s">
+        <v>1106</v>
       </c>
       <c r="E190" s="18" t="s">
-        <v>996</v>
+        <v>949</v>
       </c>
       <c r="F190" s="16"/>
       <c r="G190" s="16"/>
@@ -7514,16 +7686,16 @@
         <v>212</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>964</v>
-      </c>
-      <c r="D191" s="18" t="s">
-        <v>223</v>
+        <v>948</v>
+      </c>
+      <c r="D191" t="s">
+        <v>1106</v>
       </c>
       <c r="E191" s="18" t="s">
-        <v>972</v>
+        <v>949</v>
       </c>
       <c r="F191" s="16"/>
       <c r="G191" s="16"/>
@@ -7533,16 +7705,16 @@
         <v>212</v>
       </c>
       <c r="B192" s="18" t="s">
-        <v>966</v>
+        <v>951</v>
       </c>
       <c r="C192" s="18" t="s">
-        <v>967</v>
-      </c>
-      <c r="D192" s="18" t="s">
-        <v>223</v>
+        <v>950</v>
+      </c>
+      <c r="D192" t="s">
+        <v>1106</v>
       </c>
       <c r="E192" s="18" t="s">
-        <v>973</v>
+        <v>953</v>
       </c>
       <c r="F192" s="16"/>
       <c r="G192" s="16"/>
@@ -7552,16 +7724,16 @@
         <v>212</v>
       </c>
       <c r="B193" s="18" t="s">
-        <v>974</v>
+        <v>952</v>
       </c>
       <c r="C193" s="18" t="s">
-        <v>975</v>
-      </c>
-      <c r="D193" s="18" t="s">
-        <v>223</v>
+        <v>950</v>
+      </c>
+      <c r="D193" t="s">
+        <v>1106</v>
       </c>
       <c r="E193" s="18" t="s">
-        <v>997</v>
+        <v>953</v>
       </c>
       <c r="F193" s="16"/>
       <c r="G193" s="16"/>
@@ -7571,16 +7743,16 @@
         <v>212</v>
       </c>
       <c r="B194" s="18" t="s">
-        <v>977</v>
+        <v>1119</v>
       </c>
       <c r="C194" s="18" t="s">
-        <v>976</v>
-      </c>
-      <c r="D194" s="18" t="s">
-        <v>223</v>
+        <v>1121</v>
+      </c>
+      <c r="D194" t="s">
+        <v>1106</v>
       </c>
       <c r="E194" s="18" t="s">
-        <v>978</v>
+        <v>1124</v>
       </c>
       <c r="F194" s="16"/>
       <c r="G194" s="16"/>
@@ -7590,16 +7762,16 @@
         <v>212</v>
       </c>
       <c r="B195" s="18" t="s">
-        <v>979</v>
+        <v>1120</v>
       </c>
       <c r="C195" s="18" t="s">
-        <v>980</v>
-      </c>
-      <c r="D195" s="18" t="s">
-        <v>223</v>
+        <v>1122</v>
+      </c>
+      <c r="D195" t="s">
+        <v>1106</v>
       </c>
       <c r="E195" s="18" t="s">
-        <v>981</v>
+        <v>1123</v>
       </c>
       <c r="F195" s="16"/>
       <c r="G195" s="16"/>
@@ -7609,16 +7781,16 @@
         <v>212</v>
       </c>
       <c r="B196" s="18" t="s">
-        <v>985</v>
+        <v>954</v>
       </c>
       <c r="C196" s="18" t="s">
-        <v>986</v>
-      </c>
-      <c r="D196" s="18" t="s">
-        <v>223</v>
+        <v>955</v>
+      </c>
+      <c r="D196" t="s">
+        <v>1106</v>
       </c>
       <c r="E196" s="18" t="s">
-        <v>998</v>
+        <v>968</v>
       </c>
       <c r="F196" s="16"/>
       <c r="G196" s="16"/>
@@ -7628,16 +7800,16 @@
         <v>212</v>
       </c>
       <c r="B197" s="18" t="s">
-        <v>987</v>
+        <v>956</v>
       </c>
       <c r="C197" s="18" t="s">
-        <v>988</v>
-      </c>
-      <c r="D197" s="18" t="s">
-        <v>223</v>
+        <v>959</v>
+      </c>
+      <c r="D197" t="s">
+        <v>1106</v>
       </c>
       <c r="E197" s="18" t="s">
-        <v>989</v>
+        <v>969</v>
       </c>
       <c r="F197" s="16"/>
       <c r="G197" s="16"/>
@@ -7647,16 +7819,16 @@
         <v>212</v>
       </c>
       <c r="B198" s="18" t="s">
-        <v>982</v>
+        <v>957</v>
       </c>
       <c r="C198" s="18" t="s">
-        <v>990</v>
-      </c>
-      <c r="D198" s="18" t="s">
-        <v>223</v>
+        <v>960</v>
+      </c>
+      <c r="D198" t="s">
+        <v>1106</v>
       </c>
       <c r="E198" s="18" t="s">
-        <v>1008</v>
+        <v>970</v>
       </c>
       <c r="F198" s="16"/>
       <c r="G198" s="16"/>
@@ -7666,16 +7838,16 @@
         <v>212</v>
       </c>
       <c r="B199" s="18" t="s">
-        <v>991</v>
+        <v>958</v>
       </c>
       <c r="C199" s="18" t="s">
-        <v>992</v>
-      </c>
-      <c r="D199" s="18" t="s">
-        <v>223</v>
+        <v>961</v>
+      </c>
+      <c r="D199" t="s">
+        <v>1106</v>
       </c>
       <c r="E199" s="18" t="s">
-        <v>999</v>
+        <v>971</v>
       </c>
       <c r="F199" s="16"/>
       <c r="G199" s="16"/>
@@ -7685,16 +7857,16 @@
         <v>212</v>
       </c>
       <c r="B200" s="18" t="s">
-        <v>993</v>
+        <v>963</v>
       </c>
       <c r="C200" s="18" t="s">
-        <v>994</v>
-      </c>
-      <c r="D200" s="18" t="s">
-        <v>223</v>
+        <v>962</v>
+      </c>
+      <c r="D200" t="s">
+        <v>1106</v>
       </c>
       <c r="E200" s="18" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F200" s="16"/>
       <c r="G200" s="16"/>
@@ -7704,16 +7876,16 @@
         <v>212</v>
       </c>
       <c r="B201" s="18" t="s">
-        <v>983</v>
+        <v>965</v>
       </c>
       <c r="C201" s="18" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D201" s="18" t="s">
-        <v>223</v>
+        <v>964</v>
+      </c>
+      <c r="D201" t="s">
+        <v>1106</v>
       </c>
       <c r="E201" s="18" t="s">
-        <v>1009</v>
+        <v>972</v>
       </c>
       <c r="F201" s="16"/>
       <c r="G201" s="16"/>
@@ -7723,16 +7895,16 @@
         <v>212</v>
       </c>
       <c r="B202" s="18" t="s">
-        <v>1003</v>
+        <v>966</v>
       </c>
       <c r="C202" s="18" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D202" s="18" t="s">
-        <v>223</v>
+        <v>967</v>
+      </c>
+      <c r="D202" t="s">
+        <v>1106</v>
       </c>
       <c r="E202" s="18" t="s">
-        <v>1002</v>
+        <v>973</v>
       </c>
       <c r="F202" s="16"/>
       <c r="G202" s="16"/>
@@ -7742,16 +7914,16 @@
         <v>212</v>
       </c>
       <c r="B203" s="18" t="s">
-        <v>1004</v>
+        <v>974</v>
       </c>
       <c r="C203" s="18" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D203" s="18" t="s">
-        <v>223</v>
+        <v>975</v>
+      </c>
+      <c r="D203" t="s">
+        <v>1106</v>
       </c>
       <c r="E203" s="18" t="s">
-        <v>1006</v>
+        <v>997</v>
       </c>
       <c r="F203" s="16"/>
       <c r="G203" s="16"/>
@@ -7761,263 +7933,263 @@
         <v>212</v>
       </c>
       <c r="B204" s="18" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="C204" s="18" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D204" s="18" t="s">
-        <v>223</v>
+        <v>976</v>
+      </c>
+      <c r="D204" t="s">
+        <v>1106</v>
       </c>
       <c r="E204" s="18" t="s">
-        <v>1010</v>
+        <v>978</v>
       </c>
       <c r="F204" s="16"/>
       <c r="G204" s="16"/>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B205" s="18" t="s">
-        <v>636</v>
+        <v>979</v>
       </c>
       <c r="C205" s="18" t="s">
-        <v>662</v>
-      </c>
-      <c r="D205" s="18" t="s">
-        <v>200</v>
+        <v>980</v>
+      </c>
+      <c r="D205" t="s">
+        <v>1106</v>
       </c>
       <c r="E205" s="18" t="s">
-        <v>674</v>
+        <v>981</v>
       </c>
       <c r="F205" s="16"/>
       <c r="G205" s="16"/>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B206" s="18" t="s">
-        <v>637</v>
+        <v>985</v>
       </c>
       <c r="C206" s="18" t="s">
-        <v>663</v>
-      </c>
-      <c r="D206" s="18" t="s">
-        <v>200</v>
+        <v>986</v>
+      </c>
+      <c r="D206" t="s">
+        <v>1106</v>
       </c>
       <c r="E206" s="18" t="s">
-        <v>675</v>
+        <v>998</v>
       </c>
       <c r="F206" s="16"/>
       <c r="G206" s="16"/>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B207" s="18" t="s">
-        <v>638</v>
+        <v>987</v>
       </c>
       <c r="C207" s="18" t="s">
-        <v>676</v>
-      </c>
-      <c r="D207" s="18" t="s">
-        <v>200</v>
+        <v>988</v>
+      </c>
+      <c r="D207" t="s">
+        <v>1106</v>
       </c>
       <c r="E207" s="18" t="s">
-        <v>677</v>
+        <v>989</v>
       </c>
       <c r="F207" s="16"/>
       <c r="G207" s="16"/>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B208" s="18" t="s">
-        <v>649</v>
+        <v>982</v>
       </c>
       <c r="C208" s="18" t="s">
-        <v>648</v>
-      </c>
-      <c r="D208" s="18" t="s">
-        <v>200</v>
+        <v>990</v>
+      </c>
+      <c r="D208" t="s">
+        <v>1106</v>
       </c>
       <c r="E208" s="18" t="s">
-        <v>678</v>
+        <v>1008</v>
       </c>
       <c r="F208" s="16"/>
       <c r="G208" s="16"/>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B209" s="18" t="s">
-        <v>650</v>
-      </c>
-      <c r="C209" s="19" t="s">
-        <v>651</v>
-      </c>
-      <c r="D209" s="18" t="s">
-        <v>200</v>
+        <v>991</v>
+      </c>
+      <c r="C209" s="18" t="s">
+        <v>992</v>
+      </c>
+      <c r="D209" t="s">
+        <v>1106</v>
       </c>
       <c r="E209" s="18" t="s">
-        <v>679</v>
+        <v>999</v>
       </c>
       <c r="F209" s="16"/>
       <c r="G209" s="16"/>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B210" s="18" t="s">
-        <v>639</v>
+        <v>993</v>
       </c>
       <c r="C210" s="18" t="s">
-        <v>664</v>
-      </c>
-      <c r="D210" s="18" t="s">
-        <v>200</v>
+        <v>994</v>
+      </c>
+      <c r="D210" t="s">
+        <v>1106</v>
       </c>
       <c r="E210" s="18" t="s">
-        <v>717</v>
+        <v>995</v>
       </c>
       <c r="F210" s="16"/>
       <c r="G210" s="16"/>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B211" s="18" t="s">
-        <v>640</v>
+        <v>983</v>
       </c>
       <c r="C211" s="18" t="s">
-        <v>665</v>
-      </c>
-      <c r="D211" s="18" t="s">
-        <v>200</v>
+        <v>1000</v>
+      </c>
+      <c r="D211" t="s">
+        <v>1106</v>
       </c>
       <c r="E211" s="18" t="s">
-        <v>718</v>
+        <v>1009</v>
       </c>
       <c r="F211" s="16"/>
       <c r="G211" s="16"/>
     </row>
     <row r="212" spans="1:7">
       <c r="A212" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B212" s="18" t="s">
-        <v>641</v>
+        <v>1003</v>
       </c>
       <c r="C212" s="18" t="s">
-        <v>666</v>
-      </c>
-      <c r="D212" s="18" t="s">
-        <v>200</v>
+        <v>1001</v>
+      </c>
+      <c r="D212" t="s">
+        <v>1106</v>
       </c>
       <c r="E212" s="18" t="s">
-        <v>719</v>
+        <v>1002</v>
       </c>
       <c r="F212" s="16"/>
       <c r="G212" s="16"/>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B213" s="18" t="s">
-        <v>642</v>
+        <v>1004</v>
       </c>
       <c r="C213" s="18" t="s">
-        <v>667</v>
-      </c>
-      <c r="D213" s="18" t="s">
-        <v>200</v>
+        <v>1005</v>
+      </c>
+      <c r="D213" t="s">
+        <v>1106</v>
       </c>
       <c r="E213" s="18" t="s">
-        <v>673</v>
+        <v>1006</v>
       </c>
       <c r="F213" s="16"/>
       <c r="G213" s="16"/>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B214" s="18" t="s">
-        <v>643</v>
+        <v>984</v>
       </c>
       <c r="C214" s="18" t="s">
-        <v>668</v>
-      </c>
-      <c r="D214" s="18" t="s">
-        <v>200</v>
+        <v>1007</v>
+      </c>
+      <c r="D214" t="s">
+        <v>1106</v>
       </c>
       <c r="E214" s="18" t="s">
-        <v>720</v>
+        <v>1010</v>
       </c>
       <c r="F214" s="16"/>
       <c r="G214" s="16"/>
     </row>
     <row r="215" spans="1:7">
       <c r="A215" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B215" s="18" t="s">
-        <v>644</v>
+        <v>1110</v>
       </c>
       <c r="C215" s="18" t="s">
-        <v>669</v>
-      </c>
-      <c r="D215" s="18" t="s">
-        <v>200</v>
+        <v>1115</v>
+      </c>
+      <c r="D215" t="s">
+        <v>1106</v>
       </c>
       <c r="E215" s="18" t="s">
-        <v>721</v>
+        <v>1117</v>
       </c>
       <c r="F215" s="16"/>
       <c r="G215" s="16"/>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B216" s="18" t="s">
-        <v>645</v>
+        <v>1112</v>
       </c>
       <c r="C216" s="18" t="s">
-        <v>670</v>
-      </c>
-      <c r="D216" s="18" t="s">
-        <v>200</v>
+        <v>1114</v>
+      </c>
+      <c r="D216" t="s">
+        <v>1106</v>
       </c>
       <c r="E216" s="18" t="s">
-        <v>722</v>
+        <v>1116</v>
       </c>
       <c r="F216" s="16"/>
       <c r="G216" s="16"/>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B217" s="18" t="s">
-        <v>646</v>
+        <v>1111</v>
       </c>
       <c r="C217" s="18" t="s">
-        <v>671</v>
-      </c>
-      <c r="D217" s="18" t="s">
-        <v>200</v>
+        <v>1113</v>
+      </c>
+      <c r="D217" t="s">
+        <v>1106</v>
       </c>
       <c r="E217" s="18" t="s">
-        <v>672</v>
+        <v>1118</v>
       </c>
       <c r="F217" s="16"/>
       <c r="G217" s="16"/>
@@ -8027,16 +8199,16 @@
         <v>282</v>
       </c>
       <c r="B218" s="18" t="s">
-        <v>1089</v>
+        <v>636</v>
       </c>
       <c r="C218" s="18" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D218" s="18" t="s">
-        <v>200</v>
+        <v>662</v>
+      </c>
+      <c r="D218" t="s">
+        <v>1107</v>
       </c>
       <c r="E218" s="18" t="s">
-        <v>717</v>
+        <v>674</v>
       </c>
       <c r="F218" s="16"/>
       <c r="G218" s="16"/>
@@ -8046,16 +8218,16 @@
         <v>282</v>
       </c>
       <c r="B219" s="18" t="s">
-        <v>1090</v>
+        <v>637</v>
       </c>
       <c r="C219" s="18" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D219" s="18" t="s">
-        <v>200</v>
+        <v>663</v>
+      </c>
+      <c r="D219" t="s">
+        <v>1107</v>
       </c>
       <c r="E219" s="18" t="s">
-        <v>718</v>
+        <v>675</v>
       </c>
       <c r="F219" s="16"/>
       <c r="G219" s="16"/>
@@ -8065,16 +8237,16 @@
         <v>282</v>
       </c>
       <c r="B220" s="18" t="s">
-        <v>1091</v>
+        <v>638</v>
       </c>
       <c r="C220" s="18" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D220" s="18" t="s">
-        <v>200</v>
+        <v>676</v>
+      </c>
+      <c r="D220" t="s">
+        <v>1107</v>
       </c>
       <c r="E220" s="18" t="s">
-        <v>719</v>
+        <v>677</v>
       </c>
       <c r="F220" s="16"/>
       <c r="G220" s="16"/>
@@ -8084,16 +8256,16 @@
         <v>282</v>
       </c>
       <c r="B221" s="18" t="s">
-        <v>1092</v>
+        <v>649</v>
       </c>
       <c r="C221" s="18" t="s">
-        <v>1098</v>
-      </c>
-      <c r="D221" s="18" t="s">
-        <v>200</v>
+        <v>648</v>
+      </c>
+      <c r="D221" t="s">
+        <v>1107</v>
       </c>
       <c r="E221" s="18" t="s">
-        <v>720</v>
+        <v>678</v>
       </c>
       <c r="F221" s="16"/>
       <c r="G221" s="16"/>
@@ -8103,16 +8275,16 @@
         <v>282</v>
       </c>
       <c r="B222" s="18" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C222" s="18" t="s">
-        <v>1099</v>
-      </c>
-      <c r="D222" s="18" t="s">
-        <v>200</v>
+        <v>650</v>
+      </c>
+      <c r="C222" s="19" t="s">
+        <v>651</v>
+      </c>
+      <c r="D222" t="s">
+        <v>1107</v>
       </c>
       <c r="E222" s="18" t="s">
-        <v>721</v>
+        <v>679</v>
       </c>
       <c r="F222" s="16"/>
       <c r="G222" s="16"/>
@@ -8122,16 +8294,16 @@
         <v>282</v>
       </c>
       <c r="B223" s="18" t="s">
-        <v>1094</v>
+        <v>639</v>
       </c>
       <c r="C223" s="18" t="s">
-        <v>1100</v>
-      </c>
-      <c r="D223" s="18" t="s">
-        <v>200</v>
+        <v>664</v>
+      </c>
+      <c r="D223" t="s">
+        <v>1107</v>
       </c>
       <c r="E223" s="18" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="F223" s="16"/>
       <c r="G223" s="16"/>
@@ -8141,16 +8313,16 @@
         <v>282</v>
       </c>
       <c r="B224" s="18" t="s">
-        <v>1016</v>
+        <v>640</v>
       </c>
       <c r="C224" s="18" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D224" s="18" t="s">
-        <v>200</v>
+        <v>665</v>
+      </c>
+      <c r="D224" t="s">
+        <v>1107</v>
       </c>
       <c r="E224" s="18" t="s">
-        <v>1023</v>
+        <v>718</v>
       </c>
       <c r="F224" s="16"/>
       <c r="G224" s="16"/>
@@ -8160,16 +8332,16 @@
         <v>282</v>
       </c>
       <c r="B225" s="18" t="s">
-        <v>1018</v>
+        <v>641</v>
       </c>
       <c r="C225" s="18" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D225" s="18" t="s">
-        <v>200</v>
+        <v>666</v>
+      </c>
+      <c r="D225" t="s">
+        <v>1107</v>
       </c>
       <c r="E225" s="18" t="s">
-        <v>1024</v>
+        <v>719</v>
       </c>
       <c r="F225" s="16"/>
       <c r="G225" s="16"/>
@@ -8179,16 +8351,16 @@
         <v>282</v>
       </c>
       <c r="B226" s="18" t="s">
-        <v>1020</v>
+        <v>642</v>
       </c>
       <c r="C226" s="18" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D226" s="18" t="s">
-        <v>200</v>
+        <v>667</v>
+      </c>
+      <c r="D226" t="s">
+        <v>1107</v>
       </c>
       <c r="E226" s="18" t="s">
-        <v>1025</v>
+        <v>673</v>
       </c>
       <c r="F226" s="16"/>
       <c r="G226" s="16"/>
@@ -8198,16 +8370,16 @@
         <v>282</v>
       </c>
       <c r="B227" s="18" t="s">
-        <v>1040</v>
+        <v>643</v>
       </c>
       <c r="C227" s="18" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D227" s="18" t="s">
-        <v>200</v>
+        <v>668</v>
+      </c>
+      <c r="D227" t="s">
+        <v>1107</v>
       </c>
       <c r="E227" s="18" t="s">
-        <v>1026</v>
+        <v>720</v>
       </c>
       <c r="F227" s="16"/>
       <c r="G227" s="16"/>
@@ -8217,16 +8389,16 @@
         <v>282</v>
       </c>
       <c r="B228" s="18" t="s">
-        <v>1021</v>
+        <v>644</v>
       </c>
       <c r="C228" s="18" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D228" s="18" t="s">
-        <v>200</v>
+        <v>669</v>
+      </c>
+      <c r="D228" t="s">
+        <v>1107</v>
       </c>
       <c r="E228" s="18" t="s">
-        <v>1042</v>
+        <v>721</v>
       </c>
       <c r="F228" s="16"/>
       <c r="G228" s="16"/>
@@ -8236,374 +8408,366 @@
         <v>282</v>
       </c>
       <c r="B229" s="18" t="s">
-        <v>1031</v>
+        <v>645</v>
       </c>
       <c r="C229" s="18" t="s">
-        <v>1032</v>
-      </c>
-      <c r="D229" s="18" t="s">
-        <v>200</v>
+        <v>670</v>
+      </c>
+      <c r="D229" t="s">
+        <v>1107</v>
       </c>
       <c r="E229" s="18" t="s">
-        <v>1038</v>
-      </c>
-      <c r="F229" s="20"/>
-      <c r="G229" s="20"/>
+        <v>722</v>
+      </c>
+      <c r="F229" s="16"/>
+      <c r="G229" s="16"/>
     </row>
     <row r="230" spans="1:7">
       <c r="A230" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B230" s="18" t="s">
-        <v>1033</v>
+        <v>646</v>
       </c>
       <c r="C230" s="18" t="s">
-        <v>1034</v>
-      </c>
-      <c r="D230" s="18" t="s">
-        <v>200</v>
+        <v>671</v>
+      </c>
+      <c r="D230" t="s">
+        <v>1107</v>
       </c>
       <c r="E230" s="18" t="s">
-        <v>1035</v>
-      </c>
-      <c r="F230" s="20"/>
-      <c r="G230" s="20"/>
+        <v>672</v>
+      </c>
+      <c r="F230" s="16"/>
+      <c r="G230" s="16"/>
     </row>
     <row r="231" spans="1:7">
       <c r="A231" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B231" s="18" t="s">
-        <v>1036</v>
+        <v>1089</v>
       </c>
       <c r="C231" s="18" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D231" s="18" t="s">
-        <v>200</v>
+        <v>1095</v>
+      </c>
+      <c r="D231" t="s">
+        <v>1107</v>
       </c>
       <c r="E231" s="18" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F231" s="20"/>
-      <c r="G231" s="20"/>
+        <v>717</v>
+      </c>
+      <c r="F231" s="16"/>
+      <c r="G231" s="16"/>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B232" s="18" t="s">
-        <v>5</v>
+        <v>1090</v>
       </c>
       <c r="C232" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D232" s="18" t="s">
-        <v>198</v>
+        <v>1096</v>
+      </c>
+      <c r="D232" t="s">
+        <v>1107</v>
       </c>
       <c r="E232" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F232" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G232" s="16" t="s">
-        <v>7</v>
-      </c>
+        <v>718</v>
+      </c>
+      <c r="F232" s="16"/>
+      <c r="G232" s="16"/>
     </row>
     <row r="233" spans="1:7">
       <c r="A233" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B233" s="18" t="s">
-        <v>9</v>
+        <v>1091</v>
       </c>
       <c r="C233" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D233" s="18" t="s">
-        <v>198</v>
+        <v>1097</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1107</v>
       </c>
       <c r="E233" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="F233" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G233" s="16" t="s">
-        <v>10</v>
-      </c>
+        <v>719</v>
+      </c>
+      <c r="F233" s="16"/>
+      <c r="G233" s="16"/>
     </row>
     <row r="234" spans="1:7">
       <c r="A234" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B234" s="18" t="s">
-        <v>12</v>
+        <v>1092</v>
       </c>
       <c r="C234" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D234" s="18" t="s">
-        <v>198</v>
+        <v>1098</v>
+      </c>
+      <c r="D234" t="s">
+        <v>1107</v>
       </c>
       <c r="E234" s="18" t="s">
-        <v>167</v>
+        <v>720</v>
       </c>
       <c r="F234" s="16"/>
       <c r="G234" s="16"/>
     </row>
     <row r="235" spans="1:7">
       <c r="A235" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B235" s="18" t="s">
-        <v>14</v>
+        <v>1093</v>
       </c>
       <c r="C235" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D235" s="18" t="s">
-        <v>198</v>
+        <v>1099</v>
+      </c>
+      <c r="D235" t="s">
+        <v>1107</v>
       </c>
       <c r="E235" s="18" t="s">
-        <v>166</v>
+        <v>721</v>
       </c>
       <c r="F235" s="16"/>
       <c r="G235" s="16"/>
     </row>
     <row r="236" spans="1:7">
       <c r="A236" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B236" s="18" t="s">
-        <v>16</v>
+        <v>1094</v>
       </c>
       <c r="C236" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D236" s="18" t="s">
-        <v>198</v>
+        <v>1100</v>
+      </c>
+      <c r="D236" t="s">
+        <v>1107</v>
       </c>
       <c r="E236" s="18" t="s">
-        <v>168</v>
+        <v>722</v>
       </c>
       <c r="F236" s="16"/>
       <c r="G236" s="16"/>
     </row>
     <row r="237" spans="1:7">
       <c r="A237" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B237" s="18" t="s">
-        <v>19</v>
+        <v>1016</v>
       </c>
       <c r="C237" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="D237" s="18" t="s">
-        <v>198</v>
+        <v>1017</v>
+      </c>
+      <c r="D237" t="s">
+        <v>1107</v>
       </c>
       <c r="E237" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="F237" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G237" s="16" t="s">
-        <v>134</v>
-      </c>
+        <v>1023</v>
+      </c>
+      <c r="F237" s="16"/>
+      <c r="G237" s="16"/>
     </row>
     <row r="238" spans="1:7">
       <c r="A238" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B238" s="18" t="s">
-        <v>133</v>
+        <v>1018</v>
       </c>
       <c r="C238" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D238" s="18" t="s">
-        <v>198</v>
+        <v>1019</v>
+      </c>
+      <c r="D238" t="s">
+        <v>1107</v>
       </c>
       <c r="E238" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="F238" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G238" s="16" t="s">
-        <v>21</v>
-      </c>
+        <v>1024</v>
+      </c>
+      <c r="F238" s="16"/>
+      <c r="G238" s="16"/>
     </row>
     <row r="239" spans="1:7">
       <c r="A239" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B239" s="18" t="s">
-        <v>132</v>
+        <v>1020</v>
       </c>
       <c r="C239" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D239" s="18" t="s">
-        <v>198</v>
+        <v>1027</v>
+      </c>
+      <c r="D239" t="s">
+        <v>1107</v>
       </c>
       <c r="E239" s="18" t="s">
-        <v>140</v>
+        <v>1025</v>
       </c>
       <c r="F239" s="16"/>
       <c r="G239" s="16"/>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B240" s="18" t="s">
-        <v>23</v>
+        <v>1040</v>
       </c>
       <c r="C240" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D240" s="18" t="s">
-        <v>198</v>
+        <v>1041</v>
+      </c>
+      <c r="D240" t="s">
+        <v>1107</v>
       </c>
       <c r="E240" s="18" t="s">
-        <v>139</v>
+        <v>1026</v>
       </c>
       <c r="F240" s="16"/>
       <c r="G240" s="16"/>
     </row>
     <row r="241" spans="1:7">
       <c r="A241" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B241" s="18" t="s">
-        <v>141</v>
+        <v>1021</v>
       </c>
       <c r="C241" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D241" s="18" t="s">
-        <v>198</v>
+        <v>1022</v>
+      </c>
+      <c r="D241" t="s">
+        <v>1107</v>
       </c>
       <c r="E241" s="18" t="s">
-        <v>142</v>
+        <v>1042</v>
       </c>
       <c r="F241" s="16"/>
       <c r="G241" s="16"/>
     </row>
     <row r="242" spans="1:7">
       <c r="A242" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B242" s="18" t="s">
-        <v>25</v>
+        <v>1031</v>
       </c>
       <c r="C242" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D242" s="18" t="s">
-        <v>198</v>
+        <v>1032</v>
+      </c>
+      <c r="D242" t="s">
+        <v>1107</v>
       </c>
       <c r="E242" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="F242" s="16"/>
-      <c r="G242" s="16"/>
+        <v>1038</v>
+      </c>
+      <c r="F242" s="20"/>
+      <c r="G242" s="20"/>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B243" s="18" t="s">
-        <v>27</v>
+        <v>1033</v>
       </c>
       <c r="C243" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D243" s="18" t="s">
-        <v>198</v>
+        <v>1034</v>
+      </c>
+      <c r="D243" t="s">
+        <v>1107</v>
       </c>
       <c r="E243" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F243" s="16"/>
-      <c r="G243" s="16"/>
+        <v>1035</v>
+      </c>
+      <c r="F243" s="20"/>
+      <c r="G243" s="20"/>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B244" s="18" t="s">
-        <v>29</v>
+        <v>1036</v>
       </c>
       <c r="C244" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D244" s="18" t="s">
-        <v>198</v>
+        <v>1037</v>
+      </c>
+      <c r="D244" t="s">
+        <v>1107</v>
       </c>
       <c r="E244" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="F244" s="16"/>
-      <c r="G244" s="16"/>
+        <v>1039</v>
+      </c>
+      <c r="F244" s="20"/>
+      <c r="G244" s="20"/>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" s="18" t="s">
         <v>118</v>
       </c>
       <c r="B245" s="18" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="C245" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D245" s="18" t="s">
-        <v>198</v>
+        <v>4</v>
+      </c>
+      <c r="D245" t="s">
+        <v>1109</v>
       </c>
       <c r="E245" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F245" s="16"/>
-      <c r="G245" s="16"/>
+        <v>164</v>
+      </c>
+      <c r="F245" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G245" s="16" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="246" spans="1:7">
       <c r="A246" s="18" t="s">
         <v>118</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D246" s="18" t="s">
-        <v>198</v>
+        <v>8</v>
+      </c>
+      <c r="D246" t="s">
+        <v>1109</v>
       </c>
       <c r="E246" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="F246" s="16"/>
-      <c r="G246" s="16"/>
+        <v>165</v>
+      </c>
+      <c r="F246" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G246" s="16" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="247" spans="1:7">
       <c r="A247" s="18" t="s">
         <v>118</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C247" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D247" s="18" t="s">
-        <v>198</v>
+        <v>11</v>
+      </c>
+      <c r="D247" t="s">
+        <v>1109</v>
       </c>
       <c r="E247" s="18" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="F247" s="16"/>
       <c r="G247" s="16"/>
@@ -8613,16 +8777,16 @@
         <v>118</v>
       </c>
       <c r="B248" s="18" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C248" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D248" s="18" t="s">
-        <v>198</v>
+        <v>13</v>
+      </c>
+      <c r="D248" t="s">
+        <v>1109</v>
       </c>
       <c r="E248" s="18" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="F248" s="16"/>
       <c r="G248" s="16"/>
@@ -8632,16 +8796,16 @@
         <v>118</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="D249" s="18" t="s">
-        <v>198</v>
+        <v>15</v>
+      </c>
+      <c r="D249" t="s">
+        <v>1109</v>
       </c>
       <c r="E249" s="18" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="F249" s="16"/>
       <c r="G249" s="16"/>
@@ -8650,23 +8814,23 @@
       <c r="A250" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="B250" s="28" t="s">
-        <v>40</v>
+      <c r="B250" s="18" t="s">
+        <v>19</v>
       </c>
       <c r="C250" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D250" s="18" t="s">
-        <v>199</v>
+        <v>18</v>
+      </c>
+      <c r="D250" t="s">
+        <v>1109</v>
       </c>
       <c r="E250" s="18" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="F250" s="16" t="s">
         <v>6</v>
       </c>
       <c r="G250" s="16" t="s">
-        <v>7</v>
+        <v>134</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -8674,22 +8838,22 @@
         <v>118</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="C251" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D251" s="18" t="s">
-        <v>199</v>
+        <v>20</v>
+      </c>
+      <c r="D251" t="s">
+        <v>1109</v>
       </c>
       <c r="E251" s="18" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="F251" s="16" t="s">
         <v>6</v>
       </c>
       <c r="G251" s="16" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -8697,16 +8861,16 @@
         <v>118</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D252" s="18" t="s">
-        <v>199</v>
+        <v>17</v>
+      </c>
+      <c r="D252" t="s">
+        <v>1109</v>
       </c>
       <c r="E252" s="18" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="F252" s="16"/>
       <c r="G252" s="16"/>
@@ -8716,16 +8880,16 @@
         <v>118</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C253" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D253" s="18" t="s">
-        <v>199</v>
+        <v>24</v>
+      </c>
+      <c r="D253" t="s">
+        <v>1109</v>
       </c>
       <c r="E253" s="18" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="F253" s="16"/>
       <c r="G253" s="16"/>
@@ -8735,16 +8899,16 @@
         <v>118</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D254" s="18" t="s">
-        <v>199</v>
+        <v>22</v>
+      </c>
+      <c r="D254" t="s">
+        <v>1109</v>
       </c>
       <c r="E254" s="18" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="F254" s="16"/>
       <c r="G254" s="16"/>
@@ -8754,16 +8918,16 @@
         <v>118</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C255" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D255" s="18" t="s">
-        <v>199</v>
+        <v>26</v>
+      </c>
+      <c r="D255" t="s">
+        <v>1109</v>
       </c>
       <c r="E255" s="18" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F255" s="16"/>
       <c r="G255" s="16"/>
@@ -8773,16 +8937,16 @@
         <v>118</v>
       </c>
       <c r="B256" s="18" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C256" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="D256" s="18" t="s">
-        <v>199</v>
+        <v>28</v>
+      </c>
+      <c r="D256" t="s">
+        <v>1109</v>
       </c>
       <c r="E256" s="18" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F256" s="16"/>
       <c r="G256" s="16"/>
@@ -8792,16 +8956,16 @@
         <v>118</v>
       </c>
       <c r="B257" s="18" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C257" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D257" s="18" t="s">
-        <v>199</v>
+        <v>30</v>
+      </c>
+      <c r="D257" t="s">
+        <v>1109</v>
       </c>
       <c r="E257" s="18" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F257" s="16"/>
       <c r="G257" s="16"/>
@@ -8811,16 +8975,16 @@
         <v>118</v>
       </c>
       <c r="B258" s="18" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C258" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D258" s="18" t="s">
-        <v>199</v>
+        <v>32</v>
+      </c>
+      <c r="D258" t="s">
+        <v>1109</v>
       </c>
       <c r="E258" s="18" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F258" s="16"/>
       <c r="G258" s="16"/>
@@ -8830,16 +8994,16 @@
         <v>118</v>
       </c>
       <c r="B259" s="18" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C259" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D259" s="18" t="s">
-        <v>199</v>
+        <v>34</v>
+      </c>
+      <c r="D259" t="s">
+        <v>1109</v>
       </c>
       <c r="E259" s="18" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="F259" s="16"/>
       <c r="G259" s="16"/>
@@ -8849,16 +9013,16 @@
         <v>118</v>
       </c>
       <c r="B260" s="18" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C260" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D260" s="18" t="s">
-        <v>199</v>
+        <v>36</v>
+      </c>
+      <c r="D260" t="s">
+        <v>1109</v>
       </c>
       <c r="E260" s="18" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="F260" s="16"/>
       <c r="G260" s="16"/>
@@ -8868,16 +9032,16 @@
         <v>118</v>
       </c>
       <c r="B261" s="18" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C261" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D261" s="18" t="s">
-        <v>199</v>
+        <v>38</v>
+      </c>
+      <c r="D261" t="s">
+        <v>1109</v>
       </c>
       <c r="E261" s="18" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F261" s="16"/>
       <c r="G261" s="16"/>
@@ -8887,16 +9051,16 @@
         <v>118</v>
       </c>
       <c r="B262" s="18" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C262" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D262" s="18" t="s">
-        <v>199</v>
+        <v>150</v>
+      </c>
+      <c r="D262" t="s">
+        <v>1109</v>
       </c>
       <c r="E262" s="18" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F262" s="16"/>
       <c r="G262" s="16"/>
@@ -8905,55 +9069,63 @@
       <c r="A263" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="B263" s="18" t="s">
-        <v>52</v>
+      <c r="B263" s="28" t="s">
+        <v>40</v>
       </c>
       <c r="C263" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D263" s="18" t="s">
-        <v>199</v>
+        <v>4</v>
+      </c>
+      <c r="D263" t="s">
+        <v>1109</v>
       </c>
       <c r="E263" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F263" s="16"/>
-      <c r="G263" s="16"/>
+        <v>169</v>
+      </c>
+      <c r="F263" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G263" s="16" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="264" spans="1:7">
       <c r="A264" s="18" t="s">
         <v>118</v>
       </c>
       <c r="B264" s="18" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C264" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D264" s="18" t="s">
-        <v>199</v>
+        <v>8</v>
+      </c>
+      <c r="D264" t="s">
+        <v>1109</v>
       </c>
       <c r="E264" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="F264" s="16"/>
-      <c r="G264" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="F264" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G264" s="16" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="265" spans="1:7">
       <c r="A265" s="18" t="s">
         <v>118</v>
       </c>
       <c r="B265" s="18" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C265" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D265" s="18" t="s">
-        <v>199</v>
+        <v>11</v>
+      </c>
+      <c r="D265" t="s">
+        <v>1109</v>
       </c>
       <c r="E265" s="18" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="F265" s="16"/>
       <c r="G265" s="16"/>
@@ -8963,320 +9135,288 @@
         <v>118</v>
       </c>
       <c r="B266" s="18" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C266" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="D266" s="18" t="s">
-        <v>199</v>
+        <v>13</v>
+      </c>
+      <c r="D266" t="s">
+        <v>1109</v>
       </c>
       <c r="E266" s="18" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="F266" s="16"/>
       <c r="G266" s="16"/>
     </row>
     <row r="267" spans="1:7">
       <c r="A267" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B267" s="18" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C267" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D267" s="18" t="s">
-        <v>200</v>
+        <v>15</v>
+      </c>
+      <c r="D267" t="s">
+        <v>1109</v>
       </c>
       <c r="E267" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="F267" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G267" s="16" t="s">
-        <v>58</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="F267" s="16"/>
+      <c r="G267" s="16"/>
     </row>
     <row r="268" spans="1:7">
       <c r="A268" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B268" s="18" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C268" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D268" s="18" t="s">
-        <v>200</v>
+        <v>17</v>
+      </c>
+      <c r="D268" t="s">
+        <v>1109</v>
       </c>
       <c r="E268" s="18" t="s">
-        <v>622</v>
+        <v>152</v>
       </c>
       <c r="F268" s="16"/>
       <c r="G268" s="16"/>
     </row>
     <row r="269" spans="1:7">
       <c r="A269" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B269" s="18" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C269" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D269" s="18" t="s">
-        <v>200</v>
+        <v>18</v>
+      </c>
+      <c r="D269" t="s">
+        <v>1109</v>
       </c>
       <c r="E269" s="18" t="s">
-        <v>623</v>
-      </c>
-      <c r="F269" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G269" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="F269" s="16"/>
+      <c r="G269" s="16"/>
     </row>
     <row r="270" spans="1:7">
       <c r="A270" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B270" s="18" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C270" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D270" s="18" t="s">
-        <v>200</v>
+        <v>22</v>
+      </c>
+      <c r="D270" t="s">
+        <v>1109</v>
       </c>
       <c r="E270" s="18" t="s">
-        <v>627</v>
+        <v>154</v>
       </c>
       <c r="F270" s="16"/>
       <c r="G270" s="16"/>
     </row>
     <row r="271" spans="1:7">
       <c r="A271" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B271" s="18" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C271" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D271" s="18" t="s">
-        <v>200</v>
+        <v>24</v>
+      </c>
+      <c r="D271" t="s">
+        <v>1109</v>
       </c>
       <c r="E271" s="18" t="s">
-        <v>626</v>
-      </c>
-      <c r="F271" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G271" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="F271" s="16"/>
+      <c r="G271" s="16"/>
     </row>
     <row r="272" spans="1:7">
       <c r="A272" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B272" s="18" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="C272" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D272" s="18" t="s">
-        <v>200</v>
+        <v>26</v>
+      </c>
+      <c r="D272" t="s">
+        <v>1109</v>
       </c>
       <c r="E272" s="18" t="s">
-        <v>624</v>
+        <v>156</v>
       </c>
       <c r="F272" s="16"/>
       <c r="G272" s="16"/>
     </row>
     <row r="273" spans="1:7">
       <c r="A273" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B273" s="18" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="C273" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D273" s="18" t="s">
-        <v>200</v>
+        <v>28</v>
+      </c>
+      <c r="D273" t="s">
+        <v>1109</v>
       </c>
       <c r="E273" s="18" t="s">
-        <v>625</v>
-      </c>
-      <c r="F273" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G273" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="F273" s="16"/>
+      <c r="G273" s="16"/>
     </row>
     <row r="274" spans="1:7">
       <c r="A274" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B274" s="18" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="C274" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D274" s="18" t="s">
-        <v>200</v>
+        <v>30</v>
+      </c>
+      <c r="D274" t="s">
+        <v>1109</v>
       </c>
       <c r="E274" s="18" t="s">
-        <v>629</v>
+        <v>158</v>
       </c>
       <c r="F274" s="16"/>
       <c r="G274" s="16"/>
     </row>
     <row r="275" spans="1:7">
       <c r="A275" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B275" s="18" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="C275" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D275" s="18" t="s">
-        <v>200</v>
+        <v>32</v>
+      </c>
+      <c r="D275" t="s">
+        <v>1109</v>
       </c>
       <c r="E275" s="18" t="s">
-        <v>630</v>
-      </c>
-      <c r="F275" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G275" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="F275" s="16"/>
+      <c r="G275" s="16"/>
     </row>
     <row r="276" spans="1:7">
       <c r="A276" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B276" s="18" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="C276" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D276" s="18" t="s">
-        <v>200</v>
+        <v>34</v>
+      </c>
+      <c r="D276" t="s">
+        <v>1109</v>
       </c>
       <c r="E276" s="18" t="s">
-        <v>628</v>
+        <v>160</v>
       </c>
       <c r="F276" s="16"/>
       <c r="G276" s="16"/>
     </row>
     <row r="277" spans="1:7">
       <c r="A277" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B277" s="18" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C277" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D277" s="18" t="s">
-        <v>200</v>
+        <v>36</v>
+      </c>
+      <c r="D277" t="s">
+        <v>1109</v>
       </c>
       <c r="E277" s="18" t="s">
-        <v>631</v>
-      </c>
-      <c r="F277" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G277" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="F277" s="16"/>
+      <c r="G277" s="16"/>
     </row>
     <row r="278" spans="1:7">
       <c r="A278" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B278" s="18" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="C278" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D278" s="18" t="s">
-        <v>200</v>
+        <v>38</v>
+      </c>
+      <c r="D278" t="s">
+        <v>1109</v>
       </c>
       <c r="E278" s="18" t="s">
-        <v>684</v>
-      </c>
-      <c r="F278" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G278" s="16" t="s">
-        <v>82</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="F278" s="16"/>
+      <c r="G278" s="16"/>
     </row>
     <row r="279" spans="1:7">
       <c r="A279" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B279" s="18" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="C279" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D279" s="18" t="s">
-        <v>200</v>
+        <v>150</v>
+      </c>
+      <c r="D279" t="s">
+        <v>1109</v>
       </c>
       <c r="E279" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="F279" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G279" s="16" t="s">
-        <v>85</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="F279" s="16"/>
+      <c r="G279" s="16"/>
     </row>
     <row r="280" spans="1:7">
       <c r="A280" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B280" s="18" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="C280" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D280" s="18" t="s">
-        <v>200</v>
+        <v>56</v>
+      </c>
+      <c r="D280" t="s">
+        <v>1107</v>
       </c>
       <c r="E280" s="18" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F280" s="16" t="s">
         <v>6</v>
       </c>
       <c r="G280" s="16" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -9284,45 +9424,41 @@
         <v>282</v>
       </c>
       <c r="B281" s="18" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="C281" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D281" s="18" t="s">
-        <v>200</v>
+        <v>59</v>
+      </c>
+      <c r="D281" t="s">
+        <v>1107</v>
       </c>
       <c r="E281" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="F281" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G281" s="16" t="s">
-        <v>91</v>
-      </c>
+        <v>622</v>
+      </c>
+      <c r="F281" s="16"/>
+      <c r="G281" s="16"/>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B282" s="18" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="C282" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D282" s="18" t="s">
-        <v>200</v>
+        <v>61</v>
+      </c>
+      <c r="D282" t="s">
+        <v>1107</v>
       </c>
       <c r="E282" s="18" t="s">
-        <v>205</v>
+        <v>623</v>
       </c>
       <c r="F282" s="16" t="s">
         <v>6</v>
       </c>
       <c r="G282" s="16" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -9330,45 +9466,41 @@
         <v>282</v>
       </c>
       <c r="B283" s="18" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="C283" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D283" s="18" t="s">
-        <v>200</v>
+        <v>64</v>
+      </c>
+      <c r="D283" t="s">
+        <v>1107</v>
       </c>
       <c r="E283" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="F283" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G283" s="16" t="s">
-        <v>97</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="F283" s="16"/>
+      <c r="G283" s="16"/>
     </row>
     <row r="284" spans="1:7">
       <c r="A284" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B284" s="18" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="C284" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D284" s="18" t="s">
-        <v>200</v>
+        <v>66</v>
+      </c>
+      <c r="D284" t="s">
+        <v>1107</v>
       </c>
       <c r="E284" s="18" t="s">
-        <v>207</v>
+        <v>626</v>
       </c>
       <c r="F284" s="16" t="s">
         <v>6</v>
       </c>
       <c r="G284" s="16" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -9376,45 +9508,41 @@
         <v>282</v>
       </c>
       <c r="B285" s="18" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="C285" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D285" s="18" t="s">
-        <v>200</v>
+        <v>68</v>
+      </c>
+      <c r="D285" t="s">
+        <v>1107</v>
       </c>
       <c r="E285" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="F285" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G285" s="16" t="s">
-        <v>103</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="F285" s="16"/>
+      <c r="G285" s="16"/>
     </row>
     <row r="286" spans="1:7">
       <c r="A286" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B286" s="18" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="C286" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D286" s="18" t="s">
-        <v>200</v>
+        <v>70</v>
+      </c>
+      <c r="D286" t="s">
+        <v>1107</v>
       </c>
       <c r="E286" s="18" t="s">
-        <v>209</v>
+        <v>625</v>
       </c>
       <c r="F286" s="16" t="s">
         <v>6</v>
       </c>
       <c r="G286" s="16" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -9422,16 +9550,16 @@
         <v>282</v>
       </c>
       <c r="B287" s="18" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="C287" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D287" s="18" t="s">
-        <v>200</v>
+        <v>72</v>
+      </c>
+      <c r="D287" t="s">
+        <v>1107</v>
       </c>
       <c r="E287" s="18" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F287" s="16"/>
       <c r="G287" s="16"/>
@@ -9441,16 +9569,16 @@
         <v>282</v>
       </c>
       <c r="B288" s="18" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C288" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D288" s="18" t="s">
-        <v>200</v>
+        <v>74</v>
+      </c>
+      <c r="D288" t="s">
+        <v>1107</v>
       </c>
       <c r="E288" s="18" t="s">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="F288" s="16" t="s">
         <v>6</v>
@@ -9464,16 +9592,16 @@
         <v>282</v>
       </c>
       <c r="B289" s="18" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C289" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D289" s="18" t="s">
-        <v>200</v>
+        <v>76</v>
+      </c>
+      <c r="D289" t="s">
+        <v>1107</v>
       </c>
       <c r="E289" s="18" t="s">
-        <v>682</v>
+        <v>628</v>
       </c>
       <c r="F289" s="16"/>
       <c r="G289" s="16"/>
@@ -9483,16 +9611,16 @@
         <v>282</v>
       </c>
       <c r="B290" s="18" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="C290" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D290" s="18" t="s">
-        <v>200</v>
+        <v>78</v>
+      </c>
+      <c r="D290" t="s">
+        <v>1107</v>
       </c>
       <c r="E290" s="18" t="s">
-        <v>681</v>
+        <v>631</v>
       </c>
       <c r="F290" s="16" t="s">
         <v>6</v>
@@ -9506,21 +9634,312 @@
         <v>282</v>
       </c>
       <c r="B291" s="18" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="C291" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="D291" s="18" t="s">
-        <v>200</v>
+        <v>80</v>
+      </c>
+      <c r="D291" t="s">
+        <v>1107</v>
       </c>
       <c r="E291" s="18" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F291" s="16" t="s">
         <v>6</v>
       </c>
       <c r="G291" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B292" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C292" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D292" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E292" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="F292" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G292" s="16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B293" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C293" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D293" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E293" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="F293" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G293" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B294" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C294" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D294" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E294" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="F294" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G294" s="16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B295" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C295" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D295" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E295" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="F295" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G295" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B296" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C296" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D296" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E296" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="F296" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G296" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B297" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C297" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D297" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E297" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="F297" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G297" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B298" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C298" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D298" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E298" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="F298" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G298" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B299" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C299" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D299" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E299" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="F299" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G299" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B300" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C300" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D300" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E300" s="18" t="s">
+        <v>632</v>
+      </c>
+      <c r="F300" s="16"/>
+      <c r="G300" s="16"/>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B301" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C301" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D301" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E301" s="18" t="s">
+        <v>680</v>
+      </c>
+      <c r="F301" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G301" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B302" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C302" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D302" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E302" s="18" t="s">
+        <v>682</v>
+      </c>
+      <c r="F302" s="16"/>
+      <c r="G302" s="16"/>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B303" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C303" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D303" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E303" s="18" t="s">
+        <v>681</v>
+      </c>
+      <c r="F303" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G303" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B304" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C304" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D304" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E304" s="18" t="s">
+        <v>683</v>
+      </c>
+      <c r="F304" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G304" s="16" t="s">
         <v>117</v>
       </c>
     </row>
@@ -9530,6 +9949,1174 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB9E522F-7F91-A843-B49B-20AEA4844ADA}">
+  <dimension ref="H1:K152"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
+  <cols>
+    <col min="8" max="8" width="32.1640625" style="34" customWidth="1"/>
+    <col min="9" max="9" width="29.6640625" style="35" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="8:11">
+      <c r="H1" s="33" t="s">
+        <v>1130</v>
+      </c>
+      <c r="I1" s="36" t="str" cm="1">
+        <f t="array" ref="I1:I124">_xlfn.UNIQUE(H1:H200)</f>
+        <v>q_alc_any_life</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="2" spans="8:11">
+      <c r="H2" s="33" t="s">
+        <v>1130</v>
+      </c>
+      <c r="I2" s="36" t="str">
+        <v>q_alc_any_yr</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="3" spans="8:11">
+      <c r="H3" s="33" t="s">
+        <v>1129</v>
+      </c>
+      <c r="I3" s="36" t="str">
+        <v>q_alc_drinksday</v>
+      </c>
+      <c r="K3" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="4" spans="8:11">
+      <c r="H4" s="33" t="s">
+        <v>1129</v>
+      </c>
+      <c r="I4" s="36" t="str">
+        <v>q_alc_freq</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="5" spans="8:11">
+      <c r="H5" s="33" t="s">
+        <v>1129</v>
+      </c>
+      <c r="I5" s="36" t="str">
+        <v>q_alc_freq_units</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="6" spans="8:11">
+      <c r="H6" s="33" t="s">
+        <v>909</v>
+      </c>
+      <c r="I6" s="35" t="str">
+        <v>q_anxiety</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="7" spans="8:11">
+      <c r="H7" s="33" t="s">
+        <v>907</v>
+      </c>
+      <c r="I7" s="36" t="str">
+        <v>q_commmute_bike_minday</v>
+      </c>
+    </row>
+    <row r="8" spans="8:11">
+      <c r="H8" s="33" t="s">
+        <v>907</v>
+      </c>
+      <c r="I8" s="36" t="str">
+        <v>q_commute_bike_freq</v>
+      </c>
+    </row>
+    <row r="9" spans="8:11">
+      <c r="H9" s="33" t="s">
+        <v>908</v>
+      </c>
+      <c r="I9" s="36" t="str">
+        <v>q_commute_bike_yn</v>
+      </c>
+    </row>
+    <row r="10" spans="8:11">
+      <c r="H10" s="33" t="s">
+        <v>900</v>
+      </c>
+      <c r="I10" s="35" t="str">
+        <v>q_depress</v>
+      </c>
+    </row>
+    <row r="11" spans="8:11">
+      <c r="H11" s="33" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I11" s="35" t="str">
+        <v>q_feel_riskdiab</v>
+      </c>
+    </row>
+    <row r="12" spans="8:11">
+      <c r="H12" s="33" t="s">
+        <v>989</v>
+      </c>
+      <c r="I12" s="35" t="str">
+        <v>q_genhealth_rating</v>
+      </c>
+    </row>
+    <row r="13" spans="8:11">
+      <c r="H13" s="33" t="s">
+        <v>998</v>
+      </c>
+      <c r="I13" s="35" t="str">
+        <v>q_govtmeal</v>
+      </c>
+    </row>
+    <row r="14" spans="8:11">
+      <c r="H14" s="33" t="s">
+        <v>897</v>
+      </c>
+      <c r="I14" s="35" t="str">
+        <v>q_had_dialysis</v>
+      </c>
+    </row>
+    <row r="15" spans="8:11">
+      <c r="H15" s="33" t="s">
+        <v>863</v>
+      </c>
+      <c r="I15" s="35" t="str">
+        <v>q_hc_admissions_pastyr</v>
+      </c>
+    </row>
+    <row r="16" spans="8:11">
+      <c r="H16" s="33" t="s">
+        <v>934</v>
+      </c>
+      <c r="I16" s="35" t="str">
+        <v>q_hc_admit</v>
+      </c>
+    </row>
+    <row r="17" spans="8:9">
+      <c r="H17" s="33" t="s">
+        <v>905</v>
+      </c>
+      <c r="I17" s="35" t="str">
+        <v>q_hc_drvisit</v>
+      </c>
+    </row>
+    <row r="18" spans="8:9">
+      <c r="H18" s="33" t="s">
+        <v>905</v>
+      </c>
+      <c r="I18" s="35" t="str">
+        <v>q_hc_place</v>
+      </c>
+    </row>
+    <row r="19" spans="8:9">
+      <c r="H19" s="33" t="s">
+        <v>876</v>
+      </c>
+      <c r="I19" s="35" t="str">
+        <v>q_hc_place_type</v>
+      </c>
+    </row>
+    <row r="20" spans="8:9">
+      <c r="H20" s="33" t="s">
+        <v>945</v>
+      </c>
+      <c r="I20" s="35" t="str">
+        <v>q_hh_foodsec</v>
+      </c>
+    </row>
+    <row r="21" spans="8:9">
+      <c r="H21" s="33" t="s">
+        <v>949</v>
+      </c>
+      <c r="I21" s="35" t="str">
+        <v>q_icd1</v>
+      </c>
+    </row>
+    <row r="22" spans="8:9">
+      <c r="H22" s="33" t="s">
+        <v>949</v>
+      </c>
+      <c r="I22" s="35" t="str">
+        <v>q_icd2</v>
+      </c>
+    </row>
+    <row r="23" spans="8:9">
+      <c r="H23" s="33" t="s">
+        <v>953</v>
+      </c>
+      <c r="I23" s="35" t="str">
+        <v>q_icd3</v>
+      </c>
+    </row>
+    <row r="24" spans="8:9">
+      <c r="H24" s="33" t="s">
+        <v>953</v>
+      </c>
+      <c r="I24" s="35" t="str">
+        <v>q_insur_any</v>
+      </c>
+    </row>
+    <row r="25" spans="8:9">
+      <c r="H25" s="33" t="s">
+        <v>937</v>
+      </c>
+      <c r="I25" s="35" t="str">
+        <v>q_insur_private</v>
+      </c>
+    </row>
+    <row r="26" spans="8:9">
+      <c r="H26" s="33" t="s">
+        <v>938</v>
+      </c>
+      <c r="I26" s="35" t="str">
+        <v>q_med_asthma</v>
+      </c>
+    </row>
+    <row r="27" spans="8:9">
+      <c r="H27" s="33" t="s">
+        <v>938</v>
+      </c>
+      <c r="I27" s="35" t="str">
+        <v>q_med_bp</v>
+      </c>
+    </row>
+    <row r="28" spans="8:9">
+      <c r="H28" s="33" t="s">
+        <v>938</v>
+      </c>
+      <c r="I28" s="35" t="str">
+        <v>q_med_depress</v>
+      </c>
+    </row>
+    <row r="29" spans="8:9">
+      <c r="H29" s="33" t="s">
+        <v>915</v>
+      </c>
+      <c r="I29" s="35" t="str">
+        <v>q_med_diab</v>
+      </c>
+    </row>
+    <row r="30" spans="8:9">
+      <c r="H30" s="33" t="s">
+        <v>915</v>
+      </c>
+      <c r="I30" s="35" t="str">
+        <v>q_med_insulin</v>
+      </c>
+    </row>
+    <row r="31" spans="8:9">
+      <c r="H31" s="33" t="s">
+        <v>1117</v>
+      </c>
+      <c r="I31" s="35" t="str">
+        <v>q_mpa_recr_freq</v>
+      </c>
+    </row>
+    <row r="32" spans="8:9">
+      <c r="H32" s="33" t="s">
+        <v>1116</v>
+      </c>
+      <c r="I32" s="35" t="str">
+        <v>q_mpa_recr_minday</v>
+      </c>
+    </row>
+    <row r="33" spans="8:9">
+      <c r="H33" s="33" t="s">
+        <v>1118</v>
+      </c>
+      <c r="I33" s="35" t="str">
+        <v>q_mpa_recr_yn</v>
+      </c>
+    </row>
+    <row r="34" spans="8:9">
+      <c r="H34" s="33" t="s">
+        <v>925</v>
+      </c>
+      <c r="I34" s="35" t="str">
+        <v>q_mpa_work_dur</v>
+      </c>
+    </row>
+    <row r="35" spans="8:9">
+      <c r="H35" s="33" t="s">
+        <v>925</v>
+      </c>
+      <c r="I35" s="35" t="str">
+        <v>q_mpa_work_freq</v>
+      </c>
+    </row>
+    <row r="36" spans="8:9">
+      <c r="H36" s="33" t="s">
+        <v>926</v>
+      </c>
+      <c r="I36" s="35" t="str">
+        <v>q_mpa_work_yn</v>
+      </c>
+    </row>
+    <row r="37" spans="8:9">
+      <c r="H37" s="33" t="s">
+        <v>926</v>
+      </c>
+      <c r="I37" s="35" t="str">
+        <v>q_mvpa_anympa</v>
+      </c>
+    </row>
+    <row r="38" spans="8:9">
+      <c r="H38" s="33" t="s">
+        <v>926</v>
+      </c>
+      <c r="I38" s="35" t="str">
+        <v>q_mvpa_anyvpa</v>
+      </c>
+    </row>
+    <row r="39" spans="8:9">
+      <c r="H39" s="33" t="s">
+        <v>860</v>
+      </c>
+      <c r="I39" s="35" t="str">
+        <v>q_mvpa_dur</v>
+      </c>
+    </row>
+    <row r="40" spans="8:9">
+      <c r="H40" s="33" t="s">
+        <v>859</v>
+      </c>
+      <c r="I40" s="35" t="str">
+        <v>q_mvpa_freq</v>
+      </c>
+    </row>
+    <row r="41" spans="8:9">
+      <c r="H41" s="33" t="s">
+        <v>898</v>
+      </c>
+      <c r="I41" s="35" t="str">
+        <v>q_mvpa_mets</v>
+      </c>
+    </row>
+    <row r="42" spans="8:9">
+      <c r="H42" s="33" t="s">
+        <v>826</v>
+      </c>
+      <c r="I42" s="35" t="str">
+        <v>q_mvpa_type</v>
+      </c>
+    </row>
+    <row r="43" spans="8:9">
+      <c r="H43" s="33" t="s">
+        <v>826</v>
+      </c>
+      <c r="I43" s="35" t="str">
+        <v>q_phq_appetite</v>
+      </c>
+    </row>
+    <row r="44" spans="8:9">
+      <c r="H44" s="33" t="s">
+        <v>862</v>
+      </c>
+      <c r="I44" s="35" t="str">
+        <v>q_phq_check</v>
+      </c>
+    </row>
+    <row r="45" spans="8:9">
+      <c r="H45" s="33" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I45" s="35" t="str">
+        <v>q_phq_conc</v>
+      </c>
+    </row>
+    <row r="46" spans="8:9">
+      <c r="H46" s="33" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I46" s="35" t="str">
+        <v>q_phq_energy</v>
+      </c>
+    </row>
+    <row r="47" spans="8:9">
+      <c r="H47" s="33" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I47" s="35" t="str">
+        <v>q_phq_feelbad</v>
+      </c>
+    </row>
+    <row r="48" spans="8:9">
+      <c r="H48" s="33" t="s">
+        <v>981</v>
+      </c>
+      <c r="I48" s="35" t="str">
+        <v>q_phq_hope</v>
+      </c>
+    </row>
+    <row r="49" spans="8:9">
+      <c r="H49" s="33" t="s">
+        <v>978</v>
+      </c>
+      <c r="I49" s="35" t="str">
+        <v>q_phq_hurtself</v>
+      </c>
+    </row>
+    <row r="50" spans="8:9">
+      <c r="H50" s="33" t="s">
+        <v>997</v>
+      </c>
+      <c r="I50" s="35" t="str">
+        <v>q_phq_interest</v>
+      </c>
+    </row>
+    <row r="51" spans="8:9">
+      <c r="H51" s="33" t="s">
+        <v>1123</v>
+      </c>
+      <c r="I51" s="35" t="str">
+        <v>q_phq_sleep</v>
+      </c>
+    </row>
+    <row r="52" spans="8:9">
+      <c r="H52" s="33" t="s">
+        <v>1124</v>
+      </c>
+      <c r="I52" s="35" t="str">
+        <v>q_phq_slow</v>
+      </c>
+    </row>
+    <row r="53" spans="8:9">
+      <c r="H53" s="33" t="s">
+        <v>970</v>
+      </c>
+      <c r="I53" s="35" t="str">
+        <v>q_phq_work</v>
+      </c>
+    </row>
+    <row r="54" spans="8:9">
+      <c r="H54" s="33" t="s">
+        <v>969</v>
+      </c>
+      <c r="I54" s="35" t="str">
+        <v>q_restaur_week</v>
+      </c>
+    </row>
+    <row r="55" spans="8:9">
+      <c r="H55" s="33" t="s">
+        <v>971</v>
+      </c>
+      <c r="I55" s="35" t="str">
+        <v>q_riskdiab_age</v>
+      </c>
+    </row>
+    <row r="56" spans="8:9">
+      <c r="H56" s="33" t="s">
+        <v>968</v>
+      </c>
+      <c r="I56" s="35" t="str">
+        <v>q_riskdiab_anyone</v>
+      </c>
+    </row>
+    <row r="57" spans="8:9">
+      <c r="H57" s="33" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I57" s="35" t="str">
+        <v>q_riskdiab_bg</v>
+      </c>
+    </row>
+    <row r="58" spans="8:9">
+      <c r="H58" s="33" t="s">
+        <v>1084</v>
+      </c>
+      <c r="I58" s="35" t="str">
+        <v>q_riskdiab_blurvis</v>
+      </c>
+    </row>
+    <row r="59" spans="8:9">
+      <c r="H59" s="33" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I59" s="35" t="str">
+        <v>q_riskdiab_chol</v>
+      </c>
+    </row>
+    <row r="60" spans="8:9">
+      <c r="H60" s="33" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I60" s="35" t="str">
+        <v>q_riskdiab_craveswt</v>
+      </c>
+    </row>
+    <row r="61" spans="8:9">
+      <c r="H61" s="33" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I61" s="35" t="str">
+        <v>q_riskdiab_diet</v>
+      </c>
+    </row>
+    <row r="62" spans="8:9">
+      <c r="H62" s="33" t="s">
+        <v>1086</v>
+      </c>
+      <c r="I62" s="35" t="str">
+        <v>q_riskdiab_drwarn</v>
+      </c>
+    </row>
+    <row r="63" spans="8:9">
+      <c r="H63" s="33" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I63" s="35" t="str">
+        <v>q_riskdiab_fatigue</v>
+      </c>
+    </row>
+    <row r="64" spans="8:9">
+      <c r="H64" s="33" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I64" s="35" t="str">
+        <v>q_riskdiab_fh</v>
+      </c>
+    </row>
+    <row r="65" spans="8:9">
+      <c r="H65" s="33" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I65" s="35" t="str">
+        <v>q_riskdiab_gdm</v>
+      </c>
+    </row>
+    <row r="66" spans="8:9">
+      <c r="H66" s="33" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I66" s="35" t="str">
+        <v>q_riskdiab_htn</v>
+      </c>
+    </row>
+    <row r="67" spans="8:9">
+      <c r="H67" s="33" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I67" s="35" t="str">
+        <v>q_riskdiab_hunger</v>
+      </c>
+    </row>
+    <row r="68" spans="8:9">
+      <c r="H68" s="33" t="s">
+        <v>920</v>
+      </c>
+      <c r="I68" s="35" t="str">
+        <v>q_riskdiab_hypogly</v>
+      </c>
+    </row>
+    <row r="69" spans="8:9">
+      <c r="H69" s="33" t="s">
+        <v>920</v>
+      </c>
+      <c r="I69" s="35" t="str">
+        <v>q_riskdiab_lgababy</v>
+      </c>
+    </row>
+    <row r="70" spans="8:9">
+      <c r="H70" s="33" t="s">
+        <v>920</v>
+      </c>
+      <c r="I70" s="35" t="str">
+        <v>q_riskdiab_medrisk</v>
+      </c>
+    </row>
+    <row r="71" spans="8:9">
+      <c r="H71" s="33" t="s">
+        <v>803</v>
+      </c>
+      <c r="I71" s="35" t="str">
+        <v>q_riskdiab_other</v>
+      </c>
+    </row>
+    <row r="72" spans="8:9">
+      <c r="H72" s="33" t="s">
+        <v>816</v>
+      </c>
+      <c r="I72" s="35" t="str">
+        <v>q_riskdiab_pares</v>
+      </c>
+    </row>
+    <row r="73" spans="8:9">
+      <c r="H73" s="33" t="s">
+        <v>809</v>
+      </c>
+      <c r="I73" s="35" t="str">
+        <v>q_riskdiab_pcos</v>
+      </c>
+    </row>
+    <row r="74" spans="8:9">
+      <c r="H74" s="33" t="s">
+        <v>814</v>
+      </c>
+      <c r="I74" s="35" t="str">
+        <v>q_riskdiab_polydips</v>
+      </c>
+    </row>
+    <row r="75" spans="8:9">
+      <c r="H75" s="33" t="s">
+        <v>810</v>
+      </c>
+      <c r="I75" s="35" t="str">
+        <v>q_riskdiab_polyuria</v>
+      </c>
+    </row>
+    <row r="76" spans="8:9">
+      <c r="H76" s="33" t="s">
+        <v>822</v>
+      </c>
+      <c r="I76" s="35" t="str">
+        <v>q_riskdiab_race</v>
+      </c>
+    </row>
+    <row r="77" spans="8:9">
+      <c r="H77" s="33" t="s">
+        <v>804</v>
+      </c>
+      <c r="I77" s="35" t="str">
+        <v>q_riskdiab_sedent</v>
+      </c>
+    </row>
+    <row r="78" spans="8:9">
+      <c r="H78" s="33" t="s">
+        <v>817</v>
+      </c>
+      <c r="I78" s="35" t="str">
+        <v>q_riskdiab_wt</v>
+      </c>
+    </row>
+    <row r="79" spans="8:9">
+      <c r="H79" s="33" t="s">
+        <v>815</v>
+      </c>
+      <c r="I79" s="35" t="str">
+        <v>q_rx_drug</v>
+      </c>
+    </row>
+    <row r="80" spans="8:9">
+      <c r="H80" s="33" t="s">
+        <v>801</v>
+      </c>
+      <c r="I80" s="35" t="str">
+        <v>q_rx_drugid</v>
+      </c>
+    </row>
+    <row r="81" spans="8:9">
+      <c r="H81" s="33" t="s">
+        <v>819</v>
+      </c>
+      <c r="I81" s="35" t="str">
+        <v>q_rx_use</v>
+      </c>
+    </row>
+    <row r="82" spans="8:9">
+      <c r="H82" s="33" t="s">
+        <v>808</v>
+      </c>
+      <c r="I82" s="35" t="str">
+        <v>q_selfreport_ht</v>
+      </c>
+    </row>
+    <row r="83" spans="8:9">
+      <c r="H83" s="33" t="s">
+        <v>812</v>
+      </c>
+      <c r="I83" s="35" t="str">
+        <v>q_selfreport_wt</v>
+      </c>
+    </row>
+    <row r="84" spans="8:9">
+      <c r="H84" s="33" t="s">
+        <v>811</v>
+      </c>
+      <c r="I84" s="35" t="str">
+        <v>q_smoke_current</v>
+      </c>
+    </row>
+    <row r="85" spans="8:9">
+      <c r="H85" s="33" t="s">
+        <v>806</v>
+      </c>
+      <c r="I85" s="35" t="str">
+        <v>q_smoke_ever</v>
+      </c>
+    </row>
+    <row r="86" spans="8:9">
+      <c r="H86" s="33" t="s">
+        <v>823</v>
+      </c>
+      <c r="I86" s="35" t="str">
+        <v>q_sob_inclilne</v>
+      </c>
+    </row>
+    <row r="87" spans="8:9">
+      <c r="H87" s="33" t="s">
+        <v>818</v>
+      </c>
+      <c r="I87" s="35" t="str">
+        <v>q_told_angina</v>
+      </c>
+    </row>
+    <row r="88" spans="8:9">
+      <c r="H88" s="33" t="s">
+        <v>813</v>
+      </c>
+      <c r="I88" s="35" t="str">
+        <v>q_told_anybronch</v>
+      </c>
+    </row>
+    <row r="89" spans="8:9">
+      <c r="H89" s="33" t="s">
+        <v>824</v>
+      </c>
+      <c r="I89" s="35" t="str">
+        <v>q_told_bpmed</v>
+      </c>
+    </row>
+    <row r="90" spans="8:9">
+      <c r="H90" s="33" t="s">
+        <v>821</v>
+      </c>
+      <c r="I90" s="35" t="str">
+        <v>q_told_bronch</v>
+      </c>
+    </row>
+    <row r="91" spans="8:9">
+      <c r="H91" s="33" t="s">
+        <v>820</v>
+      </c>
+      <c r="I91" s="35" t="str">
+        <v>q_told_chd</v>
+      </c>
+    </row>
+    <row r="92" spans="8:9">
+      <c r="H92" s="33" t="s">
+        <v>805</v>
+      </c>
+      <c r="I92" s="35" t="str">
+        <v>q_told_chf</v>
+      </c>
+    </row>
+    <row r="93" spans="8:9">
+      <c r="H93" s="33" t="s">
+        <v>807</v>
+      </c>
+      <c r="I93" s="35" t="str">
+        <v>q_told_copd</v>
+      </c>
+    </row>
+    <row r="94" spans="8:9">
+      <c r="H94" s="33" t="s">
+        <v>802</v>
+      </c>
+      <c r="I94" s="35" t="str">
+        <v>q_told_diab</v>
+      </c>
+    </row>
+    <row r="95" spans="8:9">
+      <c r="H95" s="33" t="s">
+        <v>748</v>
+      </c>
+      <c r="I95" s="35" t="str">
+        <v>q_told_diab_age</v>
+      </c>
+    </row>
+    <row r="96" spans="8:9">
+      <c r="H96" s="33" t="s">
+        <v>749</v>
+      </c>
+      <c r="I96" s="35" t="str">
+        <v>q_told_diab_age1</v>
+      </c>
+    </row>
+    <row r="97" spans="8:9">
+      <c r="H97" s="33" t="s">
+        <v>747</v>
+      </c>
+      <c r="I97" s="35" t="str">
+        <v>q_told_diab_age2</v>
+      </c>
+    </row>
+    <row r="98" spans="8:9">
+      <c r="H98" s="33" t="s">
+        <v>887</v>
+      </c>
+      <c r="I98" s="35" t="str">
+        <v>q_told_emphys</v>
+      </c>
+    </row>
+    <row r="99" spans="8:9">
+      <c r="H99" s="33" t="s">
+        <v>888</v>
+      </c>
+      <c r="I99" s="35" t="str">
+        <v>q_told_htn</v>
+      </c>
+    </row>
+    <row r="100" spans="8:9">
+      <c r="H100" s="33" t="s">
+        <v>910</v>
+      </c>
+      <c r="I100" s="35" t="str">
+        <v>q_told_htn_x2+</v>
+      </c>
+    </row>
+    <row r="101" spans="8:9">
+      <c r="H101" s="33" t="s">
+        <v>901</v>
+      </c>
+      <c r="I101" s="35" t="str">
+        <v>q_told_kidfail</v>
+      </c>
+    </row>
+    <row r="102" spans="8:9">
+      <c r="H102" s="33" t="s">
+        <v>911</v>
+      </c>
+      <c r="I102" s="35" t="str">
+        <v>q_told_mi</v>
+      </c>
+    </row>
+    <row r="103" spans="8:9">
+      <c r="H103" s="33" t="s">
+        <v>868</v>
+      </c>
+      <c r="I103" s="35" t="str">
+        <v>q_told_overwt_gte20</v>
+      </c>
+    </row>
+    <row r="104" spans="8:9">
+      <c r="H104" s="33" t="s">
+        <v>868</v>
+      </c>
+      <c r="I104" s="35" t="str">
+        <v>q_told_overwt_lt20</v>
+      </c>
+    </row>
+    <row r="105" spans="8:9">
+      <c r="H105" s="33" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I105" s="35" t="str">
+        <v>q_told_prediabetes</v>
+      </c>
+    </row>
+    <row r="106" spans="8:9">
+      <c r="H106" s="33" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I106" s="35" t="str">
+        <v>q_told_riskdiab</v>
+      </c>
+    </row>
+    <row r="107" spans="8:9">
+      <c r="H107" s="33" t="s">
+        <v>895</v>
+      </c>
+      <c r="I107" s="35" t="str">
+        <v>q_told_stroke</v>
+      </c>
+    </row>
+    <row r="108" spans="8:9">
+      <c r="H108" s="33" t="s">
+        <v>791</v>
+      </c>
+      <c r="I108" s="35" t="str">
+        <v>q_told_stroke_age</v>
+      </c>
+    </row>
+    <row r="109" spans="8:9">
+      <c r="H109" s="33" t="s">
+        <v>791</v>
+      </c>
+      <c r="I109" s="35" t="str">
+        <v>q_uninsur_pastyr</v>
+      </c>
+    </row>
+    <row r="110" spans="8:9">
+      <c r="H110" s="33" t="s">
+        <v>788</v>
+      </c>
+      <c r="I110" s="35" t="str">
+        <v>q_vpa_recr_freq</v>
+      </c>
+    </row>
+    <row r="111" spans="8:9">
+      <c r="H111" s="33" t="s">
+        <v>788</v>
+      </c>
+      <c r="I111" s="35" t="str">
+        <v>q_vpa_recr_minday</v>
+      </c>
+    </row>
+    <row r="112" spans="8:9">
+      <c r="H112" s="33" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I112" s="35" t="str">
+        <v>q_vpa_recr_yn</v>
+      </c>
+    </row>
+    <row r="113" spans="8:9">
+      <c r="H113" s="33" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I113" s="35" t="str">
+        <v>q_vpa_work_dur</v>
+      </c>
+    </row>
+    <row r="114" spans="8:9">
+      <c r="H114" s="33" t="s">
+        <v>789</v>
+      </c>
+      <c r="I114" s="35" t="str">
+        <v>q_vpa_work_freq</v>
+      </c>
+    </row>
+    <row r="115" spans="8:9">
+      <c r="H115" s="33" t="s">
+        <v>789</v>
+      </c>
+      <c r="I115" s="35" t="str">
+        <v>q_vpa_work_yn</v>
+      </c>
+    </row>
+    <row r="116" spans="8:9">
+      <c r="H116" s="33" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I116" s="35" t="str">
+        <v>q_work_gt35hr</v>
+      </c>
+    </row>
+    <row r="117" spans="8:9">
+      <c r="H117" s="33" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I117" s="35" t="str">
+        <v>q_work_hrs</v>
+      </c>
+    </row>
+    <row r="118" spans="8:9">
+      <c r="H118" s="33" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I118" s="35" t="str">
+        <v>q_work_type</v>
+      </c>
+    </row>
+    <row r="119" spans="8:9">
+      <c r="H119" s="33" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I119" s="35" t="str">
+        <v>q_wtloss_dietrx</v>
+      </c>
+    </row>
+    <row r="120" spans="8:9">
+      <c r="H120" s="33" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I120" s="35" t="str">
+        <v>q_wtloss_dietsup</v>
+      </c>
+    </row>
+    <row r="121" spans="8:9">
+      <c r="H121" s="33" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I121" s="35" t="str">
+        <v>q_wtloss_eatless</v>
+      </c>
+    </row>
+    <row r="122" spans="8:9">
+      <c r="H122" s="33" t="s">
+        <v>790</v>
+      </c>
+      <c r="I122" s="35" t="str">
+        <v>q_wtloss_lessfat</v>
+      </c>
+    </row>
+    <row r="123" spans="8:9">
+      <c r="H123" s="33" t="s">
+        <v>790</v>
+      </c>
+      <c r="I123" s="35" t="str">
+        <v>q_wtloss_lowcal</v>
+      </c>
+    </row>
+    <row r="124" spans="8:9">
+      <c r="H124" s="33" t="s">
+        <v>861</v>
+      </c>
+      <c r="I124" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="8:9">
+      <c r="H125" s="33" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="126" spans="8:9">
+      <c r="H126" s="33" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="127" spans="8:9">
+      <c r="H127" s="33" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="128" spans="8:9">
+      <c r="H128" s="33" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="129" spans="8:8">
+      <c r="H129" s="33" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="130" spans="8:8">
+      <c r="H130" s="33" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="131" spans="8:8">
+      <c r="H131" s="33" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="132" spans="8:8">
+      <c r="H132" s="33" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="133" spans="8:8">
+      <c r="H133" s="33" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="134" spans="8:8">
+      <c r="H134" s="33" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="135" spans="8:8">
+      <c r="H135" s="33" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="136" spans="8:8">
+      <c r="H136" s="33" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="137" spans="8:8">
+      <c r="H137" s="33" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="138" spans="8:8">
+      <c r="H138" s="33" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="139" spans="8:8">
+      <c r="H139" s="33" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="140" spans="8:8">
+      <c r="H140" s="33" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="141" spans="8:8">
+      <c r="H141" s="33" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="142" spans="8:8">
+      <c r="H142" s="33" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="143" spans="8:8">
+      <c r="H143" s="33" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="144" spans="8:8">
+      <c r="H144" s="33" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="145" spans="8:8">
+      <c r="H145" s="33" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="146" spans="8:8">
+      <c r="H146" s="33" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="147" spans="8:8">
+      <c r="H147" s="33" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="148" spans="8:8">
+      <c r="H148" s="33" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="149" spans="8:8">
+      <c r="H149" s="33" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="150" spans="8:8">
+      <c r="H150" s="33" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="151" spans="8:8">
+      <c r="H151" s="33" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="152" spans="8:8">
+      <c r="H152" s="33" t="s">
+        <v>890</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H1:H152">
+    <sortCondition ref="H1:H152"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A63764-F0AB-1549-BAB2-B0DD4C1C3DF5}">
   <dimension ref="A1:G241"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -14036,7 +15623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBBF4455-AB7B-0A4A-A50B-43737E8D6EF1}">
   <dimension ref="A1:G329"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>

--- a/run/nhanes_pullrequest_IndVsArea_07.30.2026.xlsx
+++ b/run/nhanes_pullrequest_IndVsArea_07.30.2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jg1671/Documents/GitHub/nhanes_area_ses/run/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA9C5BD-9A37-FA41-9D67-B699D16BD182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F530924-341D-304A-8351-6104DA320730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36900" yWindow="2060" windowWidth="36800" windowHeight="21340" xr2:uid="{BFFDAA01-B797-C24A-A87F-A362CCE94DEB}"/>
+    <workbookView xWindow="30520" yWindow="2300" windowWidth="28800" windowHeight="16280" xr2:uid="{BFFDAA01-B797-C24A-A87F-A362CCE94DEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable_List" sheetId="6" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4399" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4499" uniqueCount="1198">
   <si>
     <t>RECODE</t>
   </si>
@@ -3396,24 +3396,6 @@
     <t>WTDR2D</t>
   </si>
   <si>
-    <t>RXDRSC1</t>
-  </si>
-  <si>
-    <t>RXDRSC3</t>
-  </si>
-  <si>
-    <t>RXDRSC2</t>
-  </si>
-  <si>
-    <t>ICD-10-CM code 3.</t>
-  </si>
-  <si>
-    <t>ICD-10-CM code 2.</t>
-  </si>
-  <si>
-    <t>ICD-10-CM code 1.</t>
-  </si>
-  <si>
     <t>q_icd2</t>
   </si>
   <si>
@@ -3499,6 +3481,183 @@
   </si>
   <si>
     <t>HUD070</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Main reason did not work last week</t>
+  </si>
+  <si>
+    <t>OCQ380</t>
+  </si>
+  <si>
+    <t>OCD150</t>
+  </si>
+  <si>
+    <t>q_work_lastwk</t>
+  </si>
+  <si>
+    <t>OCD241</t>
+  </si>
+  <si>
+    <t>What kind of work {were you/was SP} doing? (For example: farming, mail clerk, computer specialist.)</t>
+  </si>
+  <si>
+    <t>OCD240</t>
+  </si>
+  <si>
+    <t>q_nowork_reason</t>
+  </si>
+  <si>
+    <t>OCD180</t>
+  </si>
+  <si>
+    <t>OCD383</t>
+  </si>
+  <si>
+    <t>OCD210</t>
+  </si>
+  <si>
+    <t>DMDEDUC3</t>
+  </si>
+  <si>
+    <t>educ_20plus</t>
+  </si>
+  <si>
+    <t>educ_under20</t>
+  </si>
+  <si>
+    <t>CSQ080</t>
+  </si>
+  <si>
+    <t>Had problem with taste past 12 months?</t>
+  </si>
+  <si>
+    <t>CSQ090A</t>
+  </si>
+  <si>
+    <t>Ability to Taste Salt</t>
+  </si>
+  <si>
+    <t>CSQ090C</t>
+  </si>
+  <si>
+    <t>CSQ090B</t>
+  </si>
+  <si>
+    <t>Ability to Taste Sourness</t>
+  </si>
+  <si>
+    <t>Ability to Taste Sweetness</t>
+  </si>
+  <si>
+    <t>CSQ090D</t>
+  </si>
+  <si>
+    <t>Ability to Taste Bitterness</t>
+  </si>
+  <si>
+    <t>CSQ100</t>
+  </si>
+  <si>
+    <t>Change in ability to taste food flavors?</t>
+  </si>
+  <si>
+    <t>CSQ140</t>
+  </si>
+  <si>
+    <t>How long ago {did you/did SP} first notice a problem with, or a change in, {your/his/her} ability to taste?</t>
+  </si>
+  <si>
+    <t>q_tastechange_salt</t>
+  </si>
+  <si>
+    <t>q_tastechange_sour</t>
+  </si>
+  <si>
+    <t>q_tastechange_sweet</t>
+  </si>
+  <si>
+    <t>q_tastechange_bitter</t>
+  </si>
+  <si>
+    <t>q_tastechange_flavor</t>
+  </si>
+  <si>
+    <t>q_tastechange_time</t>
+  </si>
+  <si>
+    <t>q_tastechange_pastyr</t>
+  </si>
+  <si>
+    <t>Persistent cold/flu last 12 months?</t>
+  </si>
+  <si>
+    <t>CSQ200</t>
+  </si>
+  <si>
+    <t>Had persistent dry mouth in past 12 mth</t>
+  </si>
+  <si>
+    <t>CSQ202</t>
+  </si>
+  <si>
+    <t>CSQ204</t>
+  </si>
+  <si>
+    <t>Frequent nasal congestion in past 12 mth</t>
+  </si>
+  <si>
+    <t>CSQ210</t>
+  </si>
+  <si>
+    <t>Ever had Wisdom Teeth Removed</t>
+  </si>
+  <si>
+    <t>CSQ220</t>
+  </si>
+  <si>
+    <t>Ever had Tonsils Removed</t>
+  </si>
+  <si>
+    <t>Head Injury/Loss of counsciousness</t>
+  </si>
+  <si>
+    <t>CSQ240</t>
+  </si>
+  <si>
+    <t>Broke Nose/Serious Injury to Face/Skull</t>
+  </si>
+  <si>
+    <t>CSQ250</t>
+  </si>
+  <si>
+    <t>Ever had two or more sinus infections</t>
+  </si>
+  <si>
+    <t>CSQ260</t>
+  </si>
+  <si>
+    <t>q_csq_cold</t>
+  </si>
+  <si>
+    <t>q_csq_drymouth</t>
+  </si>
+  <si>
+    <t>q_csq_wisdomteeth</t>
+  </si>
+  <si>
+    <t>q_csq_congest</t>
+  </si>
+  <si>
+    <t>q_csq_tonsils</t>
+  </si>
+  <si>
+    <t>q_csq_headinj</t>
+  </si>
+  <si>
+    <t>q_csq_faceinj</t>
+  </si>
+  <si>
+    <t>q_csq_sinusinfect</t>
   </si>
 </sst>
 </file>
@@ -4054,7 +4213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3D6F9ED-9DEC-0147-B030-50BD2869D005}">
-  <dimension ref="A1:G304"/>
+  <dimension ref="A1:G324"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="19.5" style="5" customWidth="1"/>
@@ -4347,7 +4506,7 @@
         <v>1106</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>190</v>
+        <v>1151</v>
       </c>
       <c r="F15" s="20"/>
       <c r="G15" s="20"/>
@@ -4357,16 +4516,16 @@
         <v>121</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>186</v>
+        <v>1150</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
         <v>1106</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>220</v>
+        <v>1152</v>
       </c>
       <c r="F16" s="20"/>
       <c r="G16" s="20"/>
@@ -4376,16 +4535,16 @@
         <v>121</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D17" t="s">
         <v>1106</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F17" s="20"/>
       <c r="G17" s="20"/>
@@ -4395,16 +4554,16 @@
         <v>121</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s">
         <v>1106</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
@@ -4414,7 +4573,7 @@
         <v>121</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>187</v>
@@ -4423,7 +4582,7 @@
         <v>1106</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="F19" s="20"/>
       <c r="G19" s="20"/>
@@ -4433,7 +4592,7 @@
         <v>121</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>192</v>
@@ -4452,16 +4611,16 @@
         <v>121</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="D21" t="s">
         <v>1106</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
@@ -4471,7 +4630,7 @@
         <v>121</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C22" s="18" t="s">
         <v>222</v>
@@ -4490,34 +4649,36 @@
         <v>121</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>654</v>
+        <v>219</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>655</v>
+        <v>222</v>
       </c>
       <c r="D23" t="s">
         <v>1106</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>656</v>
+        <v>285</v>
       </c>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="18" t="s">
-        <v>224</v>
+        <v>121</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>227</v>
+        <v>654</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>704</v>
-      </c>
-      <c r="E24" s="18"/>
+        <v>655</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>656</v>
+      </c>
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
     </row>
@@ -4526,17 +4687,15 @@
         <v>224</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="D25" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>827</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>704</v>
+      </c>
+      <c r="E25" s="18"/>
       <c r="F25" s="20"/>
       <c r="G25" s="20"/>
     </row>
@@ -4545,18 +4704,18 @@
         <v>224</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1107</v>
+        <v>225</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>227</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>828</v>
-      </c>
-      <c r="F26" s="16"/>
+        <v>827</v>
+      </c>
+      <c r="F26" s="20"/>
       <c r="G26" s="20"/>
     </row>
     <row r="27" spans="1:7">
@@ -4564,16 +4723,16 @@
         <v>224</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D27" t="s">
         <v>1107</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>1013</v>
+        <v>828</v>
       </c>
       <c r="F27" s="16"/>
       <c r="G27" s="20"/>
@@ -4583,16 +4742,16 @@
         <v>224</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D28" t="s">
         <v>1107</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>829</v>
+        <v>1013</v>
       </c>
       <c r="F28" s="16"/>
       <c r="G28" s="20"/>
@@ -4602,16 +4761,16 @@
         <v>224</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D29" t="s">
         <v>1107</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="F29" s="16"/>
       <c r="G29" s="20"/>
@@ -4621,16 +4780,16 @@
         <v>224</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="D30" t="s">
         <v>1107</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="F30" s="16"/>
       <c r="G30" s="20"/>
@@ -4640,16 +4799,16 @@
         <v>224</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>239</v>
+        <v>281</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="D31" t="s">
         <v>1107</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F31" s="16"/>
       <c r="G31" s="20"/>
@@ -4659,16 +4818,16 @@
         <v>224</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D32" t="s">
         <v>1107</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F32" s="16"/>
       <c r="G32" s="20"/>
@@ -4678,16 +4837,16 @@
         <v>224</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D33" t="s">
         <v>1107</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="F33" s="16"/>
       <c r="G33" s="20"/>
@@ -4697,16 +4856,16 @@
         <v>224</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D34" t="s">
         <v>1107</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F34" s="16"/>
       <c r="G34" s="20"/>
@@ -4716,16 +4875,16 @@
         <v>224</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D35" t="s">
         <v>1107</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="F35" s="16"/>
       <c r="G35" s="20"/>
@@ -4735,16 +4894,16 @@
         <v>224</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D36" t="s">
         <v>1107</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="F36" s="16"/>
       <c r="G36" s="20"/>
@@ -4754,54 +4913,54 @@
         <v>224</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>710</v>
+        <v>249</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>711</v>
+        <v>250</v>
       </c>
       <c r="D37" t="s">
         <v>1107</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
+      <c r="G37" s="20"/>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="18" t="s">
         <v>224</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>708</v>
-      </c>
-      <c r="D38" s="28" t="s">
-        <v>227</v>
+        <v>711</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1107</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F38" s="16"/>
-      <c r="G38" s="20"/>
+      <c r="G38" s="16"/>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="18" t="s">
         <v>224</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>279</v>
+        <v>707</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="D39" t="s">
-        <v>1107</v>
+        <v>708</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>227</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F39" s="16"/>
       <c r="G39" s="20"/>
@@ -4811,16 +4970,16 @@
         <v>224</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D40" t="s">
         <v>1107</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="F40" s="16"/>
       <c r="G40" s="20"/>
@@ -4830,16 +4989,16 @@
         <v>224</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D41" t="s">
         <v>1107</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="F41" s="16"/>
       <c r="G41" s="20"/>
@@ -4849,16 +5008,16 @@
         <v>224</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="D42" t="s">
         <v>1107</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F42" s="16"/>
       <c r="G42" s="20"/>
@@ -4868,16 +5027,16 @@
         <v>224</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>398</v>
+        <v>287</v>
       </c>
       <c r="D43" t="s">
         <v>1107</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F43" s="16"/>
       <c r="G43" s="20"/>
@@ -4886,17 +5045,17 @@
       <c r="A44" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="B44" s="18" t="s">
-        <v>291</v>
+      <c r="B44" s="28" t="s">
+        <v>290</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>276</v>
+        <v>398</v>
       </c>
       <c r="D44" t="s">
         <v>1107</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F44" s="16"/>
       <c r="G44" s="20"/>
@@ -4906,7 +5065,7 @@
         <v>224</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C45" s="18" t="s">
         <v>276</v>
@@ -4925,18 +5084,18 @@
         <v>224</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>349</v>
+        <v>292</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>468</v>
+        <v>276</v>
       </c>
       <c r="D46" t="s">
         <v>1107</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>846</v>
-      </c>
-      <c r="F46" s="20"/>
+        <v>845</v>
+      </c>
+      <c r="F46" s="16"/>
       <c r="G46" s="20"/>
     </row>
     <row r="47" spans="1:7">
@@ -4944,16 +5103,16 @@
         <v>224</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>293</v>
+        <v>349</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>1029</v>
+        <v>468</v>
       </c>
       <c r="D47" t="s">
         <v>1107</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>1030</v>
+        <v>846</v>
       </c>
       <c r="F47" s="20"/>
       <c r="G47" s="20"/>
@@ -4963,16 +5122,16 @@
         <v>224</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>779</v>
+        <v>293</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>778</v>
+        <v>1029</v>
       </c>
       <c r="D48" t="s">
         <v>1107</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>847</v>
+        <v>1030</v>
       </c>
       <c r="F48" s="20"/>
       <c r="G48" s="20"/>
@@ -4982,16 +5141,16 @@
         <v>224</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>294</v>
+        <v>779</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>399</v>
+        <v>778</v>
       </c>
       <c r="D49" t="s">
         <v>1107</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>858</v>
+        <v>847</v>
       </c>
       <c r="F49" s="20"/>
       <c r="G49" s="20"/>
@@ -5001,16 +5160,16 @@
         <v>224</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D50" t="s">
         <v>1107</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="F50" s="20"/>
       <c r="G50" s="20"/>
@@ -5020,16 +5179,16 @@
         <v>224</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D51" t="s">
         <v>1107</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F51" s="20"/>
       <c r="G51" s="20"/>
@@ -5039,16 +5198,16 @@
         <v>224</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D52" t="s">
         <v>1107</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F52" s="20"/>
       <c r="G52" s="20"/>
@@ -5058,7 +5217,7 @@
         <v>224</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>402</v>
@@ -5077,16 +5236,16 @@
         <v>224</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D54" t="s">
         <v>1107</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="F54" s="20"/>
       <c r="G54" s="20"/>
@@ -5096,16 +5255,16 @@
         <v>224</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>784</v>
+        <v>299</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>785</v>
+        <v>403</v>
       </c>
       <c r="D55" t="s">
         <v>1107</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F55" s="20"/>
       <c r="G55" s="20"/>
@@ -5115,16 +5274,16 @@
         <v>224</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>406</v>
+        <v>784</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>407</v>
+        <v>785</v>
       </c>
       <c r="D56" t="s">
         <v>1107</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="F56" s="20"/>
       <c r="G56" s="20"/>
@@ -5134,16 +5293,16 @@
         <v>224</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>786</v>
+        <v>406</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>787</v>
+        <v>407</v>
       </c>
       <c r="D57" t="s">
         <v>1107</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="F57" s="20"/>
       <c r="G57" s="20"/>
@@ -5153,16 +5312,16 @@
         <v>224</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>408</v>
+        <v>786</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>409</v>
+        <v>787</v>
       </c>
       <c r="D58" t="s">
         <v>1107</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="F58" s="20"/>
       <c r="G58" s="20"/>
@@ -5172,7 +5331,7 @@
         <v>224</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C59" s="18" t="s">
         <v>409</v>
@@ -5191,16 +5350,16 @@
         <v>224</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>303</v>
+        <v>405</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D60" t="s">
-        <v>227</v>
+        <v>1107</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F60" s="20"/>
       <c r="G60" s="20"/>
@@ -5210,16 +5369,16 @@
         <v>224</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>713</v>
+        <v>404</v>
       </c>
       <c r="D61" t="s">
-        <v>1107</v>
+        <v>227</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F61" s="20"/>
       <c r="G61" s="20"/>
@@ -5229,16 +5388,16 @@
         <v>224</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D62" t="s">
-        <v>227</v>
+        <v>1107</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F62" s="20"/>
       <c r="G62" s="20"/>
@@ -5248,10 +5407,10 @@
         <v>224</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>1105</v>
+        <v>304</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D63" t="s">
         <v>227</v>
@@ -5264,38 +5423,38 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="18" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>548</v>
+        <v>1105</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>1053</v>
+        <v>713</v>
       </c>
       <c r="D64" t="s">
-        <v>1106</v>
+        <v>227</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>1052</v>
-      </c>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
+        <v>854</v>
+      </c>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>551</v>
+        <v>1053</v>
       </c>
       <c r="D65" t="s">
         <v>1106</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F65" s="16"/>
       <c r="G65" s="16"/>
@@ -5305,7 +5464,7 @@
         <v>212</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>551</v>
@@ -5314,7 +5473,7 @@
         <v>1106</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F66" s="16"/>
       <c r="G66" s="16"/>
@@ -5324,16 +5483,16 @@
         <v>212</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>795</v>
+        <v>550</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>797</v>
+        <v>551</v>
       </c>
       <c r="D67" t="s">
         <v>1106</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F67" s="16"/>
       <c r="G67" s="16"/>
@@ -5343,7 +5502,7 @@
         <v>212</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>797</v>
@@ -5352,7 +5511,7 @@
         <v>1106</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F68" s="16"/>
       <c r="G68" s="16"/>
@@ -5362,16 +5521,16 @@
         <v>212</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D69" t="s">
         <v>1106</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="F69" s="16"/>
       <c r="G69" s="16"/>
@@ -5381,16 +5540,16 @@
         <v>212</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>603</v>
+        <v>793</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>607</v>
+        <v>794</v>
       </c>
       <c r="D70" t="s">
         <v>1106</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>862</v>
+        <v>1049</v>
       </c>
       <c r="F70" s="16"/>
       <c r="G70" s="16"/>
@@ -5400,16 +5559,16 @@
         <v>212</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D71" t="s">
         <v>1106</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>826</v>
+        <v>862</v>
       </c>
       <c r="F71" s="16"/>
       <c r="G71" s="16"/>
@@ -5419,10 +5578,10 @@
         <v>212</v>
       </c>
       <c r="B72" s="18" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>825</v>
+        <v>606</v>
       </c>
       <c r="D72" t="s">
         <v>1106</v>
@@ -5438,16 +5597,16 @@
         <v>212</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>546</v>
+        <v>605</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>544</v>
+        <v>825</v>
       </c>
       <c r="D73" t="s">
         <v>1106</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>792</v>
+        <v>826</v>
       </c>
       <c r="F73" s="16"/>
       <c r="G73" s="16"/>
@@ -5457,16 +5616,16 @@
         <v>212</v>
       </c>
       <c r="B74" s="18" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="D74" t="s">
         <v>1106</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="F74" s="16"/>
       <c r="G74" s="16"/>
@@ -5476,16 +5635,16 @@
         <v>212</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D75" t="s">
         <v>1106</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>863</v>
+        <v>798</v>
       </c>
       <c r="F75" s="16"/>
       <c r="G75" s="16"/>
@@ -5495,16 +5654,16 @@
         <v>212</v>
       </c>
       <c r="B76" s="18" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>800</v>
+        <v>554</v>
       </c>
       <c r="D76" t="s">
         <v>1106</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>801</v>
+        <v>863</v>
       </c>
       <c r="F76" s="16"/>
       <c r="G76" s="16"/>
@@ -5514,16 +5673,16 @@
         <v>212</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D77" t="s">
         <v>1106</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F77" s="16"/>
       <c r="G77" s="16"/>
@@ -5533,7 +5692,7 @@
         <v>212</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C78" s="18" t="s">
         <v>799</v>
@@ -5542,7 +5701,7 @@
         <v>1106</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F78" s="16"/>
       <c r="G78" s="16"/>
@@ -5552,7 +5711,7 @@
         <v>212</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C79" s="18" t="s">
         <v>799</v>
@@ -5561,7 +5720,7 @@
         <v>1106</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="F79" s="16"/>
       <c r="G79" s="16"/>
@@ -5571,7 +5730,7 @@
         <v>212</v>
       </c>
       <c r="B80" s="18" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C80" s="18" t="s">
         <v>799</v>
@@ -5580,7 +5739,7 @@
         <v>1106</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F80" s="16"/>
       <c r="G80" s="16"/>
@@ -5590,7 +5749,7 @@
         <v>212</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C81" s="18" t="s">
         <v>799</v>
@@ -5599,7 +5758,7 @@
         <v>1106</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="F81" s="16"/>
       <c r="G81" s="16"/>
@@ -5609,7 +5768,7 @@
         <v>212</v>
       </c>
       <c r="B82" s="18" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C82" s="18" t="s">
         <v>799</v>
@@ -5618,7 +5777,7 @@
         <v>1106</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F82" s="16"/>
       <c r="G82" s="16"/>
@@ -5628,7 +5787,7 @@
         <v>212</v>
       </c>
       <c r="B83" s="18" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C83" s="18" t="s">
         <v>799</v>
@@ -5637,7 +5796,7 @@
         <v>1106</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F83" s="16"/>
       <c r="G83" s="16"/>
@@ -5647,7 +5806,7 @@
         <v>212</v>
       </c>
       <c r="B84" s="18" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C84" s="18" t="s">
         <v>799</v>
@@ -5656,7 +5815,7 @@
         <v>1106</v>
       </c>
       <c r="E84" s="18" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F84" s="16"/>
       <c r="G84" s="16"/>
@@ -5666,7 +5825,7 @@
         <v>212</v>
       </c>
       <c r="B85" s="18" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C85" s="18" t="s">
         <v>799</v>
@@ -5675,7 +5834,7 @@
         <v>1106</v>
       </c>
       <c r="E85" s="18" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F85" s="16"/>
       <c r="G85" s="16"/>
@@ -5685,7 +5844,7 @@
         <v>212</v>
       </c>
       <c r="B86" s="18" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C86" s="18" t="s">
         <v>799</v>
@@ -5694,7 +5853,7 @@
         <v>1106</v>
       </c>
       <c r="E86" s="18" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F86" s="16"/>
       <c r="G86" s="16"/>
@@ -5704,7 +5863,7 @@
         <v>212</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C87" s="18" t="s">
         <v>799</v>
@@ -5713,7 +5872,7 @@
         <v>1106</v>
       </c>
       <c r="E87" s="18" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F87" s="16"/>
       <c r="G87" s="16"/>
@@ -5723,7 +5882,7 @@
         <v>212</v>
       </c>
       <c r="B88" s="18" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C88" s="18" t="s">
         <v>799</v>
@@ -5732,7 +5891,7 @@
         <v>1106</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F88" s="16"/>
       <c r="G88" s="16"/>
@@ -5742,7 +5901,7 @@
         <v>212</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C89" s="18" t="s">
         <v>799</v>
@@ -5751,7 +5910,7 @@
         <v>1106</v>
       </c>
       <c r="E89" s="18" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F89" s="16"/>
       <c r="G89" s="16"/>
@@ -5761,7 +5920,7 @@
         <v>212</v>
       </c>
       <c r="B90" s="18" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C90" s="18" t="s">
         <v>799</v>
@@ -5770,7 +5929,7 @@
         <v>1106</v>
       </c>
       <c r="E90" s="18" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F90" s="16"/>
       <c r="G90" s="16"/>
@@ -5780,7 +5939,7 @@
         <v>212</v>
       </c>
       <c r="B91" s="18" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C91" s="18" t="s">
         <v>799</v>
@@ -5789,7 +5948,7 @@
         <v>1106</v>
       </c>
       <c r="E91" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F91" s="16"/>
       <c r="G91" s="16"/>
@@ -5799,7 +5958,7 @@
         <v>212</v>
       </c>
       <c r="B92" s="18" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C92" s="18" t="s">
         <v>799</v>
@@ -5808,7 +5967,7 @@
         <v>1106</v>
       </c>
       <c r="E92" s="18" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="F92" s="16"/>
       <c r="G92" s="16"/>
@@ -5818,7 +5977,7 @@
         <v>212</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C93" s="18" t="s">
         <v>799</v>
@@ -5827,7 +5986,7 @@
         <v>1106</v>
       </c>
       <c r="E93" s="18" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F93" s="16"/>
       <c r="G93" s="16"/>
@@ -5837,7 +5996,7 @@
         <v>212</v>
       </c>
       <c r="B94" s="18" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C94" s="18" t="s">
         <v>799</v>
@@ -5846,7 +6005,7 @@
         <v>1106</v>
       </c>
       <c r="E94" s="18" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F94" s="16"/>
       <c r="G94" s="16"/>
@@ -5856,7 +6015,7 @@
         <v>212</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C95" s="18" t="s">
         <v>799</v>
@@ -5865,7 +6024,7 @@
         <v>1106</v>
       </c>
       <c r="E95" s="18" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F95" s="16"/>
       <c r="G95" s="16"/>
@@ -5875,7 +6034,7 @@
         <v>212</v>
       </c>
       <c r="B96" s="18" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C96" s="18" t="s">
         <v>799</v>
@@ -5884,7 +6043,7 @@
         <v>1106</v>
       </c>
       <c r="E96" s="18" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F96" s="16"/>
       <c r="G96" s="16"/>
@@ -5894,7 +6053,7 @@
         <v>212</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C97" s="18" t="s">
         <v>799</v>
@@ -5903,7 +6062,7 @@
         <v>1106</v>
       </c>
       <c r="E97" s="18" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F97" s="16"/>
       <c r="G97" s="16"/>
@@ -5913,7 +6072,7 @@
         <v>212</v>
       </c>
       <c r="B98" s="18" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C98" s="18" t="s">
         <v>799</v>
@@ -5922,7 +6081,7 @@
         <v>1106</v>
       </c>
       <c r="E98" s="18" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F98" s="16"/>
       <c r="G98" s="16"/>
@@ -5932,7 +6091,7 @@
         <v>212</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C99" s="18" t="s">
         <v>799</v>
@@ -5941,7 +6100,7 @@
         <v>1106</v>
       </c>
       <c r="E99" s="18" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F99" s="16"/>
       <c r="G99" s="16"/>
@@ -5951,16 +6110,16 @@
         <v>212</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>864</v>
+        <v>799</v>
       </c>
       <c r="D100" t="s">
         <v>1106</v>
       </c>
       <c r="E100" s="18" t="s">
-        <v>899</v>
+        <v>824</v>
       </c>
       <c r="F100" s="16"/>
       <c r="G100" s="16"/>
@@ -5970,16 +6129,16 @@
         <v>212</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>894</v>
+        <v>864</v>
       </c>
       <c r="D101" t="s">
         <v>1106</v>
       </c>
       <c r="E101" s="18" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="F101" s="16"/>
       <c r="G101" s="16"/>
@@ -5989,16 +6148,16 @@
         <v>212</v>
       </c>
       <c r="B102" s="18" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="C102" s="18" t="s">
-        <v>600</v>
+        <v>894</v>
       </c>
       <c r="D102" t="s">
         <v>1106</v>
       </c>
       <c r="E102" s="18" t="s">
-        <v>860</v>
+        <v>895</v>
       </c>
       <c r="F102" s="16"/>
       <c r="G102" s="16"/>
@@ -6008,16 +6167,16 @@
         <v>212</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>541</v>
+        <v>601</v>
       </c>
       <c r="C103" s="18" t="s">
-        <v>765</v>
+        <v>600</v>
       </c>
       <c r="D103" t="s">
         <v>1106</v>
       </c>
       <c r="E103" s="18" t="s">
-        <v>1012</v>
+        <v>860</v>
       </c>
       <c r="F103" s="16"/>
       <c r="G103" s="16"/>
@@ -6027,16 +6186,16 @@
         <v>212</v>
       </c>
       <c r="B104" s="18" t="s">
-        <v>581</v>
+        <v>541</v>
       </c>
       <c r="C104" s="18" t="s">
-        <v>602</v>
+        <v>765</v>
       </c>
       <c r="D104" t="s">
         <v>1106</v>
       </c>
       <c r="E104" s="18" t="s">
-        <v>861</v>
+        <v>1012</v>
       </c>
       <c r="F104" s="16"/>
       <c r="G104" s="16"/>
@@ -6046,16 +6205,16 @@
         <v>212</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="C105" s="18" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="D105" t="s">
         <v>1106</v>
       </c>
       <c r="E105" s="18" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="F105" s="16"/>
       <c r="G105" s="16"/>
@@ -6065,16 +6224,16 @@
         <v>212</v>
       </c>
       <c r="B106" s="18" t="s">
-        <v>633</v>
+        <v>599</v>
       </c>
       <c r="C106" s="18" t="s">
-        <v>1014</v>
+        <v>598</v>
       </c>
       <c r="D106" t="s">
         <v>1106</v>
       </c>
       <c r="E106" s="18" t="s">
-        <v>1015</v>
+        <v>859</v>
       </c>
       <c r="F106" s="16"/>
       <c r="G106" s="16"/>
@@ -6084,7 +6243,7 @@
         <v>212</v>
       </c>
       <c r="B107" s="18" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C107" s="18" t="s">
         <v>1014</v>
@@ -6103,16 +6262,16 @@
         <v>212</v>
       </c>
       <c r="B108" s="18" t="s">
-        <v>583</v>
+        <v>635</v>
       </c>
       <c r="C108" s="18" t="s">
-        <v>760</v>
+        <v>1014</v>
       </c>
       <c r="D108" t="s">
         <v>1106</v>
       </c>
       <c r="E108" s="18" t="s">
-        <v>788</v>
+        <v>1015</v>
       </c>
       <c r="F108" s="16"/>
       <c r="G108" s="16"/>
@@ -6122,7 +6281,7 @@
         <v>212</v>
       </c>
       <c r="B109" s="18" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C109" s="18" t="s">
         <v>760</v>
@@ -6141,16 +6300,16 @@
         <v>212</v>
       </c>
       <c r="B110" s="18" t="s">
-        <v>865</v>
+        <v>586</v>
       </c>
       <c r="C110" s="18" t="s">
-        <v>867</v>
+        <v>760</v>
       </c>
       <c r="D110" t="s">
         <v>1106</v>
       </c>
       <c r="E110" s="18" t="s">
-        <v>868</v>
+        <v>788</v>
       </c>
       <c r="F110" s="16"/>
       <c r="G110" s="16"/>
@@ -6160,7 +6319,7 @@
         <v>212</v>
       </c>
       <c r="B111" s="18" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C111" s="18" t="s">
         <v>867</v>
@@ -6179,16 +6338,16 @@
         <v>212</v>
       </c>
       <c r="B112" s="18" t="s">
-        <v>1046</v>
+        <v>866</v>
       </c>
       <c r="C112" s="18" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="D112" t="s">
         <v>1106</v>
       </c>
       <c r="E112" s="18" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="F112" s="16"/>
       <c r="G112" s="16"/>
@@ -6198,7 +6357,7 @@
         <v>212</v>
       </c>
       <c r="B113" s="18" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C113" s="18" t="s">
         <v>871</v>
@@ -6217,16 +6376,16 @@
         <v>212</v>
       </c>
       <c r="B114" s="18" t="s">
-        <v>869</v>
+        <v>1047</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>1048</v>
+        <v>871</v>
       </c>
       <c r="D114" t="s">
         <v>1106</v>
       </c>
       <c r="E114" s="18" t="s">
-        <v>1045</v>
+        <v>872</v>
       </c>
       <c r="F114" s="16"/>
       <c r="G114" s="16"/>
@@ -6236,7 +6395,7 @@
         <v>212</v>
       </c>
       <c r="B115" s="18" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C115" s="18" t="s">
         <v>1048</v>
@@ -6255,16 +6414,16 @@
         <v>212</v>
       </c>
       <c r="B116" s="18" t="s">
-        <v>594</v>
+        <v>870</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>763</v>
+        <v>1048</v>
       </c>
       <c r="D116" t="s">
         <v>1106</v>
       </c>
       <c r="E116" s="18" t="s">
-        <v>790</v>
+        <v>1045</v>
       </c>
       <c r="F116" s="16"/>
       <c r="G116" s="16"/>
@@ -6274,7 +6433,7 @@
         <v>212</v>
       </c>
       <c r="B117" s="18" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C117" s="18" t="s">
         <v>763</v>
@@ -6293,16 +6452,16 @@
         <v>212</v>
       </c>
       <c r="B118" s="18" t="s">
-        <v>543</v>
+        <v>593</v>
       </c>
       <c r="C118" s="18" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="D118" t="s">
         <v>1106</v>
       </c>
       <c r="E118" s="18" t="s">
-        <v>1011</v>
+        <v>790</v>
       </c>
       <c r="F118" s="16"/>
       <c r="G118" s="16"/>
@@ -6312,16 +6471,16 @@
         <v>212</v>
       </c>
       <c r="B119" s="18" t="s">
-        <v>597</v>
+        <v>543</v>
       </c>
       <c r="C119" s="18" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="D119" t="s">
         <v>1106</v>
       </c>
       <c r="E119" s="18" t="s">
-        <v>791</v>
+        <v>1011</v>
       </c>
       <c r="F119" s="16"/>
       <c r="G119" s="16"/>
@@ -6331,7 +6490,7 @@
         <v>212</v>
       </c>
       <c r="B120" s="18" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C120" s="18" t="s">
         <v>764</v>
@@ -6350,16 +6509,16 @@
         <v>212</v>
       </c>
       <c r="B121" s="18" t="s">
-        <v>1043</v>
+        <v>596</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D121" t="s">
         <v>1106</v>
       </c>
       <c r="E121" s="18" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="F121" s="16"/>
       <c r="G121" s="16"/>
@@ -6369,7 +6528,7 @@
         <v>212</v>
       </c>
       <c r="B122" s="18" t="s">
-        <v>590</v>
+        <v>1043</v>
       </c>
       <c r="C122" s="18" t="s">
         <v>762</v>
@@ -6388,16 +6547,16 @@
         <v>212</v>
       </c>
       <c r="B123" s="18" t="s">
-        <v>1044</v>
+        <v>590</v>
       </c>
       <c r="C123" s="18" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D123" t="s">
         <v>1106</v>
       </c>
       <c r="E123" s="18" t="s">
-        <v>1028</v>
+        <v>789</v>
       </c>
       <c r="F123" s="16"/>
       <c r="G123" s="16"/>
@@ -6407,7 +6566,7 @@
         <v>212</v>
       </c>
       <c r="B124" s="18" t="s">
-        <v>589</v>
+        <v>1044</v>
       </c>
       <c r="C124" s="18" t="s">
         <v>761</v>
@@ -6426,16 +6585,16 @@
         <v>212</v>
       </c>
       <c r="B125" s="18" t="s">
-        <v>1103</v>
+        <v>589</v>
       </c>
       <c r="C125" s="18" t="s">
-        <v>1102</v>
+        <v>761</v>
       </c>
       <c r="D125" t="s">
         <v>1106</v>
       </c>
       <c r="E125" s="18" t="s">
-        <v>1104</v>
+        <v>1028</v>
       </c>
       <c r="F125" s="16"/>
       <c r="G125" s="16"/>
@@ -6445,7 +6604,7 @@
         <v>212</v>
       </c>
       <c r="B126" s="18" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C126" s="18" t="s">
         <v>1102</v>
@@ -6464,16 +6623,16 @@
         <v>212</v>
       </c>
       <c r="B127" s="18" t="s">
-        <v>584</v>
+        <v>1101</v>
       </c>
       <c r="C127" s="18" t="s">
-        <v>873</v>
+        <v>1102</v>
       </c>
       <c r="D127" t="s">
         <v>1106</v>
       </c>
       <c r="E127" s="18" t="s">
-        <v>875</v>
+        <v>1104</v>
       </c>
       <c r="F127" s="16"/>
       <c r="G127" s="16"/>
@@ -6483,7 +6642,7 @@
         <v>212</v>
       </c>
       <c r="B128" s="18" t="s">
-        <v>874</v>
+        <v>584</v>
       </c>
       <c r="C128" s="18" t="s">
         <v>873</v>
@@ -6502,16 +6661,16 @@
         <v>212</v>
       </c>
       <c r="B129" s="18" t="s">
-        <v>652</v>
+        <v>874</v>
       </c>
       <c r="C129" s="18" t="s">
-        <v>653</v>
+        <v>873</v>
       </c>
       <c r="D129" t="s">
         <v>1106</v>
       </c>
       <c r="E129" s="18" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F129" s="16"/>
       <c r="G129" s="16"/>
@@ -6521,16 +6680,16 @@
         <v>212</v>
       </c>
       <c r="B130" s="18" t="s">
-        <v>609</v>
+        <v>652</v>
       </c>
       <c r="C130" s="18" t="s">
-        <v>878</v>
+        <v>653</v>
       </c>
       <c r="D130" t="s">
         <v>1106</v>
       </c>
       <c r="E130" s="18" t="s">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="F130" s="16"/>
       <c r="G130" s="16"/>
@@ -6540,16 +6699,16 @@
         <v>212</v>
       </c>
       <c r="B131" s="18" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C131" s="18" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D131" t="s">
         <v>1106</v>
       </c>
       <c r="E131" s="18" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F131" s="16"/>
       <c r="G131" s="16"/>
@@ -6559,16 +6718,16 @@
         <v>212</v>
       </c>
       <c r="B132" s="18" t="s">
-        <v>879</v>
+        <v>611</v>
       </c>
       <c r="C132" s="18" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="D132" t="s">
         <v>1106</v>
       </c>
       <c r="E132" s="18" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F132" s="16"/>
       <c r="G132" s="16"/>
@@ -6578,16 +6737,16 @@
         <v>212</v>
       </c>
       <c r="B133" s="18" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C133" s="18" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="D133" t="s">
         <v>1106</v>
       </c>
       <c r="E133" s="18" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F133" s="16"/>
       <c r="G133" s="16"/>
@@ -6597,16 +6756,16 @@
         <v>212</v>
       </c>
       <c r="B134" s="18" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C134" s="18" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D134" t="s">
         <v>1106</v>
       </c>
       <c r="E134" s="18" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F134" s="16"/>
       <c r="G134" s="16"/>
@@ -6616,16 +6775,16 @@
         <v>212</v>
       </c>
       <c r="B135" s="18" t="s">
-        <v>613</v>
+        <v>883</v>
       </c>
       <c r="C135" s="18" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D135" t="s">
         <v>1106</v>
       </c>
       <c r="E135" s="18" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F135" s="16"/>
       <c r="G135" s="16"/>
@@ -6635,16 +6794,16 @@
         <v>212</v>
       </c>
       <c r="B136" s="18" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C136" s="18" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D136" t="s">
         <v>1106</v>
       </c>
       <c r="E136" s="18" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F136" s="16"/>
       <c r="G136" s="16"/>
@@ -6654,16 +6813,16 @@
         <v>212</v>
       </c>
       <c r="B137" s="18" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C137" s="18" t="s">
-        <v>617</v>
+        <v>886</v>
       </c>
       <c r="D137" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="E137" s="18" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="F137" s="16"/>
       <c r="G137" s="16"/>
@@ -6673,16 +6832,16 @@
         <v>212</v>
       </c>
       <c r="B138" s="18" t="s">
-        <v>686</v>
+        <v>618</v>
       </c>
       <c r="C138" s="18" t="s">
-        <v>687</v>
+        <v>617</v>
       </c>
       <c r="D138" t="s">
         <v>1108</v>
       </c>
       <c r="E138" s="18" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="F138" s="16"/>
       <c r="G138" s="16"/>
@@ -6692,16 +6851,16 @@
         <v>212</v>
       </c>
       <c r="B139" s="18" t="s">
-        <v>619</v>
+        <v>686</v>
       </c>
       <c r="C139" s="18" t="s">
-        <v>896</v>
+        <v>687</v>
       </c>
       <c r="D139" t="s">
         <v>1108</v>
       </c>
       <c r="E139" s="18" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="F139" s="16"/>
       <c r="G139" s="16"/>
@@ -6711,16 +6870,16 @@
         <v>212</v>
       </c>
       <c r="B140" s="18" t="s">
-        <v>1054</v>
+        <v>619</v>
       </c>
       <c r="C140" s="18" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D140" s="18" t="s">
-        <v>1107</v>
+        <v>896</v>
+      </c>
+      <c r="D140" t="s">
+        <v>1108</v>
       </c>
       <c r="E140" s="18" t="s">
-        <v>1076</v>
+        <v>900</v>
       </c>
       <c r="F140" s="16"/>
       <c r="G140" s="16"/>
@@ -6730,16 +6889,16 @@
         <v>212</v>
       </c>
       <c r="B141" s="18" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="C141" s="18" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D141" s="18" t="s">
         <v>1107</v>
       </c>
       <c r="E141" s="18" t="s">
-        <v>1086</v>
+        <v>1076</v>
       </c>
       <c r="F141" s="16"/>
       <c r="G141" s="16"/>
@@ -6749,16 +6908,16 @@
         <v>212</v>
       </c>
       <c r="B142" s="18" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C142" s="18" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="D142" s="18" t="s">
         <v>1107</v>
       </c>
       <c r="E142" s="18" t="s">
-        <v>1077</v>
+        <v>1086</v>
       </c>
       <c r="F142" s="16"/>
       <c r="G142" s="16"/>
@@ -6768,16 +6927,16 @@
         <v>212</v>
       </c>
       <c r="B143" s="18" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="C143" s="18" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="D143" s="18" t="s">
         <v>1107</v>
       </c>
       <c r="E143" s="18" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F143" s="16"/>
       <c r="G143" s="16"/>
@@ -6787,16 +6946,16 @@
         <v>212</v>
       </c>
       <c r="B144" s="18" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="C144" s="18" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="D144" s="18" t="s">
         <v>1107</v>
       </c>
       <c r="E144" s="18" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F144" s="16"/>
       <c r="G144" s="16"/>
@@ -6806,16 +6965,16 @@
         <v>212</v>
       </c>
       <c r="B145" s="18" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C145" s="18" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="D145" s="18" t="s">
         <v>1107</v>
       </c>
       <c r="E145" s="18" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F145" s="16"/>
       <c r="G145" s="16"/>
@@ -6825,16 +6984,16 @@
         <v>212</v>
       </c>
       <c r="B146" s="18" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C146" s="18" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="D146" s="18" t="s">
         <v>1107</v>
       </c>
       <c r="E146" s="18" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F146" s="16"/>
       <c r="G146" s="16"/>
@@ -6844,16 +7003,16 @@
         <v>212</v>
       </c>
       <c r="B147" s="18" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C147" s="18" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D147" s="18" t="s">
         <v>1107</v>
       </c>
       <c r="E147" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F147" s="16"/>
       <c r="G147" s="16"/>
@@ -6863,16 +7022,16 @@
         <v>212</v>
       </c>
       <c r="B148" s="18" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C148" s="18" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="D148" s="18" t="s">
         <v>1107</v>
       </c>
       <c r="E148" s="18" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F148" s="16"/>
       <c r="G148" s="16"/>
@@ -6882,16 +7041,16 @@
         <v>212</v>
       </c>
       <c r="B149" s="18" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C149" s="18" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D149" s="18" t="s">
         <v>1107</v>
       </c>
       <c r="E149" s="18" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F149" s="16"/>
       <c r="G149" s="16"/>
@@ -6901,16 +7060,16 @@
         <v>212</v>
       </c>
       <c r="B150" s="18" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C150" s="18" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="D150" s="18" t="s">
         <v>1107</v>
       </c>
       <c r="E150" s="18" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="F150" s="16"/>
       <c r="G150" s="16"/>
@@ -6920,16 +7079,16 @@
         <v>212</v>
       </c>
       <c r="B151" s="18" t="s">
-        <v>659</v>
+        <v>1075</v>
       </c>
       <c r="C151" s="18" t="s">
-        <v>752</v>
-      </c>
-      <c r="D151" t="s">
-        <v>1106</v>
+        <v>1074</v>
+      </c>
+      <c r="D151" s="18" t="s">
+        <v>1107</v>
       </c>
       <c r="E151" s="18" t="s">
-        <v>768</v>
+        <v>1085</v>
       </c>
       <c r="F151" s="16"/>
       <c r="G151" s="16"/>
@@ -6939,16 +7098,16 @@
         <v>212</v>
       </c>
       <c r="B152" s="18" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C152" s="18" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="D152" t="s">
         <v>1106</v>
       </c>
       <c r="E152" s="18" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F152" s="16"/>
       <c r="G152" s="16"/>
@@ -6958,16 +7117,16 @@
         <v>212</v>
       </c>
       <c r="B153" s="18" t="s">
-        <v>658</v>
+        <v>1147</v>
       </c>
       <c r="C153" s="18" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D153" t="s">
         <v>1106</v>
       </c>
       <c r="E153" s="18" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F153" s="16"/>
       <c r="G153" s="16"/>
@@ -6977,16 +7136,16 @@
         <v>212</v>
       </c>
       <c r="B154" s="18" t="s">
-        <v>1126</v>
+        <v>661</v>
       </c>
       <c r="C154" s="18" t="s">
-        <v>1127</v>
+        <v>750</v>
       </c>
       <c r="D154" t="s">
         <v>1106</v>
       </c>
       <c r="E154" s="18" t="s">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="F154" s="16"/>
       <c r="G154" s="16"/>
@@ -6996,16 +7155,16 @@
         <v>212</v>
       </c>
       <c r="B155" s="18" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
       <c r="C155" s="18" t="s">
-        <v>1127</v>
+        <v>750</v>
       </c>
       <c r="D155" t="s">
         <v>1106</v>
       </c>
       <c r="E155" s="18" t="s">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="F155" s="16"/>
       <c r="G155" s="16"/>
@@ -7015,16 +7174,16 @@
         <v>212</v>
       </c>
       <c r="B156" s="18" t="s">
-        <v>1125</v>
+        <v>1149</v>
       </c>
       <c r="C156" s="18" t="s">
-        <v>1127</v>
+        <v>751</v>
       </c>
       <c r="D156" t="s">
         <v>1106</v>
       </c>
       <c r="E156" s="18" t="s">
-        <v>1129</v>
+        <v>767</v>
       </c>
       <c r="F156" s="16"/>
       <c r="G156" s="16"/>
@@ -7034,16 +7193,16 @@
         <v>212</v>
       </c>
       <c r="B157" s="18" t="s">
-        <v>1128</v>
+        <v>658</v>
       </c>
       <c r="C157" s="18" t="s">
-        <v>1131</v>
+        <v>751</v>
       </c>
       <c r="D157" t="s">
         <v>1106</v>
       </c>
       <c r="E157" s="18" t="s">
-        <v>1130</v>
+        <v>767</v>
       </c>
       <c r="F157" s="16"/>
       <c r="G157" s="16"/>
@@ -7053,16 +7212,16 @@
         <v>212</v>
       </c>
       <c r="B158" s="18" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
       <c r="C158" s="18" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="D158" t="s">
         <v>1106</v>
       </c>
       <c r="E158" s="18" t="s">
-        <v>1130</v>
+        <v>1146</v>
       </c>
       <c r="F158" s="16"/>
       <c r="G158" s="16"/>
@@ -7072,16 +7231,16 @@
         <v>212</v>
       </c>
       <c r="B159" s="18" t="s">
-        <v>1134</v>
+        <v>1148</v>
       </c>
       <c r="C159" s="18" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="D159" t="s">
         <v>1106</v>
       </c>
       <c r="E159" s="18" t="s">
-        <v>907</v>
+        <v>1146</v>
       </c>
       <c r="F159" s="16"/>
       <c r="G159" s="16"/>
@@ -7091,16 +7250,16 @@
         <v>212</v>
       </c>
       <c r="B160" s="18" t="s">
-        <v>688</v>
+        <v>1143</v>
       </c>
       <c r="C160" s="18" t="s">
-        <v>689</v>
+        <v>1144</v>
       </c>
       <c r="D160" t="s">
         <v>1106</v>
       </c>
       <c r="E160" s="18" t="s">
-        <v>907</v>
+        <v>769</v>
       </c>
       <c r="F160" s="16"/>
       <c r="G160" s="16"/>
@@ -7110,16 +7269,16 @@
         <v>212</v>
       </c>
       <c r="B161" s="18" t="s">
-        <v>690</v>
+        <v>1145</v>
       </c>
       <c r="C161" s="18" t="s">
-        <v>906</v>
+        <v>1144</v>
       </c>
       <c r="D161" t="s">
         <v>1106</v>
       </c>
       <c r="E161" s="18" t="s">
-        <v>908</v>
+        <v>769</v>
       </c>
       <c r="F161" s="16"/>
       <c r="G161" s="16"/>
@@ -7129,16 +7288,16 @@
         <v>212</v>
       </c>
       <c r="B162" s="18" t="s">
-        <v>692</v>
+        <v>1120</v>
       </c>
       <c r="C162" s="18" t="s">
-        <v>693</v>
+        <v>1121</v>
       </c>
       <c r="D162" t="s">
         <v>1106</v>
       </c>
       <c r="E162" s="18" t="s">
-        <v>909</v>
+        <v>1123</v>
       </c>
       <c r="F162" s="16"/>
       <c r="G162" s="16"/>
@@ -7148,16 +7307,16 @@
         <v>212</v>
       </c>
       <c r="B163" s="18" t="s">
-        <v>694</v>
+        <v>1130</v>
       </c>
       <c r="C163" s="18" t="s">
-        <v>737</v>
+        <v>1121</v>
       </c>
       <c r="D163" t="s">
         <v>1106</v>
       </c>
       <c r="E163" s="18" t="s">
-        <v>901</v>
+        <v>1123</v>
       </c>
       <c r="F163" s="16"/>
       <c r="G163" s="16"/>
@@ -7167,16 +7326,16 @@
         <v>212</v>
       </c>
       <c r="B164" s="18" t="s">
-        <v>696</v>
+        <v>1119</v>
       </c>
       <c r="C164" s="18" t="s">
-        <v>738</v>
+        <v>1121</v>
       </c>
       <c r="D164" t="s">
         <v>1106</v>
       </c>
       <c r="E164" s="18" t="s">
-        <v>910</v>
+        <v>1123</v>
       </c>
       <c r="F164" s="16"/>
       <c r="G164" s="16"/>
@@ -7186,16 +7345,16 @@
         <v>212</v>
       </c>
       <c r="B165" s="18" t="s">
-        <v>698</v>
+        <v>1122</v>
       </c>
       <c r="C165" s="18" t="s">
-        <v>699</v>
+        <v>1125</v>
       </c>
       <c r="D165" t="s">
         <v>1106</v>
       </c>
       <c r="E165" s="18" t="s">
-        <v>911</v>
+        <v>1124</v>
       </c>
       <c r="F165" s="16"/>
       <c r="G165" s="16"/>
@@ -7205,16 +7364,16 @@
         <v>212</v>
       </c>
       <c r="B166" s="18" t="s">
-        <v>700</v>
+        <v>1126</v>
       </c>
       <c r="C166" s="18" t="s">
-        <v>902</v>
+        <v>1127</v>
       </c>
       <c r="D166" t="s">
         <v>1106</v>
       </c>
       <c r="E166" s="18" t="s">
-        <v>920</v>
+        <v>1124</v>
       </c>
       <c r="F166" s="16"/>
       <c r="G166" s="16"/>
@@ -7224,16 +7383,16 @@
         <v>212</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>916</v>
+        <v>1128</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>917</v>
+        <v>1129</v>
       </c>
       <c r="D167" t="s">
         <v>1106</v>
       </c>
       <c r="E167" s="18" t="s">
-        <v>920</v>
+        <v>907</v>
       </c>
       <c r="F167" s="16"/>
       <c r="G167" s="16"/>
@@ -7243,33 +7402,35 @@
         <v>212</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>918</v>
+        <v>688</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>919</v>
+        <v>689</v>
       </c>
       <c r="D168" t="s">
         <v>1106</v>
       </c>
       <c r="E168" s="18" t="s">
-        <v>920</v>
-      </c>
+        <v>907</v>
+      </c>
+      <c r="F168" s="16"/>
+      <c r="G168" s="16"/>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="C169" s="18" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="D169" t="s">
         <v>1106</v>
       </c>
       <c r="E169" s="18" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="F169" s="16"/>
       <c r="G169" s="16"/>
@@ -7279,16 +7440,16 @@
         <v>212</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>903</v>
+        <v>692</v>
       </c>
       <c r="C170" s="18" t="s">
-        <v>904</v>
+        <v>693</v>
       </c>
       <c r="D170" t="s">
         <v>1106</v>
       </c>
       <c r="E170" s="18" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="F170" s="16"/>
       <c r="G170" s="16"/>
@@ -7298,16 +7459,16 @@
         <v>212</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>912</v>
+        <v>694</v>
       </c>
       <c r="C171" s="18" t="s">
-        <v>913</v>
+        <v>737</v>
       </c>
       <c r="D171" t="s">
         <v>1106</v>
       </c>
       <c r="E171" s="18" t="s">
-        <v>915</v>
+        <v>901</v>
       </c>
       <c r="F171" s="16"/>
       <c r="G171" s="16"/>
@@ -7317,16 +7478,16 @@
         <v>212</v>
       </c>
       <c r="B172" s="18" t="s">
-        <v>914</v>
+        <v>696</v>
       </c>
       <c r="C172" s="18" t="s">
-        <v>913</v>
+        <v>738</v>
       </c>
       <c r="D172" t="s">
         <v>1106</v>
       </c>
       <c r="E172" s="18" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="F172" s="16"/>
       <c r="G172" s="16"/>
@@ -7336,16 +7497,16 @@
         <v>212</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>723</v>
+        <v>698</v>
       </c>
       <c r="C173" s="18" t="s">
-        <v>729</v>
+        <v>699</v>
       </c>
       <c r="D173" t="s">
         <v>1106</v>
       </c>
       <c r="E173" s="18" t="s">
-        <v>747</v>
+        <v>911</v>
       </c>
       <c r="F173" s="16"/>
       <c r="G173" s="16"/>
@@ -7355,16 +7516,16 @@
         <v>212</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>724</v>
+        <v>700</v>
       </c>
       <c r="C174" s="18" t="s">
-        <v>730</v>
+        <v>902</v>
       </c>
       <c r="D174" t="s">
         <v>1106</v>
       </c>
       <c r="E174" s="18" t="s">
-        <v>748</v>
+        <v>920</v>
       </c>
       <c r="F174" s="16"/>
       <c r="G174" s="16"/>
@@ -7374,16 +7535,16 @@
         <v>212</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>725</v>
+        <v>916</v>
       </c>
       <c r="C175" s="18" t="s">
-        <v>731</v>
+        <v>917</v>
       </c>
       <c r="D175" t="s">
         <v>1106</v>
       </c>
       <c r="E175" s="18" t="s">
-        <v>749</v>
+        <v>920</v>
       </c>
       <c r="F175" s="16"/>
       <c r="G175" s="16"/>
@@ -7393,22 +7554,16 @@
         <v>212</v>
       </c>
       <c r="B176" s="18" t="s">
-        <v>735</v>
+        <v>918</v>
       </c>
       <c r="C176" s="18" t="s">
-        <v>736</v>
+        <v>919</v>
       </c>
       <c r="D176" t="s">
         <v>1106</v>
       </c>
       <c r="E176" s="18" t="s">
-        <v>925</v>
-      </c>
-      <c r="F176" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G176" s="16" t="s">
-        <v>743</v>
+        <v>920</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -7416,39 +7571,35 @@
         <v>212</v>
       </c>
       <c r="B177" s="18" t="s">
-        <v>746</v>
+        <v>702</v>
       </c>
       <c r="C177" s="18" t="s">
-        <v>736</v>
+        <v>904</v>
       </c>
       <c r="D177" t="s">
         <v>1106</v>
       </c>
       <c r="E177" s="18" t="s">
-        <v>925</v>
-      </c>
-      <c r="F177" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G177" s="16" t="s">
-        <v>743</v>
-      </c>
+        <v>905</v>
+      </c>
+      <c r="F177" s="16"/>
+      <c r="G177" s="16"/>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>921</v>
+        <v>903</v>
       </c>
       <c r="C178" s="18" t="s">
-        <v>922</v>
+        <v>904</v>
       </c>
       <c r="D178" t="s">
         <v>1106</v>
       </c>
       <c r="E178" s="18" t="s">
-        <v>926</v>
+        <v>905</v>
       </c>
       <c r="F178" s="16"/>
       <c r="G178" s="16"/>
@@ -7458,16 +7609,16 @@
         <v>212</v>
       </c>
       <c r="B179" s="18" t="s">
-        <v>923</v>
+        <v>912</v>
       </c>
       <c r="C179" s="18" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="D179" t="s">
         <v>1106</v>
       </c>
       <c r="E179" s="18" t="s">
-        <v>926</v>
+        <v>915</v>
       </c>
       <c r="F179" s="16"/>
       <c r="G179" s="16"/>
@@ -7477,16 +7628,16 @@
         <v>212</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>924</v>
+        <v>914</v>
       </c>
       <c r="C180" s="18" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="D180" t="s">
         <v>1106</v>
       </c>
       <c r="E180" s="18" t="s">
-        <v>926</v>
+        <v>915</v>
       </c>
       <c r="F180" s="16"/>
       <c r="G180" s="16"/>
@@ -7496,16 +7647,16 @@
         <v>212</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>928</v>
+        <v>723</v>
       </c>
       <c r="C181" s="18" t="s">
-        <v>927</v>
+        <v>729</v>
       </c>
       <c r="D181" t="s">
         <v>1106</v>
       </c>
       <c r="E181" s="18" t="s">
-        <v>929</v>
+        <v>747</v>
       </c>
       <c r="F181" s="16"/>
       <c r="G181" s="16"/>
@@ -7515,16 +7666,16 @@
         <v>212</v>
       </c>
       <c r="B182" s="18" t="s">
-        <v>931</v>
+        <v>724</v>
       </c>
       <c r="C182" s="18" t="s">
-        <v>930</v>
+        <v>730</v>
       </c>
       <c r="D182" t="s">
         <v>1106</v>
       </c>
       <c r="E182" s="18" t="s">
-        <v>934</v>
+        <v>748</v>
       </c>
       <c r="F182" s="16"/>
       <c r="G182" s="16"/>
@@ -7534,16 +7685,16 @@
         <v>212</v>
       </c>
       <c r="B183" s="18" t="s">
-        <v>933</v>
+        <v>725</v>
       </c>
       <c r="C183" s="18" t="s">
-        <v>932</v>
+        <v>731</v>
       </c>
       <c r="D183" t="s">
         <v>1106</v>
       </c>
       <c r="E183" s="18" t="s">
-        <v>937</v>
+        <v>749</v>
       </c>
       <c r="F183" s="16"/>
       <c r="G183" s="16"/>
@@ -7553,54 +7704,62 @@
         <v>212</v>
       </c>
       <c r="B184" s="18" t="s">
-        <v>936</v>
+        <v>735</v>
       </c>
       <c r="C184" s="18" t="s">
-        <v>935</v>
+        <v>736</v>
       </c>
       <c r="D184" t="s">
         <v>1106</v>
       </c>
       <c r="E184" s="18" t="s">
-        <v>938</v>
-      </c>
-      <c r="F184" s="16"/>
-      <c r="G184" s="16"/>
+        <v>925</v>
+      </c>
+      <c r="F184" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G184" s="16" t="s">
+        <v>743</v>
+      </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>939</v>
+        <v>746</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>941</v>
+        <v>736</v>
       </c>
       <c r="D185" t="s">
         <v>1106</v>
       </c>
       <c r="E185" s="18" t="s">
-        <v>938</v>
-      </c>
-      <c r="F185" s="16"/>
-      <c r="G185" s="16"/>
+        <v>925</v>
+      </c>
+      <c r="F185" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G185" s="16" t="s">
+        <v>743</v>
+      </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="18" t="s">
         <v>212</v>
       </c>
       <c r="B186" s="18" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="C186" s="18" t="s">
-        <v>942</v>
+        <v>922</v>
       </c>
       <c r="D186" t="s">
         <v>1106</v>
       </c>
       <c r="E186" s="18" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
       <c r="F186" s="16"/>
       <c r="G186" s="16"/>
@@ -7610,16 +7769,16 @@
         <v>212</v>
       </c>
       <c r="B187" s="18" t="s">
-        <v>1142</v>
+        <v>923</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>1143</v>
-      </c>
-      <c r="D187" s="18" t="s">
+        <v>922</v>
+      </c>
+      <c r="D187" t="s">
         <v>1106</v>
       </c>
       <c r="E187" s="18" t="s">
-        <v>945</v>
+        <v>926</v>
       </c>
       <c r="F187" s="16"/>
       <c r="G187" s="16"/>
@@ -7629,16 +7788,16 @@
         <v>212</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>943</v>
+        <v>924</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>944</v>
+        <v>922</v>
       </c>
       <c r="D188" t="s">
         <v>1106</v>
       </c>
       <c r="E188" s="18" t="s">
-        <v>945</v>
+        <v>926</v>
       </c>
       <c r="F188" s="16"/>
       <c r="G188" s="16"/>
@@ -7648,16 +7807,16 @@
         <v>212</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>1144</v>
+        <v>928</v>
       </c>
       <c r="C189" s="18" t="s">
-        <v>948</v>
+        <v>927</v>
       </c>
       <c r="D189" t="s">
         <v>1106</v>
       </c>
       <c r="E189" s="18" t="s">
-        <v>949</v>
+        <v>929</v>
       </c>
       <c r="F189" s="16"/>
       <c r="G189" s="16"/>
@@ -7667,16 +7826,16 @@
         <v>212</v>
       </c>
       <c r="B190" s="18" t="s">
-        <v>946</v>
+        <v>931</v>
       </c>
       <c r="C190" s="18" t="s">
-        <v>948</v>
+        <v>930</v>
       </c>
       <c r="D190" t="s">
         <v>1106</v>
       </c>
       <c r="E190" s="18" t="s">
-        <v>949</v>
+        <v>934</v>
       </c>
       <c r="F190" s="16"/>
       <c r="G190" s="16"/>
@@ -7686,16 +7845,16 @@
         <v>212</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>947</v>
+        <v>933</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>948</v>
+        <v>932</v>
       </c>
       <c r="D191" t="s">
         <v>1106</v>
       </c>
       <c r="E191" s="18" t="s">
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="F191" s="16"/>
       <c r="G191" s="16"/>
@@ -7705,16 +7864,16 @@
         <v>212</v>
       </c>
       <c r="B192" s="18" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="C192" s="18" t="s">
-        <v>950</v>
+        <v>935</v>
       </c>
       <c r="D192" t="s">
         <v>1106</v>
       </c>
       <c r="E192" s="18" t="s">
-        <v>953</v>
+        <v>938</v>
       </c>
       <c r="F192" s="16"/>
       <c r="G192" s="16"/>
@@ -7724,16 +7883,16 @@
         <v>212</v>
       </c>
       <c r="B193" s="18" t="s">
-        <v>952</v>
+        <v>939</v>
       </c>
       <c r="C193" s="18" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
       <c r="D193" t="s">
         <v>1106</v>
       </c>
       <c r="E193" s="18" t="s">
-        <v>953</v>
+        <v>938</v>
       </c>
       <c r="F193" s="16"/>
       <c r="G193" s="16"/>
@@ -7743,16 +7902,16 @@
         <v>212</v>
       </c>
       <c r="B194" s="18" t="s">
-        <v>1119</v>
+        <v>940</v>
       </c>
       <c r="C194" s="18" t="s">
-        <v>1121</v>
+        <v>942</v>
       </c>
       <c r="D194" t="s">
         <v>1106</v>
       </c>
       <c r="E194" s="18" t="s">
-        <v>1124</v>
+        <v>938</v>
       </c>
       <c r="F194" s="16"/>
       <c r="G194" s="16"/>
@@ -7762,16 +7921,16 @@
         <v>212</v>
       </c>
       <c r="B195" s="18" t="s">
-        <v>1120</v>
+        <v>1136</v>
       </c>
       <c r="C195" s="18" t="s">
-        <v>1122</v>
-      </c>
-      <c r="D195" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D195" s="18" t="s">
         <v>1106</v>
       </c>
       <c r="E195" s="18" t="s">
-        <v>1123</v>
+        <v>945</v>
       </c>
       <c r="F195" s="16"/>
       <c r="G195" s="16"/>
@@ -7781,16 +7940,16 @@
         <v>212</v>
       </c>
       <c r="B196" s="18" t="s">
-        <v>954</v>
+        <v>943</v>
       </c>
       <c r="C196" s="18" t="s">
-        <v>955</v>
+        <v>944</v>
       </c>
       <c r="D196" t="s">
         <v>1106</v>
       </c>
       <c r="E196" s="18" t="s">
-        <v>968</v>
+        <v>945</v>
       </c>
       <c r="F196" s="16"/>
       <c r="G196" s="16"/>
@@ -7800,16 +7959,16 @@
         <v>212</v>
       </c>
       <c r="B197" s="18" t="s">
-        <v>956</v>
+        <v>1138</v>
       </c>
       <c r="C197" s="18" t="s">
-        <v>959</v>
+        <v>948</v>
       </c>
       <c r="D197" t="s">
         <v>1106</v>
       </c>
       <c r="E197" s="18" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="F197" s="16"/>
       <c r="G197" s="16"/>
@@ -7819,16 +7978,16 @@
         <v>212</v>
       </c>
       <c r="B198" s="18" t="s">
-        <v>957</v>
+        <v>946</v>
       </c>
       <c r="C198" s="18" t="s">
-        <v>960</v>
+        <v>948</v>
       </c>
       <c r="D198" t="s">
         <v>1106</v>
       </c>
       <c r="E198" s="18" t="s">
-        <v>970</v>
+        <v>949</v>
       </c>
       <c r="F198" s="16"/>
       <c r="G198" s="16"/>
@@ -7838,16 +7997,16 @@
         <v>212</v>
       </c>
       <c r="B199" s="18" t="s">
-        <v>958</v>
+        <v>947</v>
       </c>
       <c r="C199" s="18" t="s">
-        <v>961</v>
+        <v>948</v>
       </c>
       <c r="D199" t="s">
         <v>1106</v>
       </c>
       <c r="E199" s="18" t="s">
-        <v>971</v>
+        <v>949</v>
       </c>
       <c r="F199" s="16"/>
       <c r="G199" s="16"/>
@@ -7857,16 +8016,16 @@
         <v>212</v>
       </c>
       <c r="B200" s="18" t="s">
-        <v>963</v>
+        <v>951</v>
       </c>
       <c r="C200" s="18" t="s">
-        <v>962</v>
+        <v>950</v>
       </c>
       <c r="D200" t="s">
         <v>1106</v>
       </c>
       <c r="E200" s="18" t="s">
-        <v>996</v>
+        <v>953</v>
       </c>
       <c r="F200" s="16"/>
       <c r="G200" s="16"/>
@@ -7876,16 +8035,16 @@
         <v>212</v>
       </c>
       <c r="B201" s="18" t="s">
-        <v>965</v>
+        <v>952</v>
       </c>
       <c r="C201" s="18" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="D201" t="s">
         <v>1106</v>
       </c>
       <c r="E201" s="18" t="s">
-        <v>972</v>
+        <v>953</v>
       </c>
       <c r="F201" s="16"/>
       <c r="G201" s="16"/>
@@ -7895,16 +8054,16 @@
         <v>212</v>
       </c>
       <c r="B202" s="18" t="s">
-        <v>966</v>
+        <v>1113</v>
       </c>
       <c r="C202" s="18" t="s">
-        <v>967</v>
+        <v>1115</v>
       </c>
       <c r="D202" t="s">
         <v>1106</v>
       </c>
       <c r="E202" s="18" t="s">
-        <v>973</v>
+        <v>1118</v>
       </c>
       <c r="F202" s="16"/>
       <c r="G202" s="16"/>
@@ -7914,16 +8073,16 @@
         <v>212</v>
       </c>
       <c r="B203" s="18" t="s">
-        <v>974</v>
+        <v>1114</v>
       </c>
       <c r="C203" s="18" t="s">
-        <v>975</v>
+        <v>1116</v>
       </c>
       <c r="D203" t="s">
         <v>1106</v>
       </c>
       <c r="E203" s="18" t="s">
-        <v>997</v>
+        <v>1117</v>
       </c>
       <c r="F203" s="16"/>
       <c r="G203" s="16"/>
@@ -7933,16 +8092,16 @@
         <v>212</v>
       </c>
       <c r="B204" s="18" t="s">
-        <v>977</v>
+        <v>954</v>
       </c>
       <c r="C204" s="18" t="s">
-        <v>976</v>
+        <v>955</v>
       </c>
       <c r="D204" t="s">
         <v>1106</v>
       </c>
       <c r="E204" s="18" t="s">
-        <v>978</v>
+        <v>968</v>
       </c>
       <c r="F204" s="16"/>
       <c r="G204" s="16"/>
@@ -7952,16 +8111,16 @@
         <v>212</v>
       </c>
       <c r="B205" s="18" t="s">
-        <v>979</v>
+        <v>956</v>
       </c>
       <c r="C205" s="18" t="s">
-        <v>980</v>
+        <v>959</v>
       </c>
       <c r="D205" t="s">
         <v>1106</v>
       </c>
       <c r="E205" s="18" t="s">
-        <v>981</v>
+        <v>969</v>
       </c>
       <c r="F205" s="16"/>
       <c r="G205" s="16"/>
@@ -7971,16 +8130,16 @@
         <v>212</v>
       </c>
       <c r="B206" s="18" t="s">
-        <v>985</v>
+        <v>957</v>
       </c>
       <c r="C206" s="18" t="s">
-        <v>986</v>
+        <v>960</v>
       </c>
       <c r="D206" t="s">
         <v>1106</v>
       </c>
       <c r="E206" s="18" t="s">
-        <v>998</v>
+        <v>970</v>
       </c>
       <c r="F206" s="16"/>
       <c r="G206" s="16"/>
@@ -7990,16 +8149,16 @@
         <v>212</v>
       </c>
       <c r="B207" s="18" t="s">
-        <v>987</v>
+        <v>958</v>
       </c>
       <c r="C207" s="18" t="s">
-        <v>988</v>
+        <v>961</v>
       </c>
       <c r="D207" t="s">
         <v>1106</v>
       </c>
       <c r="E207" s="18" t="s">
-        <v>989</v>
+        <v>971</v>
       </c>
       <c r="F207" s="16"/>
       <c r="G207" s="16"/>
@@ -8009,16 +8168,16 @@
         <v>212</v>
       </c>
       <c r="B208" s="18" t="s">
-        <v>982</v>
+        <v>963</v>
       </c>
       <c r="C208" s="18" t="s">
-        <v>990</v>
+        <v>962</v>
       </c>
       <c r="D208" t="s">
         <v>1106</v>
       </c>
       <c r="E208" s="18" t="s">
-        <v>1008</v>
+        <v>996</v>
       </c>
       <c r="F208" s="16"/>
       <c r="G208" s="16"/>
@@ -8028,16 +8187,16 @@
         <v>212</v>
       </c>
       <c r="B209" s="18" t="s">
-        <v>991</v>
+        <v>965</v>
       </c>
       <c r="C209" s="18" t="s">
-        <v>992</v>
+        <v>964</v>
       </c>
       <c r="D209" t="s">
         <v>1106</v>
       </c>
       <c r="E209" s="18" t="s">
-        <v>999</v>
+        <v>972</v>
       </c>
       <c r="F209" s="16"/>
       <c r="G209" s="16"/>
@@ -8047,16 +8206,16 @@
         <v>212</v>
       </c>
       <c r="B210" s="18" t="s">
-        <v>993</v>
+        <v>966</v>
       </c>
       <c r="C210" s="18" t="s">
-        <v>994</v>
+        <v>967</v>
       </c>
       <c r="D210" t="s">
         <v>1106</v>
       </c>
       <c r="E210" s="18" t="s">
-        <v>995</v>
+        <v>973</v>
       </c>
       <c r="F210" s="16"/>
       <c r="G210" s="16"/>
@@ -8066,16 +8225,16 @@
         <v>212</v>
       </c>
       <c r="B211" s="18" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
       <c r="C211" s="18" t="s">
-        <v>1000</v>
+        <v>975</v>
       </c>
       <c r="D211" t="s">
         <v>1106</v>
       </c>
       <c r="E211" s="18" t="s">
-        <v>1009</v>
+        <v>997</v>
       </c>
       <c r="F211" s="16"/>
       <c r="G211" s="16"/>
@@ -8085,16 +8244,16 @@
         <v>212</v>
       </c>
       <c r="B212" s="18" t="s">
-        <v>1003</v>
+        <v>977</v>
       </c>
       <c r="C212" s="18" t="s">
-        <v>1001</v>
+        <v>976</v>
       </c>
       <c r="D212" t="s">
         <v>1106</v>
       </c>
       <c r="E212" s="18" t="s">
-        <v>1002</v>
+        <v>978</v>
       </c>
       <c r="F212" s="16"/>
       <c r="G212" s="16"/>
@@ -8104,16 +8263,16 @@
         <v>212</v>
       </c>
       <c r="B213" s="18" t="s">
-        <v>1004</v>
+        <v>979</v>
       </c>
       <c r="C213" s="18" t="s">
-        <v>1005</v>
+        <v>980</v>
       </c>
       <c r="D213" t="s">
         <v>1106</v>
       </c>
       <c r="E213" s="18" t="s">
-        <v>1006</v>
+        <v>981</v>
       </c>
       <c r="F213" s="16"/>
       <c r="G213" s="16"/>
@@ -8123,16 +8282,16 @@
         <v>212</v>
       </c>
       <c r="B214" s="18" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C214" s="18" t="s">
-        <v>1007</v>
+        <v>986</v>
       </c>
       <c r="D214" t="s">
         <v>1106</v>
       </c>
       <c r="E214" s="18" t="s">
-        <v>1010</v>
+        <v>998</v>
       </c>
       <c r="F214" s="16"/>
       <c r="G214" s="16"/>
@@ -8142,16 +8301,16 @@
         <v>212</v>
       </c>
       <c r="B215" s="18" t="s">
-        <v>1110</v>
+        <v>987</v>
       </c>
       <c r="C215" s="18" t="s">
-        <v>1115</v>
+        <v>988</v>
       </c>
       <c r="D215" t="s">
         <v>1106</v>
       </c>
       <c r="E215" s="18" t="s">
-        <v>1117</v>
+        <v>989</v>
       </c>
       <c r="F215" s="16"/>
       <c r="G215" s="16"/>
@@ -8161,16 +8320,16 @@
         <v>212</v>
       </c>
       <c r="B216" s="18" t="s">
-        <v>1112</v>
+        <v>982</v>
       </c>
       <c r="C216" s="18" t="s">
-        <v>1114</v>
+        <v>990</v>
       </c>
       <c r="D216" t="s">
         <v>1106</v>
       </c>
       <c r="E216" s="18" t="s">
-        <v>1116</v>
+        <v>1008</v>
       </c>
       <c r="F216" s="16"/>
       <c r="G216" s="16"/>
@@ -8180,415 +8339,415 @@
         <v>212</v>
       </c>
       <c r="B217" s="18" t="s">
-        <v>1111</v>
+        <v>991</v>
       </c>
       <c r="C217" s="18" t="s">
-        <v>1113</v>
+        <v>992</v>
       </c>
       <c r="D217" t="s">
         <v>1106</v>
       </c>
       <c r="E217" s="18" t="s">
-        <v>1118</v>
+        <v>999</v>
       </c>
       <c r="F217" s="16"/>
       <c r="G217" s="16"/>
     </row>
     <row r="218" spans="1:7">
       <c r="A218" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B218" s="18" t="s">
-        <v>636</v>
+        <v>993</v>
       </c>
       <c r="C218" s="18" t="s">
-        <v>662</v>
+        <v>994</v>
       </c>
       <c r="D218" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E218" s="18" t="s">
-        <v>674</v>
+        <v>995</v>
       </c>
       <c r="F218" s="16"/>
       <c r="G218" s="16"/>
     </row>
     <row r="219" spans="1:7">
       <c r="A219" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B219" s="18" t="s">
-        <v>637</v>
+        <v>983</v>
       </c>
       <c r="C219" s="18" t="s">
-        <v>663</v>
+        <v>1000</v>
       </c>
       <c r="D219" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E219" s="18" t="s">
-        <v>675</v>
+        <v>1009</v>
       </c>
       <c r="F219" s="16"/>
       <c r="G219" s="16"/>
     </row>
     <row r="220" spans="1:7">
       <c r="A220" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B220" s="18" t="s">
-        <v>638</v>
+        <v>1003</v>
       </c>
       <c r="C220" s="18" t="s">
-        <v>676</v>
+        <v>1001</v>
       </c>
       <c r="D220" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E220" s="18" t="s">
-        <v>677</v>
+        <v>1002</v>
       </c>
       <c r="F220" s="16"/>
       <c r="G220" s="16"/>
     </row>
     <row r="221" spans="1:7">
       <c r="A221" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B221" s="18" t="s">
-        <v>649</v>
+        <v>1004</v>
       </c>
       <c r="C221" s="18" t="s">
-        <v>648</v>
+        <v>1005</v>
       </c>
       <c r="D221" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E221" s="18" t="s">
-        <v>678</v>
+        <v>1006</v>
       </c>
       <c r="F221" s="16"/>
       <c r="G221" s="16"/>
     </row>
     <row r="222" spans="1:7">
       <c r="A222" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B222" s="18" t="s">
-        <v>650</v>
-      </c>
-      <c r="C222" s="19" t="s">
-        <v>651</v>
+        <v>984</v>
+      </c>
+      <c r="C222" s="18" t="s">
+        <v>1007</v>
       </c>
       <c r="D222" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E222" s="18" t="s">
-        <v>679</v>
+        <v>1010</v>
       </c>
       <c r="F222" s="16"/>
       <c r="G222" s="16"/>
     </row>
     <row r="223" spans="1:7">
       <c r="A223" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B223" s="18" t="s">
-        <v>639</v>
+        <v>1153</v>
       </c>
       <c r="C223" s="18" t="s">
-        <v>664</v>
+        <v>1154</v>
       </c>
       <c r="D223" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E223" s="18" t="s">
-        <v>717</v>
+        <v>1173</v>
       </c>
       <c r="F223" s="16"/>
       <c r="G223" s="16"/>
     </row>
     <row r="224" spans="1:7">
       <c r="A224" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B224" s="18" t="s">
-        <v>640</v>
+        <v>1155</v>
       </c>
       <c r="C224" s="18" t="s">
-        <v>665</v>
+        <v>1156</v>
       </c>
       <c r="D224" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E224" s="18" t="s">
-        <v>718</v>
+        <v>1167</v>
       </c>
       <c r="F224" s="16"/>
       <c r="G224" s="16"/>
     </row>
     <row r="225" spans="1:7">
       <c r="A225" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B225" s="18" t="s">
-        <v>641</v>
+        <v>1158</v>
       </c>
       <c r="C225" s="18" t="s">
-        <v>666</v>
+        <v>1159</v>
       </c>
       <c r="D225" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E225" s="18" t="s">
-        <v>719</v>
+        <v>1168</v>
       </c>
       <c r="F225" s="16"/>
       <c r="G225" s="16"/>
     </row>
     <row r="226" spans="1:7">
       <c r="A226" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B226" s="18" t="s">
-        <v>642</v>
+        <v>1157</v>
       </c>
       <c r="C226" s="18" t="s">
-        <v>667</v>
+        <v>1160</v>
       </c>
       <c r="D226" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E226" s="18" t="s">
-        <v>673</v>
+        <v>1169</v>
       </c>
       <c r="F226" s="16"/>
       <c r="G226" s="16"/>
     </row>
     <row r="227" spans="1:7">
       <c r="A227" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B227" s="18" t="s">
-        <v>643</v>
+        <v>1161</v>
       </c>
       <c r="C227" s="18" t="s">
-        <v>668</v>
+        <v>1162</v>
       </c>
       <c r="D227" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E227" s="18" t="s">
-        <v>720</v>
+        <v>1170</v>
       </c>
       <c r="F227" s="16"/>
       <c r="G227" s="16"/>
     </row>
     <row r="228" spans="1:7">
       <c r="A228" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B228" s="18" t="s">
-        <v>644</v>
+        <v>1163</v>
       </c>
       <c r="C228" s="18" t="s">
-        <v>669</v>
+        <v>1164</v>
       </c>
       <c r="D228" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E228" s="18" t="s">
-        <v>721</v>
+        <v>1171</v>
       </c>
       <c r="F228" s="16"/>
       <c r="G228" s="16"/>
     </row>
     <row r="229" spans="1:7">
       <c r="A229" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B229" s="18" t="s">
-        <v>645</v>
+        <v>1165</v>
       </c>
       <c r="C229" s="18" t="s">
-        <v>670</v>
+        <v>1166</v>
       </c>
       <c r="D229" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E229" s="18" t="s">
-        <v>722</v>
+        <v>1172</v>
       </c>
       <c r="F229" s="16"/>
       <c r="G229" s="16"/>
     </row>
     <row r="230" spans="1:7">
       <c r="A230" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B230" s="18" t="s">
-        <v>646</v>
+        <v>1175</v>
       </c>
       <c r="C230" s="18" t="s">
-        <v>671</v>
+        <v>1174</v>
       </c>
       <c r="D230" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E230" s="18" t="s">
-        <v>672</v>
+        <v>1190</v>
       </c>
       <c r="F230" s="16"/>
       <c r="G230" s="16"/>
     </row>
     <row r="231" spans="1:7">
       <c r="A231" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B231" s="18" t="s">
-        <v>1089</v>
+        <v>1177</v>
       </c>
       <c r="C231" s="18" t="s">
-        <v>1095</v>
+        <v>1176</v>
       </c>
       <c r="D231" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E231" s="18" t="s">
-        <v>717</v>
+        <v>1191</v>
       </c>
       <c r="F231" s="16"/>
       <c r="G231" s="16"/>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B232" s="18" t="s">
-        <v>1090</v>
+        <v>1178</v>
       </c>
       <c r="C232" s="18" t="s">
-        <v>1096</v>
+        <v>1179</v>
       </c>
       <c r="D232" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E232" s="18" t="s">
-        <v>718</v>
+        <v>1193</v>
       </c>
       <c r="F232" s="16"/>
       <c r="G232" s="16"/>
     </row>
     <row r="233" spans="1:7">
       <c r="A233" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B233" s="18" t="s">
-        <v>1091</v>
+        <v>1180</v>
       </c>
       <c r="C233" s="18" t="s">
-        <v>1097</v>
+        <v>1181</v>
       </c>
       <c r="D233" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E233" s="18" t="s">
-        <v>719</v>
+        <v>1192</v>
       </c>
       <c r="F233" s="16"/>
       <c r="G233" s="16"/>
     </row>
     <row r="234" spans="1:7">
       <c r="A234" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B234" s="18" t="s">
-        <v>1092</v>
+        <v>1182</v>
       </c>
       <c r="C234" s="18" t="s">
-        <v>1098</v>
+        <v>1183</v>
       </c>
       <c r="D234" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E234" s="18" t="s">
-        <v>720</v>
+        <v>1194</v>
       </c>
       <c r="F234" s="16"/>
       <c r="G234" s="16"/>
     </row>
     <row r="235" spans="1:7">
       <c r="A235" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B235" s="18" t="s">
-        <v>1093</v>
+        <v>1185</v>
       </c>
       <c r="C235" s="18" t="s">
-        <v>1099</v>
+        <v>1184</v>
       </c>
       <c r="D235" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E235" s="18" t="s">
-        <v>721</v>
+        <v>1195</v>
       </c>
       <c r="F235" s="16"/>
       <c r="G235" s="16"/>
     </row>
     <row r="236" spans="1:7">
       <c r="A236" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B236" s="18" t="s">
-        <v>1094</v>
+        <v>1187</v>
       </c>
       <c r="C236" s="18" t="s">
-        <v>1100</v>
+        <v>1186</v>
       </c>
       <c r="D236" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E236" s="18" t="s">
-        <v>722</v>
+        <v>1196</v>
       </c>
       <c r="F236" s="16"/>
       <c r="G236" s="16"/>
     </row>
     <row r="237" spans="1:7">
       <c r="A237" s="18" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="B237" s="18" t="s">
-        <v>1016</v>
+        <v>1189</v>
       </c>
       <c r="C237" s="18" t="s">
-        <v>1017</v>
+        <v>1188</v>
       </c>
       <c r="D237" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E237" s="18" t="s">
-        <v>1023</v>
+        <v>1197</v>
       </c>
       <c r="F237" s="16"/>
       <c r="G237" s="16"/>
     </row>
-    <row r="238" spans="1:7">
+    <row r="238" spans="1:7" ht="15" customHeight="1">
       <c r="A238" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B238" s="18" t="s">
-        <v>1018</v>
+        <v>636</v>
       </c>
       <c r="C238" s="18" t="s">
-        <v>1019</v>
+        <v>662</v>
       </c>
       <c r="D238" t="s">
         <v>1107</v>
       </c>
       <c r="E238" s="18" t="s">
-        <v>1024</v>
+        <v>674</v>
       </c>
       <c r="F238" s="16"/>
       <c r="G238" s="16"/>
@@ -8598,16 +8757,16 @@
         <v>282</v>
       </c>
       <c r="B239" s="18" t="s">
-        <v>1020</v>
+        <v>637</v>
       </c>
       <c r="C239" s="18" t="s">
-        <v>1027</v>
+        <v>663</v>
       </c>
       <c r="D239" t="s">
         <v>1107</v>
       </c>
       <c r="E239" s="18" t="s">
-        <v>1025</v>
+        <v>675</v>
       </c>
       <c r="F239" s="16"/>
       <c r="G239" s="16"/>
@@ -8617,16 +8776,16 @@
         <v>282</v>
       </c>
       <c r="B240" s="18" t="s">
-        <v>1040</v>
+        <v>638</v>
       </c>
       <c r="C240" s="18" t="s">
-        <v>1041</v>
+        <v>676</v>
       </c>
       <c r="D240" t="s">
         <v>1107</v>
       </c>
       <c r="E240" s="18" t="s">
-        <v>1026</v>
+        <v>677</v>
       </c>
       <c r="F240" s="16"/>
       <c r="G240" s="16"/>
@@ -8636,16 +8795,16 @@
         <v>282</v>
       </c>
       <c r="B241" s="18" t="s">
-        <v>1021</v>
+        <v>649</v>
       </c>
       <c r="C241" s="18" t="s">
-        <v>1022</v>
+        <v>648</v>
       </c>
       <c r="D241" t="s">
         <v>1107</v>
       </c>
       <c r="E241" s="18" t="s">
-        <v>1042</v>
+        <v>678</v>
       </c>
       <c r="F241" s="16"/>
       <c r="G241" s="16"/>
@@ -8655,515 +8814,499 @@
         <v>282</v>
       </c>
       <c r="B242" s="18" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C242" s="18" t="s">
-        <v>1032</v>
+        <v>650</v>
+      </c>
+      <c r="C242" s="19" t="s">
+        <v>651</v>
       </c>
       <c r="D242" t="s">
         <v>1107</v>
       </c>
       <c r="E242" s="18" t="s">
-        <v>1038</v>
-      </c>
-      <c r="F242" s="20"/>
-      <c r="G242" s="20"/>
+        <v>679</v>
+      </c>
+      <c r="F242" s="16"/>
+      <c r="G242" s="16"/>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B243" s="18" t="s">
-        <v>1033</v>
+        <v>639</v>
       </c>
       <c r="C243" s="18" t="s">
-        <v>1034</v>
+        <v>664</v>
       </c>
       <c r="D243" t="s">
         <v>1107</v>
       </c>
       <c r="E243" s="18" t="s">
-        <v>1035</v>
-      </c>
-      <c r="F243" s="20"/>
-      <c r="G243" s="20"/>
+        <v>717</v>
+      </c>
+      <c r="F243" s="16"/>
+      <c r="G243" s="16"/>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B244" s="18" t="s">
-        <v>1036</v>
+        <v>640</v>
       </c>
       <c r="C244" s="18" t="s">
-        <v>1037</v>
+        <v>665</v>
       </c>
       <c r="D244" t="s">
         <v>1107</v>
       </c>
       <c r="E244" s="18" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F244" s="20"/>
-      <c r="G244" s="20"/>
+        <v>718</v>
+      </c>
+      <c r="F244" s="16"/>
+      <c r="G244" s="16"/>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B245" s="18" t="s">
-        <v>5</v>
+        <v>641</v>
       </c>
       <c r="C245" s="18" t="s">
-        <v>4</v>
+        <v>666</v>
       </c>
       <c r="D245" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E245" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F245" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G245" s="16" t="s">
-        <v>7</v>
-      </c>
+        <v>719</v>
+      </c>
+      <c r="F245" s="16"/>
+      <c r="G245" s="16"/>
     </row>
     <row r="246" spans="1:7">
       <c r="A246" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>9</v>
+        <v>642</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>8</v>
+        <v>667</v>
       </c>
       <c r="D246" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E246" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="F246" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G246" s="16" t="s">
-        <v>10</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="F246" s="16"/>
+      <c r="G246" s="16"/>
     </row>
     <row r="247" spans="1:7">
       <c r="A247" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>12</v>
+        <v>643</v>
       </c>
       <c r="C247" s="18" t="s">
-        <v>11</v>
+        <v>668</v>
       </c>
       <c r="D247" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E247" s="18" t="s">
-        <v>167</v>
+        <v>720</v>
       </c>
       <c r="F247" s="16"/>
       <c r="G247" s="16"/>
     </row>
     <row r="248" spans="1:7">
       <c r="A248" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B248" s="18" t="s">
-        <v>14</v>
+        <v>644</v>
       </c>
       <c r="C248" s="18" t="s">
-        <v>13</v>
+        <v>669</v>
       </c>
       <c r="D248" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E248" s="18" t="s">
-        <v>166</v>
+        <v>721</v>
       </c>
       <c r="F248" s="16"/>
       <c r="G248" s="16"/>
     </row>
     <row r="249" spans="1:7">
       <c r="A249" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>16</v>
+        <v>645</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>15</v>
+        <v>670</v>
       </c>
       <c r="D249" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E249" s="18" t="s">
-        <v>168</v>
+        <v>722</v>
       </c>
       <c r="F249" s="16"/>
       <c r="G249" s="16"/>
     </row>
     <row r="250" spans="1:7">
       <c r="A250" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B250" s="18" t="s">
-        <v>19</v>
+        <v>646</v>
       </c>
       <c r="C250" s="18" t="s">
-        <v>18</v>
+        <v>671</v>
       </c>
       <c r="D250" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E250" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="F250" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G250" s="16" t="s">
-        <v>134</v>
-      </c>
+        <v>672</v>
+      </c>
+      <c r="F250" s="16"/>
+      <c r="G250" s="16"/>
     </row>
     <row r="251" spans="1:7">
       <c r="A251" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>133</v>
+        <v>1089</v>
       </c>
       <c r="C251" s="18" t="s">
-        <v>20</v>
+        <v>1095</v>
       </c>
       <c r="D251" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E251" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="F251" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G251" s="16" t="s">
-        <v>21</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="F251" s="16"/>
+      <c r="G251" s="16"/>
     </row>
     <row r="252" spans="1:7">
       <c r="A252" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>132</v>
+        <v>1090</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>17</v>
+        <v>1096</v>
       </c>
       <c r="D252" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E252" s="18" t="s">
-        <v>140</v>
+        <v>718</v>
       </c>
       <c r="F252" s="16"/>
       <c r="G252" s="16"/>
     </row>
     <row r="253" spans="1:7">
       <c r="A253" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>23</v>
+        <v>1091</v>
       </c>
       <c r="C253" s="18" t="s">
-        <v>24</v>
+        <v>1097</v>
       </c>
       <c r="D253" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E253" s="18" t="s">
-        <v>139</v>
+        <v>719</v>
       </c>
       <c r="F253" s="16"/>
       <c r="G253" s="16"/>
     </row>
     <row r="254" spans="1:7">
       <c r="A254" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>141</v>
+        <v>1092</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>22</v>
+        <v>1098</v>
       </c>
       <c r="D254" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E254" s="18" t="s">
-        <v>142</v>
+        <v>720</v>
       </c>
       <c r="F254" s="16"/>
       <c r="G254" s="16"/>
     </row>
     <row r="255" spans="1:7">
       <c r="A255" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>25</v>
+        <v>1093</v>
       </c>
       <c r="C255" s="18" t="s">
-        <v>26</v>
+        <v>1099</v>
       </c>
       <c r="D255" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E255" s="18" t="s">
-        <v>143</v>
+        <v>721</v>
       </c>
       <c r="F255" s="16"/>
       <c r="G255" s="16"/>
     </row>
     <row r="256" spans="1:7">
       <c r="A256" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B256" s="18" t="s">
-        <v>27</v>
+        <v>1094</v>
       </c>
       <c r="C256" s="18" t="s">
-        <v>28</v>
+        <v>1100</v>
       </c>
       <c r="D256" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E256" s="18" t="s">
-        <v>149</v>
+        <v>722</v>
       </c>
       <c r="F256" s="16"/>
       <c r="G256" s="16"/>
     </row>
     <row r="257" spans="1:7">
       <c r="A257" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B257" s="18" t="s">
-        <v>29</v>
+        <v>1016</v>
       </c>
       <c r="C257" s="18" t="s">
-        <v>30</v>
+        <v>1017</v>
       </c>
       <c r="D257" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E257" s="18" t="s">
-        <v>148</v>
+        <v>1023</v>
       </c>
       <c r="F257" s="16"/>
       <c r="G257" s="16"/>
     </row>
     <row r="258" spans="1:7">
       <c r="A258" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B258" s="18" t="s">
-        <v>31</v>
+        <v>1018</v>
       </c>
       <c r="C258" s="18" t="s">
-        <v>32</v>
+        <v>1019</v>
       </c>
       <c r="D258" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E258" s="18" t="s">
-        <v>147</v>
+        <v>1024</v>
       </c>
       <c r="F258" s="16"/>
       <c r="G258" s="16"/>
     </row>
     <row r="259" spans="1:7">
       <c r="A259" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B259" s="18" t="s">
-        <v>33</v>
+        <v>1020</v>
       </c>
       <c r="C259" s="18" t="s">
-        <v>34</v>
+        <v>1027</v>
       </c>
       <c r="D259" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E259" s="18" t="s">
-        <v>146</v>
+        <v>1025</v>
       </c>
       <c r="F259" s="16"/>
       <c r="G259" s="16"/>
     </row>
     <row r="260" spans="1:7">
       <c r="A260" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B260" s="18" t="s">
-        <v>35</v>
+        <v>1040</v>
       </c>
       <c r="C260" s="18" t="s">
-        <v>36</v>
+        <v>1041</v>
       </c>
       <c r="D260" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E260" s="18" t="s">
-        <v>145</v>
+        <v>1026</v>
       </c>
       <c r="F260" s="16"/>
       <c r="G260" s="16"/>
     </row>
     <row r="261" spans="1:7">
       <c r="A261" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B261" s="18" t="s">
-        <v>37</v>
+        <v>1021</v>
       </c>
       <c r="C261" s="18" t="s">
-        <v>38</v>
+        <v>1022</v>
       </c>
       <c r="D261" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E261" s="18" t="s">
-        <v>144</v>
+        <v>1042</v>
       </c>
       <c r="F261" s="16"/>
       <c r="G261" s="16"/>
     </row>
     <row r="262" spans="1:7">
       <c r="A262" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B262" s="18" t="s">
-        <v>39</v>
+        <v>1031</v>
       </c>
       <c r="C262" s="18" t="s">
-        <v>150</v>
+        <v>1032</v>
       </c>
       <c r="D262" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E262" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="F262" s="16"/>
-      <c r="G262" s="16"/>
+        <v>1038</v>
+      </c>
+      <c r="F262" s="20"/>
+      <c r="G262" s="20"/>
     </row>
     <row r="263" spans="1:7">
       <c r="A263" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="B263" s="28" t="s">
-        <v>40</v>
+        <v>282</v>
+      </c>
+      <c r="B263" s="18" t="s">
+        <v>1033</v>
       </c>
       <c r="C263" s="18" t="s">
-        <v>4</v>
+        <v>1034</v>
       </c>
       <c r="D263" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E263" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="F263" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G263" s="16" t="s">
-        <v>7</v>
-      </c>
+        <v>1035</v>
+      </c>
+      <c r="F263" s="20"/>
+      <c r="G263" s="20"/>
     </row>
     <row r="264" spans="1:7">
       <c r="A264" s="18" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B264" s="18" t="s">
-        <v>9</v>
+        <v>1036</v>
       </c>
       <c r="C264" s="18" t="s">
-        <v>8</v>
+        <v>1037</v>
       </c>
       <c r="D264" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E264" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="F264" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G264" s="16" t="s">
-        <v>10</v>
-      </c>
+        <v>1039</v>
+      </c>
+      <c r="F264" s="20"/>
+      <c r="G264" s="20"/>
     </row>
     <row r="265" spans="1:7">
       <c r="A265" s="18" t="s">
         <v>118</v>
       </c>
       <c r="B265" s="18" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C265" s="18" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D265" t="s">
         <v>1109</v>
       </c>
       <c r="E265" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="F265" s="16"/>
-      <c r="G265" s="16"/>
+        <v>164</v>
+      </c>
+      <c r="F265" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G265" s="16" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="266" spans="1:7">
       <c r="A266" s="18" t="s">
         <v>118</v>
       </c>
       <c r="B266" s="18" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C266" s="18" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D266" t="s">
         <v>1109</v>
       </c>
       <c r="E266" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="F266" s="16"/>
-      <c r="G266" s="16"/>
+        <v>165</v>
+      </c>
+      <c r="F266" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G266" s="16" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="267" spans="1:7">
       <c r="A267" s="18" t="s">
         <v>118</v>
       </c>
       <c r="B267" s="18" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C267" s="18" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D267" t="s">
         <v>1109</v>
       </c>
       <c r="E267" s="18" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F267" s="16"/>
       <c r="G267" s="16"/>
@@ -9173,16 +9316,16 @@
         <v>118</v>
       </c>
       <c r="B268" s="18" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="C268" s="18" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D268" t="s">
         <v>1109</v>
       </c>
       <c r="E268" s="18" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="F268" s="16"/>
       <c r="G268" s="16"/>
@@ -9192,16 +9335,16 @@
         <v>118</v>
       </c>
       <c r="B269" s="18" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C269" s="18" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D269" t="s">
         <v>1109</v>
       </c>
       <c r="E269" s="18" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="F269" s="16"/>
       <c r="G269" s="16"/>
@@ -9211,54 +9354,62 @@
         <v>118</v>
       </c>
       <c r="B270" s="18" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="C270" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D270" t="s">
         <v>1109</v>
       </c>
       <c r="E270" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="F270" s="16"/>
-      <c r="G270" s="16"/>
+        <v>137</v>
+      </c>
+      <c r="F270" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G270" s="16" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="271" spans="1:7">
       <c r="A271" s="18" t="s">
         <v>118</v>
       </c>
       <c r="B271" s="18" t="s">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="C271" s="18" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D271" t="s">
         <v>1109</v>
       </c>
       <c r="E271" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="F271" s="16"/>
-      <c r="G271" s="16"/>
+        <v>138</v>
+      </c>
+      <c r="F271" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G271" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="272" spans="1:7">
       <c r="A272" s="18" t="s">
         <v>118</v>
       </c>
       <c r="B272" s="18" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="C272" s="18" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D272" t="s">
         <v>1109</v>
       </c>
       <c r="E272" s="18" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="F272" s="16"/>
       <c r="G272" s="16"/>
@@ -9268,16 +9419,16 @@
         <v>118</v>
       </c>
       <c r="B273" s="18" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C273" s="18" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D273" t="s">
         <v>1109</v>
       </c>
       <c r="E273" s="18" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="F273" s="16"/>
       <c r="G273" s="16"/>
@@ -9287,16 +9438,16 @@
         <v>118</v>
       </c>
       <c r="B274" s="18" t="s">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="C274" s="18" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D274" t="s">
         <v>1109</v>
       </c>
       <c r="E274" s="18" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="F274" s="16"/>
       <c r="G274" s="16"/>
@@ -9306,16 +9457,16 @@
         <v>118</v>
       </c>
       <c r="B275" s="18" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C275" s="18" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D275" t="s">
         <v>1109</v>
       </c>
       <c r="E275" s="18" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="F275" s="16"/>
       <c r="G275" s="16"/>
@@ -9325,16 +9476,16 @@
         <v>118</v>
       </c>
       <c r="B276" s="18" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C276" s="18" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D276" t="s">
         <v>1109</v>
       </c>
       <c r="E276" s="18" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="F276" s="16"/>
       <c r="G276" s="16"/>
@@ -9344,16 +9495,16 @@
         <v>118</v>
       </c>
       <c r="B277" s="18" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C277" s="18" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D277" t="s">
         <v>1109</v>
       </c>
       <c r="E277" s="18" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="F277" s="16"/>
       <c r="G277" s="16"/>
@@ -9363,16 +9514,16 @@
         <v>118</v>
       </c>
       <c r="B278" s="18" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C278" s="18" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D278" t="s">
         <v>1109</v>
       </c>
       <c r="E278" s="18" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="F278" s="16"/>
       <c r="G278" s="16"/>
@@ -9382,564 +9533,952 @@
         <v>118</v>
       </c>
       <c r="B279" s="18" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C279" s="18" t="s">
-        <v>150</v>
+        <v>34</v>
       </c>
       <c r="D279" t="s">
         <v>1109</v>
       </c>
       <c r="E279" s="18" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="F279" s="16"/>
       <c r="G279" s="16"/>
     </row>
     <row r="280" spans="1:7">
       <c r="A280" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B280" s="18" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C280" s="18" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D280" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E280" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="F280" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G280" s="16" t="s">
-        <v>58</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="F280" s="16"/>
+      <c r="G280" s="16"/>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B281" s="18" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C281" s="18" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="D281" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E281" s="18" t="s">
-        <v>622</v>
+        <v>144</v>
       </c>
       <c r="F281" s="16"/>
       <c r="G281" s="16"/>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B282" s="18" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="C282" s="18" t="s">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c r="D282" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E282" s="18" t="s">
-        <v>623</v>
-      </c>
-      <c r="F282" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G282" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="F282" s="16"/>
+      <c r="G282" s="16"/>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="B283" s="18" t="s">
-        <v>65</v>
+        <v>118</v>
+      </c>
+      <c r="B283" s="28" t="s">
+        <v>40</v>
       </c>
       <c r="C283" s="18" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="D283" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E283" s="18" t="s">
-        <v>627</v>
-      </c>
-      <c r="F283" s="16"/>
-      <c r="G283" s="16"/>
+        <v>169</v>
+      </c>
+      <c r="F283" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G283" s="16" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="284" spans="1:7">
       <c r="A284" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B284" s="18" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="C284" s="18" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="D284" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E284" s="18" t="s">
-        <v>626</v>
+        <v>170</v>
       </c>
       <c r="F284" s="16" t="s">
         <v>6</v>
       </c>
       <c r="G284" s="16" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
     </row>
     <row r="285" spans="1:7">
       <c r="A285" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B285" s="18" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="C285" s="18" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="D285" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E285" s="18" t="s">
-        <v>624</v>
+        <v>171</v>
       </c>
       <c r="F285" s="16"/>
       <c r="G285" s="16"/>
     </row>
     <row r="286" spans="1:7">
       <c r="A286" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B286" s="18" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C286" s="18" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="D286" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E286" s="18" t="s">
-        <v>625</v>
-      </c>
-      <c r="F286" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G286" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="F286" s="16"/>
+      <c r="G286" s="16"/>
     </row>
     <row r="287" spans="1:7">
       <c r="A287" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B287" s="18" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C287" s="18" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="D287" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E287" s="18" t="s">
-        <v>629</v>
+        <v>173</v>
       </c>
       <c r="F287" s="16"/>
       <c r="G287" s="16"/>
     </row>
     <row r="288" spans="1:7">
       <c r="A288" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B288" s="18" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="C288" s="18" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="D288" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E288" s="18" t="s">
-        <v>630</v>
-      </c>
-      <c r="F288" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G288" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="F288" s="16"/>
+      <c r="G288" s="16"/>
     </row>
     <row r="289" spans="1:7">
       <c r="A289" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B289" s="18" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="C289" s="18" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="D289" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E289" s="18" t="s">
-        <v>628</v>
+        <v>153</v>
       </c>
       <c r="F289" s="16"/>
       <c r="G289" s="16"/>
     </row>
     <row r="290" spans="1:7">
       <c r="A290" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B290" s="18" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="C290" s="18" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="D290" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E290" s="18" t="s">
-        <v>631</v>
-      </c>
-      <c r="F290" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G290" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="F290" s="16"/>
+      <c r="G290" s="16"/>
     </row>
     <row r="291" spans="1:7">
       <c r="A291" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B291" s="18" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C291" s="18" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="D291" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E291" s="18" t="s">
-        <v>684</v>
-      </c>
-      <c r="F291" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G291" s="16" t="s">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="F291" s="16"/>
+      <c r="G291" s="16"/>
     </row>
     <row r="292" spans="1:7">
       <c r="A292" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B292" s="18" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C292" s="18" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="D292" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E292" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="F292" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G292" s="16" t="s">
-        <v>85</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="F292" s="16"/>
+      <c r="G292" s="16"/>
     </row>
     <row r="293" spans="1:7">
       <c r="A293" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B293" s="18" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="C293" s="18" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="D293" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E293" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="F293" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G293" s="16" t="s">
-        <v>88</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="F293" s="16"/>
+      <c r="G293" s="16"/>
     </row>
     <row r="294" spans="1:7">
       <c r="A294" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B294" s="18" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="D294" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E294" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="F294" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G294" s="16" t="s">
-        <v>91</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="F294" s="16"/>
+      <c r="G294" s="16"/>
     </row>
     <row r="295" spans="1:7">
       <c r="A295" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B295" s="18" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="C295" s="18" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="D295" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E295" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="F295" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G295" s="16" t="s">
-        <v>94</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="F295" s="16"/>
+      <c r="G295" s="16"/>
     </row>
     <row r="296" spans="1:7">
       <c r="A296" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B296" s="18" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="C296" s="18" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="D296" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E296" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="F296" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G296" s="16" t="s">
-        <v>97</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="F296" s="16"/>
+      <c r="G296" s="16"/>
     </row>
     <row r="297" spans="1:7">
       <c r="A297" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="D297" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E297" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="F297" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G297" s="16" t="s">
-        <v>100</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="F297" s="16"/>
+      <c r="G297" s="16"/>
     </row>
     <row r="298" spans="1:7">
       <c r="A298" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B298" s="18" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="C298" s="18" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="D298" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E298" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="F298" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G298" s="16" t="s">
-        <v>103</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="F298" s="16"/>
+      <c r="G298" s="16"/>
     </row>
     <row r="299" spans="1:7">
       <c r="A299" s="18" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="B299" s="18" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="C299" s="18" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="D299" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E299" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="F299" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G299" s="16" t="s">
-        <v>106</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="F299" s="16"/>
+      <c r="G299" s="16"/>
     </row>
     <row r="300" spans="1:7">
       <c r="A300" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B300" s="18" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="C300" s="18" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D300" t="s">
         <v>1107</v>
       </c>
       <c r="E300" s="18" t="s">
-        <v>632</v>
-      </c>
-      <c r="F300" s="16"/>
-      <c r="G300" s="16"/>
+        <v>201</v>
+      </c>
+      <c r="F300" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G300" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="301" spans="1:7">
       <c r="A301" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B301" s="18" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="C301" s="18" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="D301" t="s">
         <v>1107</v>
       </c>
       <c r="E301" s="18" t="s">
-        <v>680</v>
-      </c>
-      <c r="F301" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G301" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>622</v>
+      </c>
+      <c r="F301" s="16"/>
+      <c r="G301" s="16"/>
     </row>
     <row r="302" spans="1:7">
       <c r="A302" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B302" s="18" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="C302" s="18" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="D302" t="s">
         <v>1107</v>
       </c>
       <c r="E302" s="18" t="s">
-        <v>682</v>
-      </c>
-      <c r="F302" s="16"/>
-      <c r="G302" s="16"/>
+        <v>623</v>
+      </c>
+      <c r="F302" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G302" s="16" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B303" s="18" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="C303" s="18" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="D303" t="s">
         <v>1107</v>
       </c>
       <c r="E303" s="18" t="s">
-        <v>681</v>
-      </c>
-      <c r="F303" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G303" s="16" t="s">
-        <v>63</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="F303" s="16"/>
+      <c r="G303" s="16"/>
     </row>
     <row r="304" spans="1:7">
       <c r="A304" s="18" t="s">
         <v>282</v>
       </c>
       <c r="B304" s="18" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="C304" s="18" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="D304" t="s">
         <v>1107</v>
       </c>
       <c r="E304" s="18" t="s">
-        <v>683</v>
+        <v>626</v>
       </c>
       <c r="F304" s="16" t="s">
         <v>6</v>
       </c>
       <c r="G304" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B305" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C305" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D305" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E305" s="18" t="s">
+        <v>624</v>
+      </c>
+      <c r="F305" s="16"/>
+      <c r="G305" s="16"/>
+    </row>
+    <row r="306" spans="1:7">
+      <c r="A306" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B306" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C306" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D306" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E306" s="18" t="s">
+        <v>625</v>
+      </c>
+      <c r="F306" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G306" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B307" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C307" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D307" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E307" s="18" t="s">
+        <v>629</v>
+      </c>
+      <c r="F307" s="16"/>
+      <c r="G307" s="16"/>
+    </row>
+    <row r="308" spans="1:7">
+      <c r="A308" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B308" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C308" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D308" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E308" s="18" t="s">
+        <v>630</v>
+      </c>
+      <c r="F308" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G308" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B309" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C309" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D309" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E309" s="18" t="s">
+        <v>628</v>
+      </c>
+      <c r="F309" s="16"/>
+      <c r="G309" s="16"/>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B310" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C310" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D310" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E310" s="18" t="s">
+        <v>631</v>
+      </c>
+      <c r="F310" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G310" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B311" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C311" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D311" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E311" s="18" t="s">
+        <v>684</v>
+      </c>
+      <c r="F311" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G311" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B312" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C312" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D312" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E312" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="F312" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G312" s="16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B313" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C313" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D313" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E313" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="F313" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G313" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B314" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C314" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D314" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E314" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="F314" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G314" s="16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B315" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C315" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D315" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E315" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="F315" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G315" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B316" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C316" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D316" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E316" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="F316" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G316" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B317" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C317" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D317" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E317" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="F317" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G317" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B318" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C318" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D318" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E318" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="F318" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G318" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7">
+      <c r="A319" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B319" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C319" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D319" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E319" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="F319" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G319" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7">
+      <c r="A320" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B320" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C320" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D320" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E320" s="18" t="s">
+        <v>632</v>
+      </c>
+      <c r="F320" s="16"/>
+      <c r="G320" s="16"/>
+    </row>
+    <row r="321" spans="1:7">
+      <c r="A321" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B321" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C321" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D321" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E321" s="18" t="s">
+        <v>680</v>
+      </c>
+      <c r="F321" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G321" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7">
+      <c r="A322" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B322" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C322" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D322" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E322" s="18" t="s">
+        <v>682</v>
+      </c>
+      <c r="F322" s="16"/>
+      <c r="G322" s="16"/>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="A323" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B323" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C323" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D323" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E323" s="18" t="s">
+        <v>681</v>
+      </c>
+      <c r="F323" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G323" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7">
+      <c r="A324" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B324" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C324" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D324" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E324" s="18" t="s">
+        <v>683</v>
+      </c>
+      <c r="F324" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G324" s="16" t="s">
         <v>117</v>
       </c>
     </row>
@@ -9959,30 +10498,30 @@
   <sheetData>
     <row r="1" spans="8:11">
       <c r="H1" s="33" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="I1" s="36" t="str" cm="1">
         <f t="array" ref="I1:I124">_xlfn.UNIQUE(H1:H200)</f>
         <v>q_alc_any_life</v>
       </c>
       <c r="K1" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="2" spans="8:11">
       <c r="H2" s="33" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="I2" s="36" t="str">
         <v>q_alc_any_yr</v>
       </c>
       <c r="K2" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="3" spans="8:11">
       <c r="H3" s="33" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="I3" s="36" t="str">
         <v>q_alc_drinksday</v>
@@ -9993,24 +10532,24 @@
     </row>
     <row r="4" spans="8:11">
       <c r="H4" s="33" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="I4" s="36" t="str">
         <v>q_alc_freq</v>
       </c>
       <c r="K4" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="5" spans="8:11">
       <c r="H5" s="33" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="I5" s="36" t="str">
         <v>q_alc_freq_units</v>
       </c>
       <c r="K5" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="6" spans="8:11">
@@ -10021,7 +10560,7 @@
         <v>q_anxiety</v>
       </c>
       <c r="K6" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="7" spans="8:11">
@@ -10218,7 +10757,7 @@
     </row>
     <row r="31" spans="8:9">
       <c r="H31" s="33" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
       <c r="I31" s="35" t="str">
         <v>q_mpa_recr_freq</v>
@@ -10226,7 +10765,7 @@
     </row>
     <row r="32" spans="8:9">
       <c r="H32" s="33" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="I32" s="35" t="str">
         <v>q_mpa_recr_minday</v>
@@ -10234,7 +10773,7 @@
     </row>
     <row r="33" spans="8:9">
       <c r="H33" s="33" t="s">
-        <v>1118</v>
+        <v>1112</v>
       </c>
       <c r="I33" s="35" t="str">
         <v>q_mpa_recr_yn</v>
@@ -10378,7 +10917,7 @@
     </row>
     <row r="51" spans="8:9">
       <c r="H51" s="33" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
       <c r="I51" s="35" t="str">
         <v>q_phq_sleep</v>
@@ -10386,7 +10925,7 @@
     </row>
     <row r="52" spans="8:9">
       <c r="H52" s="33" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="I52" s="35" t="str">
         <v>q_phq_slow</v>
